--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1855" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="126">
   <si>
     <t>※ 주간 전담 순서: 1. 차현철 → 2. 진영만 → 3. 박원호 → 4. 한원석 (12주 단위 / 한 줄에 4주씩 배치)</t>
   </si>
@@ -328,62 +328,18 @@
     <t>한원석</t>
   </si>
   <si>
-    <t>9/7 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>9/8 화</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>10/5 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>11/2 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>11/30 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>12/1 화</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>12/28 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>1/25 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>2/22 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>3/22 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>수</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>4/19 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>5/17 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
-    <t>6/14 월</t>
-    <phoneticPr fontId="9" type="noConversion"/>
-  </si>
-  <si>
     <t>본사 배차원 로테이션 근무표 (1주 ~ 48주)</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -397,6 +353,69 @@
   </si>
   <si>
     <t>수</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/31 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>9/28 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/26 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>11/23 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/21 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>1/18 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>2/15 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>새벽</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>3/15 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>4/12 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>5/10 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>6/7 월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/25 월</t>
+  </si>
+  <si>
+    <t>휴일이 주간-&gt;일월-&gt;화수-&gt;목금 순서인 경우</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>휴일이 주간-&gt;목금-&gt;화수-&gt;일월의 순서인 경우</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>=&gt;</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -639,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -714,6 +733,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -722,6 +742,9 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1016,7 +1039,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AD91"/>
+  <dimension ref="B2:AL91"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -1025,100 +1048,100 @@
     <col min="31" max="16384" width="8.796875" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:30">
+    <row r="2" spans="2:38">
       <c r="B2" s="20" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="3" spans="2:30">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="2:38">
       <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:30">
-      <c r="B5" s="32" t="s">
+    <row r="5" spans="2:38">
+      <c r="B5" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="33"/>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="33"/>
-      <c r="P5" s="33"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="33"/>
-      <c r="S5" s="33"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
-      <c r="Y5" s="33"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="33"/>
-      <c r="AB5" s="33"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-    </row>
-    <row r="6" spans="2:30">
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="34"/>
+      <c r="I5" s="34"/>
+      <c r="J5" s="34"/>
+      <c r="K5" s="34"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
+      <c r="X5" s="34"/>
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="34"/>
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="34"/>
+      <c r="AC5" s="34"/>
+      <c r="AD5" s="34"/>
+    </row>
+    <row r="6" spans="2:38">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="31" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="30" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="30" t="s">
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="31"/>
-      <c r="S6" s="31"/>
-      <c r="T6" s="31"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="30" t="s">
+      <c r="R6" s="32"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="32"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="31"/>
-      <c r="Z6" s="31"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="31"/>
-      <c r="AD6" s="31"/>
-    </row>
-    <row r="7" spans="2:30">
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="32"/>
+      <c r="AA6" s="32"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="32"/>
+      <c r="AD6" s="32"/>
+    </row>
+    <row r="7" spans="2:38">
       <c r="B7" s="2"/>
       <c r="C7" s="4" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>10</v>
@@ -1196,7 +1219,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:30">
+    <row r="8" spans="2:38">
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
@@ -1285,7 +1308,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:30">
+    <row r="9" spans="2:38">
       <c r="B9" s="2" t="s">
         <v>100</v>
       </c>
@@ -1374,7 +1397,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:30">
+    <row r="10" spans="2:38">
       <c r="B10" s="2" t="s">
         <v>101</v>
       </c>
@@ -1463,7 +1486,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="2:30">
+    <row r="11" spans="2:38">
       <c r="B11" s="2" t="s">
         <v>102</v>
       </c>
@@ -1552,54 +1575,57 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="2:30">
+    <row r="13" spans="2:38">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="30" t="s">
+      <c r="C13" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="31"/>
-      <c r="E13" s="31"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="30" t="s">
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="31"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="31"/>
-      <c r="Q13" s="30" t="s">
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="R13" s="31"/>
-      <c r="S13" s="31"/>
-      <c r="T13" s="31"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="30" t="s">
+      <c r="R13" s="32"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="32"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="32"/>
+      <c r="X13" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="Y13" s="31"/>
-      <c r="Z13" s="31"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="31"/>
-      <c r="AC13" s="31"/>
-      <c r="AD13" s="31"/>
-    </row>
-    <row r="14" spans="2:30">
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="32"/>
+      <c r="AA13" s="32"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="32"/>
+      <c r="AD13" s="32"/>
+      <c r="AF13" s="30" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="2:38">
       <c r="B14" s="2"/>
       <c r="C14" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>9</v>
@@ -1679,8 +1705,29 @@
       <c r="AD14" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="2:30">
+      <c r="AF14" s="26" t="s">
+        <v>112</v>
+      </c>
+      <c r="AG14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL14" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:38">
       <c r="B15" s="2" t="s">
         <v>99</v>
       </c>
@@ -1768,8 +1815,32 @@
       <c r="AD15" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="2:30">
+      <c r="AE15" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL15" s="24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="2:38">
       <c r="B16" s="2" t="s">
         <v>100</v>
       </c>
@@ -1857,8 +1928,32 @@
       <c r="AD16" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:30">
+      <c r="AE16" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:38">
       <c r="B17" s="2" t="s">
         <v>101</v>
       </c>
@@ -1946,8 +2041,32 @@
       <c r="AD17" s="24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="2:30">
+      <c r="AE17" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:38">
       <c r="B18" s="2" t="s">
         <v>102</v>
       </c>
@@ -2035,52 +2154,79 @@
       <c r="AD18" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20" spans="2:30">
+      <c r="AE18" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL18" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="2:38">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="30" t="s">
+      <c r="C20" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="30" t="s">
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="31"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="30" t="s">
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="R20" s="31"/>
-      <c r="S20" s="31"/>
-      <c r="T20" s="31"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="30" t="s">
+      <c r="R20" s="32"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="32"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="Y20" s="31"/>
-      <c r="Z20" s="31"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="31"/>
-      <c r="AC20" s="31"/>
-      <c r="AD20" s="31"/>
-    </row>
-    <row r="21" spans="2:30">
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="32"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="32"/>
+      <c r="AD20" s="32"/>
+      <c r="AF20" s="30" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="2:38">
       <c r="B21" s="2"/>
       <c r="C21" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>8</v>
@@ -2163,8 +2309,29 @@
       <c r="AD21" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="2:30">
+      <c r="AF21" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL21" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:38">
       <c r="B22" s="2" t="s">
         <v>99</v>
       </c>
@@ -2252,8 +2419,32 @@
       <c r="AD22" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="2:30">
+      <c r="AE22" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL22" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:38">
       <c r="B23" s="2" t="s">
         <v>100</v>
       </c>
@@ -2341,8 +2532,32 @@
       <c r="AD23" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="24" spans="2:30">
+      <c r="AE23" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL23" s="24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="2:38">
       <c r="B24" s="2" t="s">
         <v>101</v>
       </c>
@@ -2430,8 +2645,32 @@
       <c r="AD24" s="24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="25" spans="2:30">
+      <c r="AE24" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL24" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="2:38">
       <c r="B25" s="2" t="s">
         <v>102</v>
       </c>
@@ -2519,85 +2758,109 @@
       <c r="AD25" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="27" spans="2:30">
-      <c r="B27" s="32" t="s">
+      <c r="AE25" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="AF25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL25" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:38">
+      <c r="B27" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="33"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="33"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="33"/>
-      <c r="M27" s="33"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="33"/>
-      <c r="P27" s="33"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="33"/>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="33"/>
-      <c r="Y27" s="33"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="33"/>
-      <c r="AB27" s="33"/>
-      <c r="AC27" s="33"/>
-      <c r="AD27" s="33"/>
-    </row>
-    <row r="28" spans="2:30">
+      <c r="C27" s="34"/>
+      <c r="D27" s="34"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="34"/>
+      <c r="M27" s="34"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="34"/>
+      <c r="P27" s="34"/>
+      <c r="Q27" s="34"/>
+      <c r="R27" s="34"/>
+      <c r="S27" s="34"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="34"/>
+      <c r="Y27" s="34"/>
+      <c r="Z27" s="34"/>
+      <c r="AA27" s="34"/>
+      <c r="AB27" s="34"/>
+      <c r="AC27" s="34"/>
+      <c r="AD27" s="34"/>
+    </row>
+    <row r="28" spans="2:38">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="30" t="s">
+      <c r="C28" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="E28" s="31"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="31"/>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="30" t="s">
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="31"/>
-      <c r="N28" s="31"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="31"/>
-      <c r="Q28" s="30" t="s">
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="31"/>
-      <c r="S28" s="31"/>
-      <c r="T28" s="31"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="30" t="s">
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="Y28" s="31"/>
-      <c r="Z28" s="31"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="31"/>
-      <c r="AC28" s="31"/>
-      <c r="AD28" s="31"/>
-    </row>
-    <row r="29" spans="2:30">
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+    </row>
+    <row r="29" spans="2:38">
       <c r="B29" s="2"/>
-      <c r="C29" s="4" t="s">
-        <v>106</v>
+      <c r="C29" s="26" t="s">
+        <v>112</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>8</v>
@@ -2681,7 +2944,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:30">
+    <row r="30" spans="2:38">
       <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
@@ -2770,7 +3033,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="31" spans="2:30">
+    <row r="31" spans="2:38">
       <c r="B31" s="2" t="s">
         <v>100</v>
       </c>
@@ -2859,7 +3122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:30">
+    <row r="32" spans="2:38">
       <c r="B32" s="2" t="s">
         <v>101</v>
       </c>
@@ -3041,50 +3304,50 @@
       <c r="B35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="30" t="s">
+      <c r="C35" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="31"/>
-      <c r="E35" s="31"/>
-      <c r="F35" s="31"/>
-      <c r="G35" s="31"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="30" t="s">
+      <c r="D35" s="32"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
-      <c r="O35" s="31"/>
-      <c r="P35" s="31"/>
-      <c r="Q35" s="30" t="s">
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
+      <c r="O35" s="32"/>
+      <c r="P35" s="32"/>
+      <c r="Q35" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="31"/>
-      <c r="S35" s="31"/>
-      <c r="T35" s="31"/>
-      <c r="U35" s="31"/>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="30" t="s">
+      <c r="R35" s="32"/>
+      <c r="S35" s="32"/>
+      <c r="T35" s="32"/>
+      <c r="U35" s="32"/>
+      <c r="V35" s="32"/>
+      <c r="W35" s="32"/>
+      <c r="X35" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="Y35" s="31"/>
-      <c r="Z35" s="31"/>
-      <c r="AA35" s="31"/>
-      <c r="AB35" s="31"/>
-      <c r="AC35" s="31"/>
-      <c r="AD35" s="31"/>
+      <c r="Y35" s="32"/>
+      <c r="Z35" s="32"/>
+      <c r="AA35" s="32"/>
+      <c r="AB35" s="32"/>
+      <c r="AC35" s="32"/>
+      <c r="AD35" s="32"/>
     </row>
     <row r="36" spans="2:30" s="29" customFormat="1" ht="13.2">
       <c r="B36" s="25"/>
       <c r="C36" s="26" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D36" s="26" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>9</v>
@@ -3525,47 +3788,47 @@
       <c r="B42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="30" t="s">
+      <c r="C42" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="31"/>
-      <c r="E42" s="31"/>
-      <c r="F42" s="31"/>
-      <c r="G42" s="31"/>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="30" t="s">
+      <c r="D42" s="32"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="K42" s="31"/>
-      <c r="L42" s="31"/>
-      <c r="M42" s="31"/>
-      <c r="N42" s="31"/>
-      <c r="O42" s="31"/>
-      <c r="P42" s="31"/>
-      <c r="Q42" s="30" t="s">
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32"/>
+      <c r="N42" s="32"/>
+      <c r="O42" s="32"/>
+      <c r="P42" s="32"/>
+      <c r="Q42" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="R42" s="31"/>
-      <c r="S42" s="31"/>
-      <c r="T42" s="31"/>
-      <c r="U42" s="31"/>
-      <c r="V42" s="31"/>
-      <c r="W42" s="31"/>
-      <c r="X42" s="30" t="s">
+      <c r="R42" s="32"/>
+      <c r="S42" s="32"/>
+      <c r="T42" s="32"/>
+      <c r="U42" s="32"/>
+      <c r="V42" s="32"/>
+      <c r="W42" s="32"/>
+      <c r="X42" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="Y42" s="31"/>
-      <c r="Z42" s="31"/>
-      <c r="AA42" s="31"/>
-      <c r="AB42" s="31"/>
-      <c r="AC42" s="31"/>
-      <c r="AD42" s="31"/>
+      <c r="Y42" s="32"/>
+      <c r="Z42" s="32"/>
+      <c r="AA42" s="32"/>
+      <c r="AB42" s="32"/>
+      <c r="AC42" s="32"/>
+      <c r="AD42" s="32"/>
     </row>
     <row r="43" spans="2:30">
       <c r="B43" s="2"/>
       <c r="C43" s="26" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>8</v>
@@ -4006,83 +4269,83 @@
       </c>
     </row>
     <row r="49" spans="2:30">
-      <c r="B49" s="32" t="s">
+      <c r="B49" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="33"/>
-      <c r="P49" s="33"/>
-      <c r="Q49" s="33"/>
-      <c r="R49" s="33"/>
-      <c r="S49" s="33"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="33"/>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="33"/>
-      <c r="Y49" s="33"/>
-      <c r="Z49" s="33"/>
-      <c r="AA49" s="33"/>
-      <c r="AB49" s="33"/>
-      <c r="AC49" s="33"/>
-      <c r="AD49" s="33"/>
+      <c r="C49" s="34"/>
+      <c r="D49" s="34"/>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+      <c r="G49" s="34"/>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="34"/>
+      <c r="M49" s="34"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="34"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="34"/>
+      <c r="U49" s="34"/>
+      <c r="V49" s="34"/>
+      <c r="W49" s="34"/>
+      <c r="X49" s="34"/>
+      <c r="Y49" s="34"/>
+      <c r="Z49" s="34"/>
+      <c r="AA49" s="34"/>
+      <c r="AB49" s="34"/>
+      <c r="AC49" s="34"/>
+      <c r="AD49" s="34"/>
     </row>
     <row r="50" spans="2:30">
       <c r="B50" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="30" t="s">
+      <c r="C50" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="31"/>
-      <c r="E50" s="31"/>
-      <c r="F50" s="31"/>
-      <c r="G50" s="31"/>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="30" t="s">
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+      <c r="F50" s="32"/>
+      <c r="G50" s="32"/>
+      <c r="H50" s="32"/>
+      <c r="I50" s="32"/>
+      <c r="J50" s="31" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="31"/>
-      <c r="L50" s="31"/>
-      <c r="M50" s="31"/>
-      <c r="N50" s="31"/>
-      <c r="O50" s="31"/>
-      <c r="P50" s="31"/>
-      <c r="Q50" s="30" t="s">
+      <c r="K50" s="32"/>
+      <c r="L50" s="32"/>
+      <c r="M50" s="32"/>
+      <c r="N50" s="32"/>
+      <c r="O50" s="32"/>
+      <c r="P50" s="32"/>
+      <c r="Q50" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="R50" s="31"/>
-      <c r="S50" s="31"/>
-      <c r="T50" s="31"/>
-      <c r="U50" s="31"/>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="30" t="s">
+      <c r="R50" s="32"/>
+      <c r="S50" s="32"/>
+      <c r="T50" s="32"/>
+      <c r="U50" s="32"/>
+      <c r="V50" s="32"/>
+      <c r="W50" s="32"/>
+      <c r="X50" s="31" t="s">
         <v>45</v>
       </c>
-      <c r="Y50" s="31"/>
-      <c r="Z50" s="31"/>
-      <c r="AA50" s="31"/>
-      <c r="AB50" s="31"/>
-      <c r="AC50" s="31"/>
-      <c r="AD50" s="31"/>
+      <c r="Y50" s="32"/>
+      <c r="Z50" s="32"/>
+      <c r="AA50" s="32"/>
+      <c r="AB50" s="32"/>
+      <c r="AC50" s="32"/>
+      <c r="AD50" s="32"/>
     </row>
     <row r="51" spans="2:30">
       <c r="B51" s="2"/>
       <c r="C51" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>8</v>
@@ -4526,47 +4789,47 @@
       <c r="B57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="30" t="s">
+      <c r="C57" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="31"/>
-      <c r="E57" s="31"/>
-      <c r="F57" s="31"/>
-      <c r="G57" s="31"/>
-      <c r="H57" s="31"/>
-      <c r="I57" s="31"/>
-      <c r="J57" s="30" t="s">
+      <c r="D57" s="32"/>
+      <c r="E57" s="32"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="32"/>
+      <c r="H57" s="32"/>
+      <c r="I57" s="32"/>
+      <c r="J57" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="K57" s="31"/>
-      <c r="L57" s="31"/>
-      <c r="M57" s="31"/>
-      <c r="N57" s="31"/>
-      <c r="O57" s="31"/>
-      <c r="P57" s="31"/>
-      <c r="Q57" s="30" t="s">
+      <c r="K57" s="32"/>
+      <c r="L57" s="32"/>
+      <c r="M57" s="32"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="32"/>
+      <c r="P57" s="32"/>
+      <c r="Q57" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="R57" s="31"/>
-      <c r="S57" s="31"/>
-      <c r="T57" s="31"/>
-      <c r="U57" s="31"/>
-      <c r="V57" s="31"/>
-      <c r="W57" s="31"/>
-      <c r="X57" s="30" t="s">
+      <c r="R57" s="32"/>
+      <c r="S57" s="32"/>
+      <c r="T57" s="32"/>
+      <c r="U57" s="32"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="32"/>
+      <c r="X57" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="Y57" s="31"/>
-      <c r="Z57" s="31"/>
-      <c r="AA57" s="31"/>
-      <c r="AB57" s="31"/>
-      <c r="AC57" s="31"/>
-      <c r="AD57" s="31"/>
+      <c r="Y57" s="32"/>
+      <c r="Z57" s="32"/>
+      <c r="AA57" s="32"/>
+      <c r="AB57" s="32"/>
+      <c r="AC57" s="32"/>
+      <c r="AD57" s="32"/>
     </row>
     <row r="58" spans="2:30">
       <c r="B58" s="2"/>
       <c r="C58" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>8</v>
@@ -4655,7 +4918,7 @@
         <v>99</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>16</v>
+        <v>117</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>16</v>
@@ -5010,53 +5273,53 @@
       <c r="B64" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="30" t="s">
+      <c r="C64" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="D64" s="31"/>
-      <c r="E64" s="31"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="31"/>
-      <c r="H64" s="31"/>
-      <c r="I64" s="31"/>
-      <c r="J64" s="30" t="s">
+      <c r="D64" s="32"/>
+      <c r="E64" s="32"/>
+      <c r="F64" s="32"/>
+      <c r="G64" s="32"/>
+      <c r="H64" s="32"/>
+      <c r="I64" s="32"/>
+      <c r="J64" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="K64" s="31"/>
-      <c r="L64" s="31"/>
-      <c r="M64" s="31"/>
-      <c r="N64" s="31"/>
-      <c r="O64" s="31"/>
-      <c r="P64" s="31"/>
-      <c r="Q64" s="30" t="s">
+      <c r="K64" s="32"/>
+      <c r="L64" s="32"/>
+      <c r="M64" s="32"/>
+      <c r="N64" s="32"/>
+      <c r="O64" s="32"/>
+      <c r="P64" s="32"/>
+      <c r="Q64" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="R64" s="31"/>
-      <c r="S64" s="31"/>
-      <c r="T64" s="31"/>
-      <c r="U64" s="31"/>
-      <c r="V64" s="31"/>
-      <c r="W64" s="31"/>
-      <c r="X64" s="30" t="s">
+      <c r="R64" s="32"/>
+      <c r="S64" s="32"/>
+      <c r="T64" s="32"/>
+      <c r="U64" s="32"/>
+      <c r="V64" s="32"/>
+      <c r="W64" s="32"/>
+      <c r="X64" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="Y64" s="31"/>
-      <c r="Z64" s="31"/>
-      <c r="AA64" s="31"/>
-      <c r="AB64" s="31"/>
-      <c r="AC64" s="31"/>
-      <c r="AD64" s="31"/>
+      <c r="Y64" s="32"/>
+      <c r="Z64" s="32"/>
+      <c r="AA64" s="32"/>
+      <c r="AB64" s="32"/>
+      <c r="AC64" s="32"/>
+      <c r="AD64" s="32"/>
     </row>
     <row r="65" spans="2:30">
       <c r="B65" s="2"/>
       <c r="C65" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>8</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>10</v>
@@ -5491,83 +5754,83 @@
       </c>
     </row>
     <row r="71" spans="2:30">
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="33" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="33"/>
-      <c r="T71" s="33"/>
-      <c r="U71" s="33"/>
-      <c r="V71" s="33"/>
-      <c r="W71" s="33"/>
-      <c r="X71" s="33"/>
-      <c r="Y71" s="33"/>
-      <c r="Z71" s="33"/>
-      <c r="AA71" s="33"/>
-      <c r="AB71" s="33"/>
-      <c r="AC71" s="33"/>
-      <c r="AD71" s="33"/>
+      <c r="C71" s="34"/>
+      <c r="D71" s="34"/>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="34"/>
+      <c r="M71" s="34"/>
+      <c r="N71" s="34"/>
+      <c r="O71" s="34"/>
+      <c r="P71" s="34"/>
+      <c r="Q71" s="34"/>
+      <c r="R71" s="34"/>
+      <c r="S71" s="34"/>
+      <c r="T71" s="34"/>
+      <c r="U71" s="34"/>
+      <c r="V71" s="34"/>
+      <c r="W71" s="34"/>
+      <c r="X71" s="34"/>
+      <c r="Y71" s="34"/>
+      <c r="Z71" s="34"/>
+      <c r="AA71" s="34"/>
+      <c r="AB71" s="34"/>
+      <c r="AC71" s="34"/>
+      <c r="AD71" s="34"/>
     </row>
     <row r="72" spans="2:30">
       <c r="B72" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="30" t="s">
+      <c r="C72" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="31"/>
-      <c r="E72" s="31"/>
-      <c r="F72" s="31"/>
-      <c r="G72" s="31"/>
-      <c r="H72" s="31"/>
-      <c r="I72" s="31"/>
-      <c r="J72" s="30" t="s">
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="32"/>
+      <c r="G72" s="32"/>
+      <c r="H72" s="32"/>
+      <c r="I72" s="32"/>
+      <c r="J72" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="K72" s="31"/>
-      <c r="L72" s="31"/>
-      <c r="M72" s="31"/>
-      <c r="N72" s="31"/>
-      <c r="O72" s="31"/>
-      <c r="P72" s="31"/>
-      <c r="Q72" s="30" t="s">
+      <c r="K72" s="32"/>
+      <c r="L72" s="32"/>
+      <c r="M72" s="32"/>
+      <c r="N72" s="32"/>
+      <c r="O72" s="32"/>
+      <c r="P72" s="32"/>
+      <c r="Q72" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="R72" s="31"/>
-      <c r="S72" s="31"/>
-      <c r="T72" s="31"/>
-      <c r="U72" s="31"/>
-      <c r="V72" s="31"/>
-      <c r="W72" s="31"/>
-      <c r="X72" s="30" t="s">
+      <c r="R72" s="32"/>
+      <c r="S72" s="32"/>
+      <c r="T72" s="32"/>
+      <c r="U72" s="32"/>
+      <c r="V72" s="32"/>
+      <c r="W72" s="32"/>
+      <c r="X72" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="Y72" s="31"/>
-      <c r="Z72" s="31"/>
-      <c r="AA72" s="31"/>
-      <c r="AB72" s="31"/>
-      <c r="AC72" s="31"/>
-      <c r="AD72" s="31"/>
+      <c r="Y72" s="32"/>
+      <c r="Z72" s="32"/>
+      <c r="AA72" s="32"/>
+      <c r="AB72" s="32"/>
+      <c r="AC72" s="32"/>
+      <c r="AD72" s="32"/>
     </row>
     <row r="73" spans="2:30">
       <c r="B73" s="2"/>
       <c r="C73" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>8</v>
@@ -6011,47 +6274,47 @@
       <c r="B79" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="30" t="s">
+      <c r="C79" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="D79" s="31"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="31"/>
-      <c r="I79" s="31"/>
-      <c r="J79" s="30" t="s">
+      <c r="D79" s="32"/>
+      <c r="E79" s="32"/>
+      <c r="F79" s="32"/>
+      <c r="G79" s="32"/>
+      <c r="H79" s="32"/>
+      <c r="I79" s="32"/>
+      <c r="J79" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="K79" s="31"/>
-      <c r="L79" s="31"/>
-      <c r="M79" s="31"/>
-      <c r="N79" s="31"/>
-      <c r="O79" s="31"/>
-      <c r="P79" s="31"/>
-      <c r="Q79" s="30" t="s">
+      <c r="K79" s="32"/>
+      <c r="L79" s="32"/>
+      <c r="M79" s="32"/>
+      <c r="N79" s="32"/>
+      <c r="O79" s="32"/>
+      <c r="P79" s="32"/>
+      <c r="Q79" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="R79" s="31"/>
-      <c r="S79" s="31"/>
-      <c r="T79" s="31"/>
-      <c r="U79" s="31"/>
-      <c r="V79" s="31"/>
-      <c r="W79" s="31"/>
-      <c r="X79" s="30" t="s">
+      <c r="R79" s="32"/>
+      <c r="S79" s="32"/>
+      <c r="T79" s="32"/>
+      <c r="U79" s="32"/>
+      <c r="V79" s="32"/>
+      <c r="W79" s="32"/>
+      <c r="X79" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="Y79" s="31"/>
-      <c r="Z79" s="31"/>
-      <c r="AA79" s="31"/>
-      <c r="AB79" s="31"/>
-      <c r="AC79" s="31"/>
-      <c r="AD79" s="31"/>
+      <c r="Y79" s="32"/>
+      <c r="Z79" s="32"/>
+      <c r="AA79" s="32"/>
+      <c r="AB79" s="32"/>
+      <c r="AC79" s="32"/>
+      <c r="AD79" s="32"/>
     </row>
     <row r="80" spans="2:30">
       <c r="B80" s="2"/>
       <c r="C80" s="4" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D80" s="4" t="s">
         <v>8</v>
@@ -6495,47 +6758,47 @@
       <c r="B86" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="30" t="s">
+      <c r="C86" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="D86" s="31"/>
-      <c r="E86" s="31"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="31"/>
-      <c r="H86" s="31"/>
-      <c r="I86" s="31"/>
-      <c r="J86" s="30" t="s">
+      <c r="D86" s="32"/>
+      <c r="E86" s="32"/>
+      <c r="F86" s="32"/>
+      <c r="G86" s="32"/>
+      <c r="H86" s="32"/>
+      <c r="I86" s="32"/>
+      <c r="J86" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="K86" s="31"/>
-      <c r="L86" s="31"/>
-      <c r="M86" s="31"/>
-      <c r="N86" s="31"/>
-      <c r="O86" s="31"/>
-      <c r="P86" s="31"/>
-      <c r="Q86" s="30" t="s">
+      <c r="K86" s="32"/>
+      <c r="L86" s="32"/>
+      <c r="M86" s="32"/>
+      <c r="N86" s="32"/>
+      <c r="O86" s="32"/>
+      <c r="P86" s="32"/>
+      <c r="Q86" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="R86" s="31"/>
-      <c r="S86" s="31"/>
-      <c r="T86" s="31"/>
-      <c r="U86" s="31"/>
-      <c r="V86" s="31"/>
-      <c r="W86" s="31"/>
-      <c r="X86" s="30" t="s">
+      <c r="R86" s="32"/>
+      <c r="S86" s="32"/>
+      <c r="T86" s="32"/>
+      <c r="U86" s="32"/>
+      <c r="V86" s="32"/>
+      <c r="W86" s="32"/>
+      <c r="X86" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="Y86" s="31"/>
-      <c r="Z86" s="31"/>
-      <c r="AA86" s="31"/>
-      <c r="AB86" s="31"/>
-      <c r="AC86" s="31"/>
-      <c r="AD86" s="31"/>
+      <c r="Y86" s="32"/>
+      <c r="Z86" s="32"/>
+      <c r="AA86" s="32"/>
+      <c r="AB86" s="32"/>
+      <c r="AC86" s="32"/>
+      <c r="AD86" s="32"/>
     </row>
     <row r="87" spans="2:30">
       <c r="B87" s="2"/>
       <c r="C87" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="D87" s="4" t="s">
         <v>8</v>

--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2161" uniqueCount="130">
   <si>
     <t>※ 주간 전담 순서: 1. 차현철 → 2. 진영만 → 3. 박원호 → 4. 한원석 (12주 단위 / 한 줄에 4주씩 배치)</t>
   </si>
@@ -404,9 +404,6 @@
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
   <si>
-    <t>10/25 월</t>
-  </si>
-  <si>
     <t>휴일이 주간-&gt;일월-&gt;화수-&gt;목금 순서인 경우</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
@@ -416,6 +413,26 @@
   </si>
   <si>
     <t>=&gt;</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>주간이 변경시 새벽으로 가는 경우</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>주간이 변경시 야간으로 가는 경우</t>
+    <phoneticPr fontId="9" type="noConversion"/>
+  </si>
+  <si>
+    <t>전주</t>
     <phoneticPr fontId="9" type="noConversion"/>
   </si>
 </sst>
@@ -560,7 +577,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -615,6 +632,18 @@
         <bgColor rgb="FFEDF2F8"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -658,7 +687,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -734,17 +763,19 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1039,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AL91"/>
+  <dimension ref="B2:AT91"/>
   <sheetFormatPr defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3" style="21" customWidth="1"/>
@@ -1048,91 +1079,91 @@
     <col min="31" max="16384" width="8.796875" style="21"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:38">
+    <row r="2" spans="2:46">
       <c r="B2" s="20" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="2:38">
+    <row r="3" spans="2:46">
       <c r="B3" s="22" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:38">
-      <c r="B5" s="33" t="s">
+    <row r="5" spans="2:46">
+      <c r="B5" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34"/>
-      <c r="X5" s="34"/>
-      <c r="Y5" s="34"/>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34"/>
-      <c r="AB5" s="34"/>
-      <c r="AC5" s="34"/>
-      <c r="AD5" s="34"/>
-    </row>
-    <row r="6" spans="2:38">
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="33"/>
+    </row>
+    <row r="6" spans="2:46">
       <c r="B6" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="31" t="s">
+      <c r="D6" s="35"/>
+      <c r="E6" s="35"/>
+      <c r="F6" s="35"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="35"/>
+      <c r="J6" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="32"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="31" t="s">
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="32"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="31" t="s">
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+      <c r="X6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="32"/>
-      <c r="AA6" s="32"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="32"/>
-      <c r="AD6" s="32"/>
-    </row>
-    <row r="7" spans="2:38">
+      <c r="Y6" s="35"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="35"/>
+      <c r="AD6" s="35"/>
+    </row>
+    <row r="7" spans="2:46">
       <c r="B7" s="2"/>
       <c r="C7" s="4" t="s">
         <v>107</v>
@@ -1219,7 +1250,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:38">
+    <row r="8" spans="2:46">
       <c r="B8" s="2" t="s">
         <v>99</v>
       </c>
@@ -1308,7 +1339,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:38">
+    <row r="9" spans="2:46">
       <c r="B9" s="2" t="s">
         <v>100</v>
       </c>
@@ -1397,7 +1428,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:38">
+    <row r="10" spans="2:46">
       <c r="B10" s="2" t="s">
         <v>101</v>
       </c>
@@ -1486,7 +1517,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="2:38">
+    <row r="11" spans="2:46">
       <c r="B11" s="2" t="s">
         <v>102</v>
       </c>
@@ -1575,51 +1606,75 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="2:38">
+    <row r="12" spans="2:46">
+      <c r="AN12" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO12" s="36"/>
+      <c r="AP12" s="36"/>
+      <c r="AQ12" s="36"/>
+    </row>
+    <row r="13" spans="2:46">
       <c r="B13" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="31" t="s">
+      <c r="C13" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="31" t="s">
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="32"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
-      <c r="O13" s="32"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="31" t="s">
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35"/>
+      <c r="Q13" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="R13" s="32"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="32"/>
-      <c r="U13" s="32"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="32"/>
-      <c r="X13" s="31" t="s">
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="32"/>
-      <c r="AA13" s="32"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="32"/>
-      <c r="AD13" s="32"/>
-      <c r="AF13" s="30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="2:38">
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="35"/>
+      <c r="AF13" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG13" s="35"/>
+      <c r="AH13" s="35"/>
+      <c r="AI13" s="35"/>
+      <c r="AJ13" s="35"/>
+      <c r="AK13" s="35"/>
+      <c r="AL13" s="35"/>
+      <c r="AM13" s="30"/>
+      <c r="AN13" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO13" s="37"/>
+      <c r="AP13" s="37"/>
+      <c r="AQ13" s="37"/>
+      <c r="AR13" s="30"/>
+      <c r="AS13" s="30"/>
+      <c r="AT13" s="30"/>
+    </row>
+    <row r="14" spans="2:46">
       <c r="B14" s="2"/>
       <c r="C14" s="4" t="s">
         <v>110</v>
@@ -1705,8 +1760,8 @@
       <c r="AD14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AF14" s="26" t="s">
-        <v>112</v>
+      <c r="AF14" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="AG14" s="4" t="s">
         <v>8</v>
@@ -1726,8 +1781,30 @@
       <c r="AL14" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="15" spans="2:38">
+      <c r="AM14" s="30"/>
+      <c r="AN14" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="AO14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS14" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT14" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="2:46">
       <c r="B15" s="2" t="s">
         <v>99</v>
       </c>
@@ -1815,17 +1892,15 @@
       <c r="AD15" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AE15" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG15" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH15" s="4" t="s">
-        <v>15</v>
+      <c r="AE15" s="31"/>
+      <c r="AF15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH15" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="AI15" s="8" t="s">
         <v>16</v>
@@ -1836,11 +1911,35 @@
       <c r="AK15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AL15" s="24" t="s">
+      <c r="AL15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM15" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP15" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS15" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT15" s="24" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="16" spans="2:38">
+    <row r="16" spans="2:46">
       <c r="B16" s="2" t="s">
         <v>100</v>
       </c>
@@ -1928,32 +2027,54 @@
       <c r="AD16" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AE16" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF16" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ16" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK16" s="9" t="s">
-        <v>18</v>
+      <c r="AE16" s="31"/>
+      <c r="AF16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ16" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK16" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="AL16" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="17" spans="2:38">
+      <c r="AM16" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN16" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS16" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT16" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:46">
       <c r="B17" s="2" t="s">
         <v>101</v>
       </c>
@@ -2041,32 +2162,54 @@
       <c r="AD17" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="AE17" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ17" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK17" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL17" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="2:38">
+      <c r="AE17" s="31"/>
+      <c r="AF17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH17" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL17" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM17" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR17" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS17" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT17" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:46">
       <c r="B18" s="2" t="s">
         <v>102</v>
       </c>
@@ -2154,76 +2297,131 @@
       <c r="AD18" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="AE18" s="35" t="s">
-        <v>125</v>
-      </c>
+      <c r="AE18" s="31"/>
       <c r="AF18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="AG18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ18" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK18" s="7" t="s">
-        <v>14</v>
+      <c r="AG18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ18" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK18" s="9" t="s">
+        <v>18</v>
       </c>
       <c r="AL18" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="20" spans="2:38">
+      <c r="AM18" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP18" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR18" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS18" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT18" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="2:46">
+      <c r="AF19" s="30"/>
+      <c r="AG19" s="30"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="30"/>
+      <c r="AJ19" s="30"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="30"/>
+      <c r="AM19" s="30"/>
+      <c r="AN19" s="30"/>
+      <c r="AO19" s="30"/>
+      <c r="AP19" s="30"/>
+      <c r="AQ19" s="30"/>
+      <c r="AR19" s="30"/>
+      <c r="AS19" s="30"/>
+      <c r="AT19" s="30"/>
+    </row>
+    <row r="20" spans="2:46">
       <c r="B20" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="31" t="s">
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="K20" s="32"/>
-      <c r="L20" s="32"/>
-      <c r="M20" s="32"/>
-      <c r="N20" s="32"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="31" t="s">
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="R20" s="32"/>
-      <c r="S20" s="32"/>
-      <c r="T20" s="32"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="32"/>
-      <c r="X20" s="31" t="s">
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="Y20" s="32"/>
-      <c r="Z20" s="32"/>
-      <c r="AA20" s="32"/>
-      <c r="AB20" s="32"/>
-      <c r="AC20" s="32"/>
-      <c r="AD20" s="32"/>
-      <c r="AF20" s="30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="2:38">
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="35"/>
+      <c r="AD20" s="35"/>
+      <c r="AF20" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="35"/>
+      <c r="AI20" s="35"/>
+      <c r="AJ20" s="35"/>
+      <c r="AK20" s="35"/>
+      <c r="AL20" s="35"/>
+      <c r="AM20" s="30"/>
+      <c r="AN20" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO20" s="30"/>
+      <c r="AP20" s="30"/>
+      <c r="AQ20" s="30"/>
+      <c r="AR20" s="30"/>
+      <c r="AS20" s="30"/>
+      <c r="AT20" s="30"/>
+    </row>
+    <row r="21" spans="2:46">
       <c r="B21" s="2"/>
       <c r="C21" s="4" t="s">
         <v>111</v>
@@ -2309,8 +2507,8 @@
       <c r="AD21" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="AF21" s="26" t="s">
-        <v>122</v>
+      <c r="AF21" s="4" t="s">
+        <v>7</v>
       </c>
       <c r="AG21" s="4" t="s">
         <v>8</v>
@@ -2330,8 +2528,30 @@
       <c r="AL21" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="22" spans="2:38">
+      <c r="AM21" s="30"/>
+      <c r="AN21" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO21" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP21" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ21" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS21" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT21" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="2:46">
       <c r="B22" s="2" t="s">
         <v>99</v>
       </c>
@@ -2419,32 +2639,54 @@
       <c r="AD22" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AE22" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AG22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AH22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AI22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AJ22" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AK22" s="4" t="s">
-        <v>15</v>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ22" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK22" s="8" t="s">
+        <v>16</v>
       </c>
       <c r="AL22" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="2:38">
+      <c r="AM22" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS22" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT22" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:46">
       <c r="B23" s="2" t="s">
         <v>100</v>
       </c>
@@ -2532,32 +2774,54 @@
       <c r="AD23" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="AE23" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AG23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AH23" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AI23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ23" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK23" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL23" s="24" t="s">
+      <c r="AE23" s="31"/>
+      <c r="AF23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM23" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP23" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR23" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS23" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT23" s="24" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="24" spans="2:38">
+    <row r="24" spans="2:46">
       <c r="B24" s="2" t="s">
         <v>101</v>
       </c>
@@ -2645,32 +2909,54 @@
       <c r="AD24" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="AE24" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF24" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AJ24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AK24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="AL24" s="23" t="s">
+      <c r="AE24" s="31"/>
+      <c r="AF24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK24" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL24" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM24" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN24" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP24" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS24" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT24" s="23" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="25" spans="2:38">
+    <row r="25" spans="2:46">
       <c r="B25" s="2" t="s">
         <v>102</v>
       </c>
@@ -2758,106 +3044,153 @@
       <c r="AD25" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="AE25" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="AF25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AH25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AI25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AJ25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AK25" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="AL25" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:38">
-      <c r="B27" s="33" t="s">
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK25" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL25" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM25" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN25" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS25" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT25" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:46">
+      <c r="B27" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
-      <c r="K27" s="34"/>
-      <c r="L27" s="34"/>
-      <c r="M27" s="34"/>
-      <c r="N27" s="34"/>
-      <c r="O27" s="34"/>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="34"/>
-      <c r="R27" s="34"/>
-      <c r="S27" s="34"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-      <c r="X27" s="34"/>
-      <c r="Y27" s="34"/>
-      <c r="Z27" s="34"/>
-      <c r="AA27" s="34"/>
-      <c r="AB27" s="34"/>
-      <c r="AC27" s="34"/>
-      <c r="AD27" s="34"/>
-    </row>
-    <row r="28" spans="2:38">
+      <c r="C27" s="33"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="33"/>
+      <c r="M27" s="33"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="33"/>
+      <c r="P27" s="33"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="33"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="33"/>
+      <c r="Y27" s="33"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="33"/>
+      <c r="AB27" s="33"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="33"/>
+      <c r="AN27" s="36" t="s">
+        <v>127</v>
+      </c>
+      <c r="AO27" s="36"/>
+      <c r="AP27" s="36"/>
+      <c r="AQ27" s="36"/>
+    </row>
+    <row r="28" spans="2:46">
       <c r="B28" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="31" t="s">
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="34" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="31" t="s">
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="35"/>
+      <c r="O28" s="35"/>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="34" t="s">
         <v>31</v>
       </c>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32"/>
-      <c r="X28" s="31" t="s">
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="34" t="s">
         <v>32</v>
       </c>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-    </row>
-    <row r="29" spans="2:38">
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AF28" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG28" s="35"/>
+      <c r="AH28" s="35"/>
+      <c r="AI28" s="35"/>
+      <c r="AJ28" s="35"/>
+      <c r="AK28" s="35"/>
+      <c r="AL28" s="35"/>
+      <c r="AM28" s="30"/>
+      <c r="AN28" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="AO28" s="37"/>
+      <c r="AP28" s="37"/>
+      <c r="AQ28" s="37"/>
+      <c r="AR28" s="30"/>
+      <c r="AS28" s="30"/>
+      <c r="AT28" s="30"/>
+    </row>
+    <row r="29" spans="2:46">
       <c r="B29" s="2"/>
       <c r="C29" s="26" t="s">
         <v>112</v>
@@ -2943,8 +3276,51 @@
       <c r="AD29" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="2:38">
+      <c r="AF29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL29" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM29" s="30"/>
+      <c r="AN29" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="AO29" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ29" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR29" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS29" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT29" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="2:46">
       <c r="B30" s="2" t="s">
         <v>99</v>
       </c>
@@ -3032,8 +3408,53 @@
       <c r="AD30" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="31" spans="2:38">
+      <c r="AF30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM30" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN30" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP30" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS30" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT30" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="2:46">
       <c r="B31" s="2" t="s">
         <v>100</v>
       </c>
@@ -3121,8 +3542,53 @@
       <c r="AD31" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="32" spans="2:38">
+      <c r="AF31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ31" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM31" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN31" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS31" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT31" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="2:46">
       <c r="B32" s="2" t="s">
         <v>101</v>
       </c>
@@ -3210,8 +3676,53 @@
       <c r="AD32" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="2:30">
+      <c r="AF32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH32" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL32" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM32" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR32" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS32" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT32" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:46">
       <c r="B33" s="2" t="s">
         <v>102</v>
       </c>
@@ -3299,49 +3810,130 @@
       <c r="AD33" s="24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="35" spans="2:30">
+      <c r="AF33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK33" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL33" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM33" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP33" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR33" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS33" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT33" s="24" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="2:46">
+      <c r="AF34" s="30"/>
+      <c r="AG34" s="30"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="30"/>
+      <c r="AJ34" s="30"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="30"/>
+      <c r="AM34" s="30"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="30"/>
+      <c r="AP34" s="30"/>
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="30"/>
+      <c r="AS34" s="30"/>
+      <c r="AT34" s="30"/>
+    </row>
+    <row r="35" spans="2:46">
       <c r="B35" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="D35" s="32"/>
-      <c r="E35" s="32"/>
-      <c r="F35" s="32"/>
-      <c r="G35" s="32"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
-      <c r="J35" s="31" t="s">
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="K35" s="32"/>
-      <c r="L35" s="32"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
-      <c r="O35" s="32"/>
-      <c r="P35" s="32"/>
-      <c r="Q35" s="31" t="s">
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="34" t="s">
         <v>35</v>
       </c>
-      <c r="R35" s="32"/>
-      <c r="S35" s="32"/>
-      <c r="T35" s="32"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="32"/>
-      <c r="X35" s="31" t="s">
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="Y35" s="32"/>
-      <c r="Z35" s="32"/>
-      <c r="AA35" s="32"/>
-      <c r="AB35" s="32"/>
-      <c r="AC35" s="32"/>
-      <c r="AD35" s="32"/>
-    </row>
-    <row r="36" spans="2:30" s="29" customFormat="1" ht="13.2">
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
+      <c r="AC35" s="35"/>
+      <c r="AD35" s="35"/>
+      <c r="AF35" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG35" s="35"/>
+      <c r="AH35" s="35"/>
+      <c r="AI35" s="35"/>
+      <c r="AJ35" s="35"/>
+      <c r="AK35" s="35"/>
+      <c r="AL35" s="35"/>
+      <c r="AM35" s="30"/>
+      <c r="AN35" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="AO35" s="30"/>
+      <c r="AP35" s="30"/>
+      <c r="AQ35" s="30"/>
+      <c r="AR35" s="30"/>
+      <c r="AS35" s="30"/>
+      <c r="AT35" s="30"/>
+    </row>
+    <row r="36" spans="2:46" s="29" customFormat="1">
       <c r="B36" s="25"/>
       <c r="C36" s="26" t="s">
         <v>113</v>
@@ -3427,8 +4019,51 @@
       <c r="AD36" s="28" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="2:30">
+      <c r="AF36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL36" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM36" s="30"/>
+      <c r="AN36" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="AO36" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP36" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ36" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS36" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="2:46">
       <c r="B37" s="2" t="s">
         <v>99</v>
       </c>
@@ -3516,8 +4151,53 @@
       <c r="AD37" s="23" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="38" spans="2:30">
+      <c r="AF37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AH37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AI37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AJ37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AK37" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM37" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR37" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS37" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT37" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:46">
       <c r="B38" s="2" t="s">
         <v>100</v>
       </c>
@@ -3605,8 +4285,53 @@
       <c r="AD38" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="39" spans="2:30">
+      <c r="AF38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM38" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP38" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR38" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS38" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT38" s="23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="39" spans="2:46">
       <c r="B39" s="2" t="s">
         <v>101</v>
       </c>
@@ -3694,8 +4419,53 @@
       <c r="AD39" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="40" spans="2:30">
+      <c r="AF39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK39" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL39" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="AM39" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP39" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS39" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT39" s="8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:46">
       <c r="B40" s="2" t="s">
         <v>102</v>
       </c>
@@ -3783,49 +4553,94 @@
       <c r="AD40" s="24" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="42" spans="2:30">
+      <c r="AF40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL40" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AM40" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="AN40" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AP40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AQ40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AR40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AS40" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="AT40" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:46">
       <c r="B42" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="31" t="s">
+      <c r="C42" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="D42" s="32"/>
-      <c r="E42" s="32"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="32"/>
-      <c r="H42" s="32"/>
-      <c r="I42" s="32"/>
-      <c r="J42" s="31" t="s">
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="34" t="s">
         <v>38</v>
       </c>
-      <c r="K42" s="32"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="32"/>
-      <c r="N42" s="32"/>
-      <c r="O42" s="32"/>
-      <c r="P42" s="32"/>
-      <c r="Q42" s="31" t="s">
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
+      <c r="M42" s="35"/>
+      <c r="N42" s="35"/>
+      <c r="O42" s="35"/>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="R42" s="32"/>
-      <c r="S42" s="32"/>
-      <c r="T42" s="32"/>
-      <c r="U42" s="32"/>
-      <c r="V42" s="32"/>
-      <c r="W42" s="32"/>
-      <c r="X42" s="31" t="s">
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="35"/>
+      <c r="X42" s="34" t="s">
         <v>40</v>
       </c>
-      <c r="Y42" s="32"/>
-      <c r="Z42" s="32"/>
-      <c r="AA42" s="32"/>
-      <c r="AB42" s="32"/>
-      <c r="AC42" s="32"/>
-      <c r="AD42" s="32"/>
-    </row>
-    <row r="43" spans="2:30">
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35"/>
+      <c r="AA42" s="35"/>
+      <c r="AB42" s="35"/>
+      <c r="AC42" s="35"/>
+      <c r="AD42" s="35"/>
+    </row>
+    <row r="43" spans="2:46">
       <c r="B43" s="2"/>
       <c r="C43" s="26" t="s">
         <v>114</v>
@@ -3912,7 +4727,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:30">
+    <row r="44" spans="2:46">
       <c r="B44" s="2" t="s">
         <v>99</v>
       </c>
@@ -4001,7 +4816,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="45" spans="2:30">
+    <row r="45" spans="2:46">
       <c r="B45" s="2" t="s">
         <v>100</v>
       </c>
@@ -4090,7 +4905,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:30">
+    <row r="46" spans="2:46">
       <c r="B46" s="2" t="s">
         <v>101</v>
       </c>
@@ -4179,7 +4994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:30">
+    <row r="47" spans="2:46">
       <c r="B47" s="2" t="s">
         <v>102</v>
       </c>
@@ -4269,78 +5084,78 @@
       </c>
     </row>
     <row r="49" spans="2:30">
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="34"/>
-      <c r="F49" s="34"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="34"/>
-      <c r="I49" s="34"/>
-      <c r="J49" s="34"/>
-      <c r="K49" s="34"/>
-      <c r="L49" s="34"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-      <c r="X49" s="34"/>
-      <c r="Y49" s="34"/>
-      <c r="Z49" s="34"/>
-      <c r="AA49" s="34"/>
-      <c r="AB49" s="34"/>
-      <c r="AC49" s="34"/>
-      <c r="AD49" s="34"/>
+      <c r="C49" s="33"/>
+      <c r="D49" s="33"/>
+      <c r="E49" s="33"/>
+      <c r="F49" s="33"/>
+      <c r="G49" s="33"/>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="33"/>
+      <c r="M49" s="33"/>
+      <c r="N49" s="33"/>
+      <c r="O49" s="33"/>
+      <c r="P49" s="33"/>
+      <c r="Q49" s="33"/>
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="33"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="33"/>
+      <c r="Y49" s="33"/>
+      <c r="Z49" s="33"/>
+      <c r="AA49" s="33"/>
+      <c r="AB49" s="33"/>
+      <c r="AC49" s="33"/>
+      <c r="AD49" s="33"/>
     </row>
     <row r="50" spans="2:30">
       <c r="B50" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="31" t="s">
+      <c r="C50" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="32"/>
-      <c r="H50" s="32"/>
-      <c r="I50" s="32"/>
-      <c r="J50" s="31" t="s">
+      <c r="D50" s="35"/>
+      <c r="E50" s="35"/>
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="34" t="s">
         <v>43</v>
       </c>
-      <c r="K50" s="32"/>
-      <c r="L50" s="32"/>
-      <c r="M50" s="32"/>
-      <c r="N50" s="32"/>
-      <c r="O50" s="32"/>
-      <c r="P50" s="32"/>
-      <c r="Q50" s="31" t="s">
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="34" t="s">
         <v>44</v>
       </c>
-      <c r="R50" s="32"/>
-      <c r="S50" s="32"/>
-      <c r="T50" s="32"/>
-      <c r="U50" s="32"/>
-      <c r="V50" s="32"/>
-      <c r="W50" s="32"/>
-      <c r="X50" s="31" t="s">
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="34" t="s">
         <v>45</v>
       </c>
-      <c r="Y50" s="32"/>
-      <c r="Z50" s="32"/>
-      <c r="AA50" s="32"/>
-      <c r="AB50" s="32"/>
-      <c r="AC50" s="32"/>
-      <c r="AD50" s="32"/>
+      <c r="Y50" s="35"/>
+      <c r="Z50" s="35"/>
+      <c r="AA50" s="35"/>
+      <c r="AB50" s="35"/>
+      <c r="AC50" s="35"/>
+      <c r="AD50" s="35"/>
     </row>
     <row r="51" spans="2:30">
       <c r="B51" s="2"/>
@@ -4789,42 +5604,42 @@
       <c r="B57" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="34" t="s">
         <v>46</v>
       </c>
-      <c r="D57" s="32"/>
-      <c r="E57" s="32"/>
-      <c r="F57" s="32"/>
-      <c r="G57" s="32"/>
-      <c r="H57" s="32"/>
-      <c r="I57" s="32"/>
-      <c r="J57" s="31" t="s">
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="K57" s="32"/>
-      <c r="L57" s="32"/>
-      <c r="M57" s="32"/>
-      <c r="N57" s="32"/>
-      <c r="O57" s="32"/>
-      <c r="P57" s="32"/>
-      <c r="Q57" s="31" t="s">
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="34" t="s">
         <v>48</v>
       </c>
-      <c r="R57" s="32"/>
-      <c r="S57" s="32"/>
-      <c r="T57" s="32"/>
-      <c r="U57" s="32"/>
-      <c r="V57" s="32"/>
-      <c r="W57" s="32"/>
-      <c r="X57" s="31" t="s">
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
+      <c r="T57" s="35"/>
+      <c r="U57" s="35"/>
+      <c r="V57" s="35"/>
+      <c r="W57" s="35"/>
+      <c r="X57" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="Y57" s="32"/>
-      <c r="Z57" s="32"/>
-      <c r="AA57" s="32"/>
-      <c r="AB57" s="32"/>
-      <c r="AC57" s="32"/>
-      <c r="AD57" s="32"/>
+      <c r="Y57" s="35"/>
+      <c r="Z57" s="35"/>
+      <c r="AA57" s="35"/>
+      <c r="AB57" s="35"/>
+      <c r="AC57" s="35"/>
+      <c r="AD57" s="35"/>
     </row>
     <row r="58" spans="2:30">
       <c r="B58" s="2"/>
@@ -5273,42 +6088,42 @@
       <c r="B64" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="31" t="s">
+      <c r="C64" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="D64" s="32"/>
-      <c r="E64" s="32"/>
-      <c r="F64" s="32"/>
-      <c r="G64" s="32"/>
-      <c r="H64" s="32"/>
-      <c r="I64" s="32"/>
-      <c r="J64" s="31" t="s">
+      <c r="D64" s="35"/>
+      <c r="E64" s="35"/>
+      <c r="F64" s="35"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="35"/>
+      <c r="J64" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="K64" s="32"/>
-      <c r="L64" s="32"/>
-      <c r="M64" s="32"/>
-      <c r="N64" s="32"/>
-      <c r="O64" s="32"/>
-      <c r="P64" s="32"/>
-      <c r="Q64" s="31" t="s">
+      <c r="K64" s="35"/>
+      <c r="L64" s="35"/>
+      <c r="M64" s="35"/>
+      <c r="N64" s="35"/>
+      <c r="O64" s="35"/>
+      <c r="P64" s="35"/>
+      <c r="Q64" s="34" t="s">
         <v>52</v>
       </c>
-      <c r="R64" s="32"/>
-      <c r="S64" s="32"/>
-      <c r="T64" s="32"/>
-      <c r="U64" s="32"/>
-      <c r="V64" s="32"/>
-      <c r="W64" s="32"/>
-      <c r="X64" s="31" t="s">
+      <c r="R64" s="35"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="35"/>
+      <c r="V64" s="35"/>
+      <c r="W64" s="35"/>
+      <c r="X64" s="34" t="s">
         <v>53</v>
       </c>
-      <c r="Y64" s="32"/>
-      <c r="Z64" s="32"/>
-      <c r="AA64" s="32"/>
-      <c r="AB64" s="32"/>
-      <c r="AC64" s="32"/>
-      <c r="AD64" s="32"/>
+      <c r="Y64" s="35"/>
+      <c r="Z64" s="35"/>
+      <c r="AA64" s="35"/>
+      <c r="AB64" s="35"/>
+      <c r="AC64" s="35"/>
+      <c r="AD64" s="35"/>
     </row>
     <row r="65" spans="2:30">
       <c r="B65" s="2"/>
@@ -5754,78 +6569,78 @@
       </c>
     </row>
     <row r="71" spans="2:30">
-      <c r="B71" s="33" t="s">
+      <c r="B71" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="34"/>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="34"/>
-      <c r="J71" s="34"/>
-      <c r="K71" s="34"/>
-      <c r="L71" s="34"/>
-      <c r="M71" s="34"/>
-      <c r="N71" s="34"/>
-      <c r="O71" s="34"/>
-      <c r="P71" s="34"/>
-      <c r="Q71" s="34"/>
-      <c r="R71" s="34"/>
-      <c r="S71" s="34"/>
-      <c r="T71" s="34"/>
-      <c r="U71" s="34"/>
-      <c r="V71" s="34"/>
-      <c r="W71" s="34"/>
-      <c r="X71" s="34"/>
-      <c r="Y71" s="34"/>
-      <c r="Z71" s="34"/>
-      <c r="AA71" s="34"/>
-      <c r="AB71" s="34"/>
-      <c r="AC71" s="34"/>
-      <c r="AD71" s="34"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
+      <c r="M71" s="33"/>
+      <c r="N71" s="33"/>
+      <c r="O71" s="33"/>
+      <c r="P71" s="33"/>
+      <c r="Q71" s="33"/>
+      <c r="R71" s="33"/>
+      <c r="S71" s="33"/>
+      <c r="T71" s="33"/>
+      <c r="U71" s="33"/>
+      <c r="V71" s="33"/>
+      <c r="W71" s="33"/>
+      <c r="X71" s="33"/>
+      <c r="Y71" s="33"/>
+      <c r="Z71" s="33"/>
+      <c r="AA71" s="33"/>
+      <c r="AB71" s="33"/>
+      <c r="AC71" s="33"/>
+      <c r="AD71" s="33"/>
     </row>
     <row r="72" spans="2:30">
       <c r="B72" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="31" t="s">
+      <c r="C72" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="D72" s="32"/>
-      <c r="E72" s="32"/>
-      <c r="F72" s="32"/>
-      <c r="G72" s="32"/>
-      <c r="H72" s="32"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="31" t="s">
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="K72" s="32"/>
-      <c r="L72" s="32"/>
-      <c r="M72" s="32"/>
-      <c r="N72" s="32"/>
-      <c r="O72" s="32"/>
-      <c r="P72" s="32"/>
-      <c r="Q72" s="31" t="s">
+      <c r="K72" s="35"/>
+      <c r="L72" s="35"/>
+      <c r="M72" s="35"/>
+      <c r="N72" s="35"/>
+      <c r="O72" s="35"/>
+      <c r="P72" s="35"/>
+      <c r="Q72" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="R72" s="32"/>
-      <c r="S72" s="32"/>
-      <c r="T72" s="32"/>
-      <c r="U72" s="32"/>
-      <c r="V72" s="32"/>
-      <c r="W72" s="32"/>
-      <c r="X72" s="31" t="s">
+      <c r="R72" s="35"/>
+      <c r="S72" s="35"/>
+      <c r="T72" s="35"/>
+      <c r="U72" s="35"/>
+      <c r="V72" s="35"/>
+      <c r="W72" s="35"/>
+      <c r="X72" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="Y72" s="32"/>
-      <c r="Z72" s="32"/>
-      <c r="AA72" s="32"/>
-      <c r="AB72" s="32"/>
-      <c r="AC72" s="32"/>
-      <c r="AD72" s="32"/>
+      <c r="Y72" s="35"/>
+      <c r="Z72" s="35"/>
+      <c r="AA72" s="35"/>
+      <c r="AB72" s="35"/>
+      <c r="AC72" s="35"/>
+      <c r="AD72" s="35"/>
     </row>
     <row r="73" spans="2:30">
       <c r="B73" s="2"/>
@@ -6274,42 +7089,42 @@
       <c r="B79" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="31" t="s">
+      <c r="C79" s="34" t="s">
         <v>59</v>
       </c>
-      <c r="D79" s="32"/>
-      <c r="E79" s="32"/>
-      <c r="F79" s="32"/>
-      <c r="G79" s="32"/>
-      <c r="H79" s="32"/>
-      <c r="I79" s="32"/>
-      <c r="J79" s="31" t="s">
+      <c r="D79" s="35"/>
+      <c r="E79" s="35"/>
+      <c r="F79" s="35"/>
+      <c r="G79" s="35"/>
+      <c r="H79" s="35"/>
+      <c r="I79" s="35"/>
+      <c r="J79" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="K79" s="32"/>
-      <c r="L79" s="32"/>
-      <c r="M79" s="32"/>
-      <c r="N79" s="32"/>
-      <c r="O79" s="32"/>
-      <c r="P79" s="32"/>
-      <c r="Q79" s="31" t="s">
+      <c r="K79" s="35"/>
+      <c r="L79" s="35"/>
+      <c r="M79" s="35"/>
+      <c r="N79" s="35"/>
+      <c r="O79" s="35"/>
+      <c r="P79" s="35"/>
+      <c r="Q79" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="R79" s="32"/>
-      <c r="S79" s="32"/>
-      <c r="T79" s="32"/>
-      <c r="U79" s="32"/>
-      <c r="V79" s="32"/>
-      <c r="W79" s="32"/>
-      <c r="X79" s="31" t="s">
+      <c r="R79" s="35"/>
+      <c r="S79" s="35"/>
+      <c r="T79" s="35"/>
+      <c r="U79" s="35"/>
+      <c r="V79" s="35"/>
+      <c r="W79" s="35"/>
+      <c r="X79" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="Y79" s="32"/>
-      <c r="Z79" s="32"/>
-      <c r="AA79" s="32"/>
-      <c r="AB79" s="32"/>
-      <c r="AC79" s="32"/>
-      <c r="AD79" s="32"/>
+      <c r="Y79" s="35"/>
+      <c r="Z79" s="35"/>
+      <c r="AA79" s="35"/>
+      <c r="AB79" s="35"/>
+      <c r="AC79" s="35"/>
+      <c r="AD79" s="35"/>
     </row>
     <row r="80" spans="2:30">
       <c r="B80" s="2"/>
@@ -6758,42 +7573,42 @@
       <c r="B86" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="31" t="s">
+      <c r="C86" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="D86" s="32"/>
-      <c r="E86" s="32"/>
-      <c r="F86" s="32"/>
-      <c r="G86" s="32"/>
-      <c r="H86" s="32"/>
-      <c r="I86" s="32"/>
-      <c r="J86" s="31" t="s">
+      <c r="D86" s="35"/>
+      <c r="E86" s="35"/>
+      <c r="F86" s="35"/>
+      <c r="G86" s="35"/>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
+      <c r="J86" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="K86" s="32"/>
-      <c r="L86" s="32"/>
-      <c r="M86" s="32"/>
-      <c r="N86" s="32"/>
-      <c r="O86" s="32"/>
-      <c r="P86" s="32"/>
-      <c r="Q86" s="31" t="s">
+      <c r="K86" s="35"/>
+      <c r="L86" s="35"/>
+      <c r="M86" s="35"/>
+      <c r="N86" s="35"/>
+      <c r="O86" s="35"/>
+      <c r="P86" s="35"/>
+      <c r="Q86" s="34" t="s">
         <v>65</v>
       </c>
-      <c r="R86" s="32"/>
-      <c r="S86" s="32"/>
-      <c r="T86" s="32"/>
-      <c r="U86" s="32"/>
-      <c r="V86" s="32"/>
-      <c r="W86" s="32"/>
-      <c r="X86" s="31" t="s">
+      <c r="R86" s="35"/>
+      <c r="S86" s="35"/>
+      <c r="T86" s="35"/>
+      <c r="U86" s="35"/>
+      <c r="V86" s="35"/>
+      <c r="W86" s="35"/>
+      <c r="X86" s="34" t="s">
         <v>66</v>
       </c>
-      <c r="Y86" s="32"/>
-      <c r="Z86" s="32"/>
-      <c r="AA86" s="32"/>
-      <c r="AB86" s="32"/>
-      <c r="AC86" s="32"/>
-      <c r="AD86" s="32"/>
+      <c r="Y86" s="35"/>
+      <c r="Z86" s="35"/>
+      <c r="AA86" s="35"/>
+      <c r="AB86" s="35"/>
+      <c r="AC86" s="35"/>
+      <c r="AD86" s="35"/>
     </row>
     <row r="87" spans="2:30">
       <c r="B87" s="2"/>
@@ -7239,7 +8054,47 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="52">
+  <mergeCells count="56">
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF35:AL35"/>
+    <mergeCell ref="AF20:AL20"/>
+    <mergeCell ref="AF13:AL13"/>
+    <mergeCell ref="X13:AD13"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="X42:AD42"/>
+    <mergeCell ref="J50:P50"/>
+    <mergeCell ref="X6:AD6"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="B49:AD49"/>
+    <mergeCell ref="Q6:W6"/>
+    <mergeCell ref="X28:AD28"/>
+    <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="Q20:W20"/>
+    <mergeCell ref="B27:AD27"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="J79:P79"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="J86:P86"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="J35:P35"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B71:AD71"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="Q42:W42"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="X79:AD79"/>
+    <mergeCell ref="Q79:W79"/>
+    <mergeCell ref="Q72:W72"/>
     <mergeCell ref="B5:AD5"/>
     <mergeCell ref="J64:P64"/>
     <mergeCell ref="Q86:W86"/>
@@ -7256,42 +8111,6 @@
     <mergeCell ref="Q13:W13"/>
     <mergeCell ref="X35:AD35"/>
     <mergeCell ref="Q57:W57"/>
-    <mergeCell ref="J86:P86"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="B71:AD71"/>
-    <mergeCell ref="C42:I42"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="X86:AD86"/>
-    <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="X79:AD79"/>
-    <mergeCell ref="Q79:W79"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J79:P79"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="Q72:W72"/>
-    <mergeCell ref="X13:AD13"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="X42:AD42"/>
-    <mergeCell ref="J50:P50"/>
-    <mergeCell ref="X6:AD6"/>
-    <mergeCell ref="X20:AD20"/>
-    <mergeCell ref="B49:AD49"/>
-    <mergeCell ref="Q6:W6"/>
-    <mergeCell ref="X28:AD28"/>
-    <mergeCell ref="Q28:W28"/>
-    <mergeCell ref="Q20:W20"/>
-    <mergeCell ref="B27:AD27"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="804" yWindow="864" windowWidth="33120" windowHeight="12048"/>
+    <workbookView xWindow="810" yWindow="870" windowWidth="33120" windowHeight="12045"/>
   </bookViews>
   <sheets>
     <sheet name="48주 공정 로테이션 근무표" sheetId="1" r:id="rId1"/>
@@ -342,8 +342,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -456,7 +456,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -511,6 +511,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -539,7 +557,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -598,12 +616,26 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -891,27 +923,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AT91"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="9" customWidth="1"/>
     <col min="3" max="30" width="7" style="9" customWidth="1"/>
-    <col min="31" max="16384" width="8.796875" style="9"/>
+    <col min="31" max="16384" width="8.75" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46">
+    <row r="2" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:46">
+    <row r="3" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:46">
+    <row r="5" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B5" s="24" t="s">
         <v>1</v>
       </c>
@@ -944,7 +976,7 @@
       <c r="AC5" s="25"/>
       <c r="AD5" s="25"/>
     </row>
-    <row r="6" spans="2:46">
+    <row r="6" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
@@ -985,7 +1017,7 @@
       <c r="AC6" s="23"/>
       <c r="AD6" s="23"/>
     </row>
-    <row r="7" spans="2:46">
+    <row r="7" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
@@ -1072,7 +1104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:46">
+    <row r="8" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
@@ -1161,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:46">
+    <row r="9" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1250,7 +1282,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:46">
+    <row r="10" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>69</v>
       </c>
@@ -1339,7 +1371,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:46">
+    <row r="11" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
@@ -1428,7 +1460,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:46">
+    <row r="12" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AN12" s="20" t="s">
         <v>96</v>
       </c>
@@ -1436,7 +1468,7 @@
       <c r="AP12" s="20"/>
       <c r="AQ12" s="20"/>
     </row>
-    <row r="13" spans="2:46">
+    <row r="13" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
@@ -1496,7 +1528,7 @@
       <c r="AS13" s="18"/>
       <c r="AT13" s="18"/>
     </row>
-    <row r="14" spans="2:46">
+    <row r="14" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
         <v>78</v>
@@ -1626,7 +1658,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:46">
+    <row r="15" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
@@ -1761,7 +1793,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:46">
+    <row r="16" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
@@ -1896,7 +1928,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:46">
+    <row r="17" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -2031,7 +2063,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:46">
+    <row r="18" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
@@ -2166,7 +2198,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:46">
+    <row r="19" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AF19" s="18"/>
       <c r="AG19" s="18"/>
       <c r="AH19" s="18"/>
@@ -2183,7 +2215,7 @@
       <c r="AS19" s="18"/>
       <c r="AT19" s="18"/>
     </row>
-    <row r="20" spans="2:46">
+    <row r="20" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
@@ -2243,7 +2275,7 @@
       <c r="AS20" s="18"/>
       <c r="AT20" s="18"/>
     </row>
-    <row r="21" spans="2:46">
+    <row r="21" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
         <v>79</v>
@@ -2373,7 +2405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:46">
+    <row r="22" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
@@ -2508,7 +2540,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:46">
+    <row r="23" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>68</v>
       </c>
@@ -2643,7 +2675,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:46">
+    <row r="24" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
@@ -2778,7 +2810,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:46">
+    <row r="25" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
@@ -2913,7 +2945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:46">
+    <row r="27" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B27" s="24" t="s">
         <v>26</v>
       </c>
@@ -2952,7 +2984,7 @@
       <c r="AP27" s="20"/>
       <c r="AQ27" s="20"/>
     </row>
-    <row r="28" spans="2:46">
+    <row r="28" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
@@ -3012,7 +3044,7 @@
       <c r="AS28" s="18"/>
       <c r="AT28" s="18"/>
     </row>
-    <row r="29" spans="2:46">
+    <row r="29" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="14" t="s">
         <v>80</v>
@@ -3142,12 +3174,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:46">
+    <row r="30" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>17</v>
+      <c r="C30" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>15</v>
@@ -3276,12 +3308,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:46">
+    <row r="31" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>15</v>
+      <c r="C31" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>17</v>
@@ -3410,7 +3442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:46">
+    <row r="32" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
@@ -3544,12 +3576,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="2:46">
+    <row r="33" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>16</v>
+      <c r="C33" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>16</v>
@@ -3678,7 +3710,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:46">
+    <row r="34" spans="2:46" x14ac:dyDescent="0.25">
       <c r="AF34" s="18"/>
       <c r="AG34" s="18"/>
       <c r="AH34" s="18"/>
@@ -3695,7 +3727,7 @@
       <c r="AS34" s="18"/>
       <c r="AT34" s="18"/>
     </row>
-    <row r="35" spans="2:46">
+    <row r="35" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
@@ -3755,7 +3787,7 @@
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
     </row>
-    <row r="36" spans="2:46" s="17" customFormat="1">
+    <row r="36" spans="2:46" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -3885,7 +3917,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:46">
+    <row r="37" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>67</v>
       </c>
@@ -4019,7 +4051,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:46">
+    <row r="38" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
@@ -4153,7 +4185,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="2:46">
+    <row r="39" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
@@ -4287,7 +4319,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="2:46">
+    <row r="40" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
@@ -4421,7 +4453,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:46">
+    <row r="42" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
@@ -4462,7 +4494,7 @@
       <c r="AC42" s="23"/>
       <c r="AD42" s="23"/>
     </row>
-    <row r="43" spans="2:46">
+    <row r="43" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
         <v>82</v>
@@ -4549,7 +4581,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:46">
+    <row r="44" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
@@ -4638,7 +4670,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:46">
+    <row r="45" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>68</v>
       </c>
@@ -4727,7 +4759,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:46">
+    <row r="46" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>69</v>
       </c>
@@ -4816,7 +4848,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:46">
+    <row r="47" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
@@ -4905,7 +4937,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:30">
+    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B49" s="24" t="s">
         <v>39</v>
       </c>
@@ -4938,7 +4970,7 @@
       <c r="AC49" s="25"/>
       <c r="AD49" s="25"/>
     </row>
-    <row r="50" spans="2:30">
+    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>2</v>
       </c>
@@ -4979,7 +5011,7 @@
       <c r="AC50" s="23"/>
       <c r="AD50" s="23"/>
     </row>
-    <row r="51" spans="2:30">
+    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
         <v>83</v>
@@ -5066,12 +5098,12 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="2:30">
+    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>16</v>
+      <c r="C52" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>16</v>
@@ -5155,12 +5187,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:30">
+    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="7" t="s">
-        <v>17</v>
+      <c r="C53" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>15</v>
@@ -5244,12 +5276,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="2:30">
+    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="2" t="s">
-        <v>15</v>
+      <c r="C54" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="D54" s="7" t="s">
         <v>17</v>
@@ -5333,7 +5365,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="2:30">
+    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
@@ -5422,7 +5454,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="2:30">
+    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>2</v>
       </c>
@@ -5463,7 +5495,7 @@
       <c r="AC57" s="23"/>
       <c r="AD57" s="23"/>
     </row>
-    <row r="58" spans="2:30">
+    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -5550,7 +5582,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:30">
+    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>67</v>
       </c>
@@ -5639,7 +5671,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="2:30">
+    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>68</v>
       </c>
@@ -5728,7 +5760,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:30">
+    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>69</v>
       </c>
@@ -5817,7 +5849,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="2:30">
+    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
@@ -5906,7 +5938,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="2:30">
+    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
@@ -5947,7 +5979,7 @@
       <c r="AC64" s="23"/>
       <c r="AD64" s="23"/>
     </row>
-    <row r="65" spans="2:30">
+    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
         <v>86</v>
@@ -6034,7 +6066,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="2:30">
+    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
@@ -6123,7 +6155,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="2:30">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
@@ -6212,7 +6244,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:30">
+    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
@@ -6301,7 +6333,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="2:30">
+    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
@@ -6390,7 +6422,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="2:30">
+    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B71" s="24" t="s">
         <v>52</v>
       </c>
@@ -6423,7 +6455,7 @@
       <c r="AC71" s="25"/>
       <c r="AD71" s="25"/>
     </row>
-    <row r="72" spans="2:30">
+    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
@@ -6464,7 +6496,7 @@
       <c r="AC72" s="23"/>
       <c r="AD72" s="23"/>
     </row>
-    <row r="73" spans="2:30">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>87</v>
@@ -6551,7 +6583,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:30">
+    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>67</v>
       </c>
@@ -6640,12 +6672,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30">
+    <row r="75" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>16</v>
+      <c r="C75" s="28" t="s">
+        <v>15</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>16</v>
@@ -6729,12 +6761,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:30">
+    <row r="76" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="7" t="s">
-        <v>17</v>
+      <c r="C76" s="26" t="s">
+        <v>16</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>15</v>
@@ -6818,12 +6850,12 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="2:30">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>15</v>
+      <c r="C77" s="27" t="s">
+        <v>17</v>
       </c>
       <c r="D77" s="7" t="s">
         <v>17</v>
@@ -6907,7 +6939,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30">
+    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
@@ -6948,7 +6980,7 @@
       <c r="AC79" s="23"/>
       <c r="AD79" s="23"/>
     </row>
-    <row r="80" spans="2:30">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
       <c r="C80" s="2" t="s">
         <v>88</v>
@@ -7035,7 +7067,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="2:30">
+    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>67</v>
       </c>
@@ -7124,7 +7156,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30">
+    <row r="82" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
         <v>68</v>
       </c>
@@ -7213,7 +7245,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="2:30">
+    <row r="83" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
@@ -7302,7 +7334,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="2:30">
+    <row r="84" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
@@ -7391,7 +7423,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30">
+    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
@@ -7432,7 +7464,7 @@
       <c r="AC86" s="23"/>
       <c r="AD86" s="23"/>
     </row>
-    <row r="87" spans="2:30">
+    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
       <c r="C87" s="2" t="s">
         <v>89</v>
@@ -7519,7 +7551,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="2:30">
+    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>67</v>
       </c>
@@ -7608,7 +7640,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:30">
+    <row r="89" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>68</v>
       </c>
@@ -7697,7 +7729,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="2:30">
+    <row r="90" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>69</v>
       </c>
@@ -7786,7 +7818,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:30">
+    <row r="91" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>70</v>
       </c>
@@ -7877,15 +7909,30 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="Q86:W86"/>
-    <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="C50:I50"/>
-    <mergeCell ref="J72:P72"/>
-    <mergeCell ref="C79:I79"/>
-    <mergeCell ref="J42:P42"/>
-    <mergeCell ref="C64:I64"/>
-    <mergeCell ref="Q64:W64"/>
-    <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF35:AL35"/>
+    <mergeCell ref="AF20:AL20"/>
+    <mergeCell ref="AF13:AL13"/>
+    <mergeCell ref="X13:AD13"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="X42:AD42"/>
+    <mergeCell ref="J50:P50"/>
+    <mergeCell ref="X6:AD6"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="B49:AD49"/>
+    <mergeCell ref="Q6:W6"/>
+    <mergeCell ref="X28:AD28"/>
+    <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="Q20:W20"/>
+    <mergeCell ref="B27:AD27"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="X79:AD79"/>
     <mergeCell ref="Q79:W79"/>
     <mergeCell ref="Q72:W72"/>
@@ -7900,39 +7947,24 @@
     <mergeCell ref="J13:P13"/>
     <mergeCell ref="J79:P79"/>
     <mergeCell ref="C35:I35"/>
-    <mergeCell ref="J86:P86"/>
     <mergeCell ref="C72:I72"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="Q86:W86"/>
+    <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="J72:P72"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="J42:P42"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="Q64:W64"/>
+    <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="J86:P86"/>
     <mergeCell ref="C57:I57"/>
     <mergeCell ref="B71:AD71"/>
     <mergeCell ref="C42:I42"/>
     <mergeCell ref="Q42:W42"/>
     <mergeCell ref="X86:AD86"/>
     <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="X42:AD42"/>
-    <mergeCell ref="J50:P50"/>
-    <mergeCell ref="X6:AD6"/>
-    <mergeCell ref="X20:AD20"/>
-    <mergeCell ref="B49:AD49"/>
-    <mergeCell ref="Q6:W6"/>
-    <mergeCell ref="X28:AD28"/>
-    <mergeCell ref="Q28:W28"/>
-    <mergeCell ref="Q20:W20"/>
-    <mergeCell ref="B27:AD27"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF35:AL35"/>
-    <mergeCell ref="AF20:AL20"/>
-    <mergeCell ref="AF13:AL13"/>
-    <mergeCell ref="X13:AD13"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="870" windowWidth="33120" windowHeight="12045"/>
+    <workbookView xWindow="816" yWindow="876" windowWidth="33120" windowHeight="12048"/>
   </bookViews>
   <sheets>
-    <sheet name="48주 공정 로테이션 근무표" sheetId="1" r:id="rId1"/>
+    <sheet name="근무표 인쇄용" sheetId="2" r:id="rId1"/>
+    <sheet name="48주 로테이션 근무표" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'근무표 인쇄용'!$A$1:$AE$88</definedName>
+  </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2100" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4198" uniqueCount="98">
   <si>
     <t>※ 주간 전담 순서: 1. 차현철 → 2. 진영만 → 3. 박원호 → 4. 한원석 (12주 단위 / 한 줄에 4주씩 배치)</t>
   </si>
@@ -342,8 +346,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="15" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -530,7 +534,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -553,11 +557,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -608,6 +649,16 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -616,13 +667,13 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -923,101 +974,7100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B2:AT88"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <cols>
+    <col min="1" max="1" width="1.3984375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="22" customWidth="1"/>
+    <col min="3" max="30" width="7" style="22" customWidth="1"/>
+    <col min="31" max="31" width="1.09765625" style="22" customWidth="1"/>
+    <col min="32" max="16384" width="8.69921875" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:46">
+      <c r="B2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+    </row>
+    <row r="3" spans="2:46">
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="27"/>
+      <c r="E3" s="27"/>
+      <c r="F3" s="27"/>
+      <c r="G3" s="27"/>
+      <c r="H3" s="27"/>
+      <c r="I3" s="27"/>
+      <c r="J3" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="27"/>
+      <c r="L3" s="27"/>
+      <c r="M3" s="27"/>
+      <c r="N3" s="27"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="R3" s="27"/>
+      <c r="S3" s="27"/>
+      <c r="T3" s="27"/>
+      <c r="U3" s="27"/>
+      <c r="V3" s="27"/>
+      <c r="W3" s="27"/>
+      <c r="X3" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y3" s="27"/>
+      <c r="Z3" s="27"/>
+      <c r="AA3" s="27"/>
+      <c r="AB3" s="27"/>
+      <c r="AC3" s="27"/>
+      <c r="AD3" s="27"/>
+    </row>
+    <row r="4" spans="2:46">
+      <c r="B4" s="1"/>
+      <c r="C4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="2:46">
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:46">
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB6" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:46">
+      <c r="B7" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P7" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W7" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD7" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="2:46">
+      <c r="B8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W8" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD8" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="2:46" hidden="1">
+      <c r="AN9" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO9" s="20"/>
+      <c r="AP9" s="20"/>
+      <c r="AQ9" s="20"/>
+    </row>
+    <row r="10" spans="2:46" hidden="1">
+      <c r="B10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="31"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="31"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="R10" s="31"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="32"/>
+      <c r="X10" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="Y10" s="31"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="32"/>
+      <c r="AF10" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="31"/>
+      <c r="AL10" s="32"/>
+      <c r="AN10" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO10" s="21"/>
+      <c r="AP10" s="21"/>
+      <c r="AQ10" s="21"/>
+    </row>
+    <row r="11" spans="2:46" hidden="1">
+      <c r="B11" s="1"/>
+      <c r="C11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL11" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN11" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT11" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:46">
+      <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19"/>
+      <c r="AF12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT12" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="2:46">
+      <c r="B13" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE13" s="19"/>
+      <c r="AF13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ13" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM13" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="2:46">
+      <c r="B14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE14" s="19"/>
+      <c r="AF14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM14" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR14" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT14" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="2:46">
+      <c r="B15" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD15" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE15" s="19"/>
+      <c r="AF15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL15" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM15" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS15" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT15" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="2:46" hidden="1"/>
+    <row r="17" spans="2:46" hidden="1">
+      <c r="B17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C17" s="30" t="s">
+        <v>22</v>
+      </c>
+      <c r="D17" s="31"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="31"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="31"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="31"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="32"/>
+      <c r="Q17" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="R17" s="31"/>
+      <c r="S17" s="31"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y17" s="31"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="32"/>
+      <c r="AF17" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="31"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="31"/>
+      <c r="AK17" s="31"/>
+      <c r="AL17" s="32"/>
+      <c r="AN17" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO17" s="21"/>
+      <c r="AP17" s="21"/>
+      <c r="AQ17" s="21"/>
+    </row>
+    <row r="18" spans="2:46" hidden="1">
+      <c r="B18" s="1"/>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN18" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ18" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR18" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS18" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT18" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="2:46">
+      <c r="B19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE19" s="19"/>
+      <c r="AF19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM19" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:46">
+      <c r="B20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE20" s="19"/>
+      <c r="AF20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM20" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS20" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT20" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="21" spans="2:46">
+      <c r="B21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W21" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AE21" s="19"/>
+      <c r="AF21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL21" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM21" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT21" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="2:46">
+      <c r="B22" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W22" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE22" s="19"/>
+      <c r="AF22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL22" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM22" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:46" hidden="1"/>
+    <row r="24" spans="2:46">
+      <c r="B24" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="29"/>
+      <c r="AC24" s="29"/>
+      <c r="AD24" s="29"/>
+      <c r="AN24" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="20"/>
+      <c r="AQ24" s="20"/>
+    </row>
+    <row r="25" spans="2:46">
+      <c r="B25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="27"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="27"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="27"/>
+      <c r="I25" s="27"/>
+      <c r="J25" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="K25" s="27"/>
+      <c r="L25" s="27"/>
+      <c r="M25" s="27"/>
+      <c r="N25" s="27"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="27"/>
+      <c r="Q25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="R25" s="27"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="27"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="27"/>
+      <c r="W25" s="27"/>
+      <c r="X25" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y25" s="27"/>
+      <c r="Z25" s="27"/>
+      <c r="AA25" s="27"/>
+      <c r="AB25" s="27"/>
+      <c r="AC25" s="27"/>
+      <c r="AD25" s="27"/>
+      <c r="AF25" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG25" s="27"/>
+      <c r="AH25" s="27"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="27"/>
+      <c r="AK25" s="27"/>
+      <c r="AL25" s="27"/>
+      <c r="AN25" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="AO25" s="21"/>
+      <c r="AP25" s="21"/>
+      <c r="AQ25" s="21"/>
+    </row>
+    <row r="26" spans="2:46">
+      <c r="B26" s="1"/>
+      <c r="C26" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF26" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL26" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN26" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="AO26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ26" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT26" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="2:46">
+      <c r="B27" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P27" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W27" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD27" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM27" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP27" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT27" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="2:46">
+      <c r="B28" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C28" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ28" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM28" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT28" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="2:46">
+      <c r="B29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL29" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM29" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS29" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT29" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="30" spans="2:46">
+      <c r="B30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I30" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P30" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W30" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD30" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL30" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM30" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS30" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT30" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="2:46" hidden="1"/>
+    <row r="32" spans="2:46" hidden="1">
+      <c r="B32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="30" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="32"/>
+      <c r="Q32" s="30" t="s">
+        <v>33</v>
+      </c>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="32"/>
+      <c r="X32" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="31"/>
+      <c r="AB32" s="31"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="32"/>
+      <c r="AF32" s="30" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG32" s="31"/>
+      <c r="AH32" s="31"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="31"/>
+      <c r="AK32" s="31"/>
+      <c r="AL32" s="32"/>
+      <c r="AN32" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="AO32" s="21"/>
+      <c r="AP32" s="21"/>
+      <c r="AQ32" s="21"/>
+    </row>
+    <row r="33" spans="2:46" s="17" customFormat="1" hidden="1">
+      <c r="B33" s="13"/>
+      <c r="C33" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="M33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="N33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="O33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="P33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q33" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="R33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="T33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="U33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="V33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="W33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="X33" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA33" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB33" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC33" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD33" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="AF33" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AG33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AK33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL33" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM33" s="22"/>
+      <c r="AN33" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AQ33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AR33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AS33" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AT33" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="2:46">
+      <c r="B34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W34" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD34" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AH34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AI34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AJ34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK34" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM34" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AO34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AP34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AQ34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AR34" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AS34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT34" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="2:46">
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V35" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AG35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AI35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AJ35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AK35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM35" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AO35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AP35" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AQ35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AS35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AT35" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="2:46">
+      <c r="B36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AG36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AH36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AI36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK36" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AL36" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM36" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN36" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AO36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AR36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AS36" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AT36" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="37" spans="2:46">
+      <c r="B37" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I37" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W37" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC37" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AG37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK37" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AL37" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="AM37" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AP37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AQ37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AR37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AS37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AT37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:46" hidden="1"/>
+    <row r="39" spans="2:46" hidden="1">
+      <c r="B39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C39" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="30" t="s">
+        <v>36</v>
+      </c>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="31"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="32"/>
+      <c r="Q39" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="R39" s="31"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="32"/>
+      <c r="X39" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y39" s="31"/>
+      <c r="Z39" s="31"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="32"/>
+    </row>
+    <row r="40" spans="2:46" hidden="1">
+      <c r="B40" s="1"/>
+      <c r="C40" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W40" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X40" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA40" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC40" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD40" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="2:46">
+      <c r="B41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P41" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W41" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X41" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z41" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC41" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD41" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="2:46">
+      <c r="B42" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V42" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X42" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC42" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD42" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="43" spans="2:46">
+      <c r="B43" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB43" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC43" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD43" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44" spans="2:46">
+      <c r="B44" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P44" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W44" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z44" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC44" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD44" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="45" spans="2:46" hidden="1"/>
+    <row r="46" spans="2:46">
+      <c r="B46" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29"/>
+      <c r="AC46" s="29"/>
+      <c r="AD46" s="29"/>
+    </row>
+    <row r="47" spans="2:46">
+      <c r="B47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C47" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="27"/>
+      <c r="G47" s="27"/>
+      <c r="H47" s="27"/>
+      <c r="I47" s="27"/>
+      <c r="J47" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K47" s="27"/>
+      <c r="L47" s="27"/>
+      <c r="M47" s="27"/>
+      <c r="N47" s="27"/>
+      <c r="O47" s="27"/>
+      <c r="P47" s="27"/>
+      <c r="Q47" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="R47" s="27"/>
+      <c r="S47" s="27"/>
+      <c r="T47" s="27"/>
+      <c r="U47" s="27"/>
+      <c r="V47" s="27"/>
+      <c r="W47" s="27"/>
+      <c r="X47" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y47" s="27"/>
+      <c r="Z47" s="27"/>
+      <c r="AA47" s="27"/>
+      <c r="AB47" s="27"/>
+      <c r="AC47" s="27"/>
+      <c r="AD47" s="27"/>
+    </row>
+    <row r="48" spans="2:46">
+      <c r="B48" s="1"/>
+      <c r="C48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W48" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA48" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB48" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC48" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD48" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="49" spans="2:30">
+      <c r="B49" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I49" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P49" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W49" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z49" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC49" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD49" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="50" spans="2:30">
+      <c r="B50" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P50" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W50" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X50" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC50" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD50" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" spans="2:30">
+      <c r="B51" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC51" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD51" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="52" spans="2:30">
+      <c r="B52" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB52" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="53" spans="2:30" hidden="1"/>
+    <row r="54" spans="2:30" hidden="1">
+      <c r="B54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="27"/>
+      <c r="H54" s="27"/>
+      <c r="I54" s="27"/>
+      <c r="J54" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="K54" s="27"/>
+      <c r="L54" s="27"/>
+      <c r="M54" s="27"/>
+      <c r="N54" s="27"/>
+      <c r="O54" s="27"/>
+      <c r="P54" s="27"/>
+      <c r="Q54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="R54" s="27"/>
+      <c r="S54" s="27"/>
+      <c r="T54" s="27"/>
+      <c r="U54" s="27"/>
+      <c r="V54" s="27"/>
+      <c r="W54" s="27"/>
+      <c r="X54" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y54" s="27"/>
+      <c r="Z54" s="27"/>
+      <c r="AA54" s="27"/>
+      <c r="AB54" s="27"/>
+      <c r="AC54" s="27"/>
+      <c r="AD54" s="27"/>
+    </row>
+    <row r="55" spans="2:30" hidden="1">
+      <c r="B55" s="1"/>
+      <c r="C55" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W55" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X55" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA55" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB55" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC55" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD55" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="2:30">
+      <c r="B56" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I56" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P56" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S56" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W56" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z56" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC56" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD56" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="57" spans="2:30">
+      <c r="B57" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P57" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W57" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z57" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC57" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD57" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="2:30">
+      <c r="B58" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V58" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD58" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="59" spans="2:30">
+      <c r="B59" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC59" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD59" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="2:30" hidden="1"/>
+    <row r="61" spans="2:30" hidden="1">
+      <c r="B61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
+      <c r="F61" s="27"/>
+      <c r="G61" s="27"/>
+      <c r="H61" s="27"/>
+      <c r="I61" s="27"/>
+      <c r="J61" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="K61" s="27"/>
+      <c r="L61" s="27"/>
+      <c r="M61" s="27"/>
+      <c r="N61" s="27"/>
+      <c r="O61" s="27"/>
+      <c r="P61" s="27"/>
+      <c r="Q61" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="R61" s="27"/>
+      <c r="S61" s="27"/>
+      <c r="T61" s="27"/>
+      <c r="U61" s="27"/>
+      <c r="V61" s="27"/>
+      <c r="W61" s="27"/>
+      <c r="X61" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y61" s="27"/>
+      <c r="Z61" s="27"/>
+      <c r="AA61" s="27"/>
+      <c r="AB61" s="27"/>
+      <c r="AC61" s="27"/>
+      <c r="AD61" s="27"/>
+    </row>
+    <row r="62" spans="2:30" hidden="1">
+      <c r="B62" s="1"/>
+      <c r="C62" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W62" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X62" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y62" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA62" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB62" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD62" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="2:30">
+      <c r="B63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P63" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S63" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W63" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z63" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB63" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC63" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD63" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="64" spans="2:30">
+      <c r="B64" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P64" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W64" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X64" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC64" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD64" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30">
+      <c r="B65" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V65" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC65" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD65" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30">
+      <c r="B66" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB66" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD66" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" hidden="1"/>
+    <row r="68" spans="2:30">
+      <c r="B68" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+      <c r="P68" s="29"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="29"/>
+      <c r="S68" s="29"/>
+      <c r="T68" s="29"/>
+      <c r="U68" s="29"/>
+      <c r="V68" s="29"/>
+      <c r="W68" s="29"/>
+      <c r="X68" s="29"/>
+      <c r="Y68" s="29"/>
+      <c r="Z68" s="29"/>
+      <c r="AA68" s="29"/>
+      <c r="AB68" s="29"/>
+      <c r="AC68" s="29"/>
+      <c r="AD68" s="29"/>
+    </row>
+    <row r="69" spans="2:30">
+      <c r="B69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C69" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="27"/>
+      <c r="J69" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="K69" s="27"/>
+      <c r="L69" s="27"/>
+      <c r="M69" s="27"/>
+      <c r="N69" s="27"/>
+      <c r="O69" s="27"/>
+      <c r="P69" s="27"/>
+      <c r="Q69" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="R69" s="27"/>
+      <c r="S69" s="27"/>
+      <c r="T69" s="27"/>
+      <c r="U69" s="27"/>
+      <c r="V69" s="27"/>
+      <c r="W69" s="27"/>
+      <c r="X69" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y69" s="27"/>
+      <c r="Z69" s="27"/>
+      <c r="AA69" s="27"/>
+      <c r="AB69" s="27"/>
+      <c r="AC69" s="27"/>
+      <c r="AD69" s="27"/>
+    </row>
+    <row r="70" spans="2:30">
+      <c r="B70" s="1"/>
+      <c r="C70" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W70" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X70" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y70" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA70" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB70" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD70" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30">
+      <c r="B71" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC71" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD71" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30">
+      <c r="B72" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P72" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S72" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W72" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z72" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD72" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30">
+      <c r="B73" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P73" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W73" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X73" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z73" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC73" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD73" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30">
+      <c r="B74" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C74" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V74" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC74" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD74" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" hidden="1"/>
+    <row r="76" spans="2:30" hidden="1">
+      <c r="B76" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
+      <c r="J76" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="K76" s="27"/>
+      <c r="L76" s="27"/>
+      <c r="M76" s="27"/>
+      <c r="N76" s="27"/>
+      <c r="O76" s="27"/>
+      <c r="P76" s="27"/>
+      <c r="Q76" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="R76" s="27"/>
+      <c r="S76" s="27"/>
+      <c r="T76" s="27"/>
+      <c r="U76" s="27"/>
+      <c r="V76" s="27"/>
+      <c r="W76" s="27"/>
+      <c r="X76" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y76" s="27"/>
+      <c r="Z76" s="27"/>
+      <c r="AA76" s="27"/>
+      <c r="AB76" s="27"/>
+      <c r="AC76" s="27"/>
+      <c r="AD76" s="27"/>
+    </row>
+    <row r="77" spans="2:30" hidden="1">
+      <c r="B77" s="1"/>
+      <c r="C77" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W77" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X77" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y77" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z77" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB77" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD77" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="2:30">
+      <c r="B78" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB78" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD78" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30">
+      <c r="B79" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I79" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P79" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S79" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W79" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z79" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB79" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD79" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="2:30">
+      <c r="B80" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P80" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W80" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X80" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC80" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD80" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="81" spans="2:30">
+      <c r="B81" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V81" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC81" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD81" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="2:30" hidden="1"/>
+    <row r="83" spans="2:30" hidden="1">
+      <c r="B83" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C83" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
+      <c r="M83" s="27"/>
+      <c r="N83" s="27"/>
+      <c r="O83" s="27"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="R83" s="27"/>
+      <c r="S83" s="27"/>
+      <c r="T83" s="27"/>
+      <c r="U83" s="27"/>
+      <c r="V83" s="27"/>
+      <c r="W83" s="27"/>
+      <c r="X83" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y83" s="27"/>
+      <c r="Z83" s="27"/>
+      <c r="AA83" s="27"/>
+      <c r="AB83" s="27"/>
+      <c r="AC83" s="27"/>
+      <c r="AD83" s="27"/>
+    </row>
+    <row r="84" spans="2:30" hidden="1">
+      <c r="B84" s="1"/>
+      <c r="C84" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P84" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W84" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X84" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y84" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA84" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB84" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD84" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="2:30">
+      <c r="B85" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB85" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD85" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="2:30">
+      <c r="B86" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H86" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I86" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O86" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P86" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S86" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V86" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W86" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z86" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC86" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD86" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="87" spans="2:30">
+      <c r="B87" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P87" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W87" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X87" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC87" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD87" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="88" spans="2:30">
+      <c r="B88" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V88" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC88" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD88" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="56">
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="J76:P76"/>
+    <mergeCell ref="Q76:W76"/>
+    <mergeCell ref="X76:AD76"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="J83:P83"/>
+    <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="X83:AD83"/>
+    <mergeCell ref="C61:I61"/>
+    <mergeCell ref="J61:P61"/>
+    <mergeCell ref="Q61:W61"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="B68:AD68"/>
+    <mergeCell ref="C69:I69"/>
+    <mergeCell ref="J69:P69"/>
+    <mergeCell ref="Q69:W69"/>
+    <mergeCell ref="X69:AD69"/>
+    <mergeCell ref="B46:AD46"/>
+    <mergeCell ref="C47:I47"/>
+    <mergeCell ref="J47:P47"/>
+    <mergeCell ref="Q47:W47"/>
+    <mergeCell ref="X47:AD47"/>
+    <mergeCell ref="C54:I54"/>
+    <mergeCell ref="J54:P54"/>
+    <mergeCell ref="Q54:W54"/>
+    <mergeCell ref="X54:AD54"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:W32"/>
+    <mergeCell ref="X32:AD32"/>
+    <mergeCell ref="AF32:AL32"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="B24:AD24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="AF25:AL25"/>
+    <mergeCell ref="AF10:AL10"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:W17"/>
+    <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="AF17:AL17"/>
+    <mergeCell ref="X10:AD10"/>
+    <mergeCell ref="Q10:W10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="Q3:W3"/>
+    <mergeCell ref="X3:AD3"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="B2:AT91"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
     <col min="1" max="1" width="3" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10.3984375" style="9" customWidth="1"/>
     <col min="3" max="30" width="7" style="9" customWidth="1"/>
-    <col min="31" max="16384" width="8.75" style="9"/>
+    <col min="31" max="16384" width="8.69921875" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:46">
       <c r="B2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:46">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B5" s="24" t="s">
+    <row r="5" spans="2:46">
+      <c r="B5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="L5" s="25"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
-      <c r="R5" s="25"/>
-      <c r="S5" s="25"/>
-      <c r="T5" s="25"/>
-      <c r="U5" s="25"/>
-      <c r="V5" s="25"/>
-      <c r="W5" s="25"/>
-      <c r="X5" s="25"/>
-      <c r="Y5" s="25"/>
-      <c r="Z5" s="25"/>
-      <c r="AA5" s="25"/>
-      <c r="AB5" s="25"/>
-      <c r="AC5" s="25"/>
-      <c r="AD5" s="25"/>
-    </row>
-    <row r="6" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+    </row>
+    <row r="6" spans="2:46">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="22" t="s">
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="22" t="s">
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23"/>
-      <c r="W6" s="23"/>
-      <c r="X6" s="22" t="s">
+      <c r="R6" s="27"/>
+      <c r="S6" s="27"/>
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="23"/>
-      <c r="Z6" s="23"/>
-      <c r="AA6" s="23"/>
-      <c r="AB6" s="23"/>
-      <c r="AC6" s="23"/>
-      <c r="AD6" s="23"/>
-    </row>
-    <row r="7" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="27"/>
+      <c r="AC6" s="27"/>
+      <c r="AD6" s="27"/>
+    </row>
+    <row r="7" spans="2:46">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
@@ -1104,7 +8154,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:46">
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
@@ -1193,7 +8243,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:46">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -1282,7 +8332,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:46">
       <c r="B10" s="1" t="s">
         <v>69</v>
       </c>
@@ -1371,7 +8421,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:46">
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
@@ -1460,7 +8510,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:46">
       <c r="AN12" s="20" t="s">
         <v>96</v>
       </c>
@@ -1468,55 +8518,55 @@
       <c r="AP12" s="20"/>
       <c r="AQ12" s="20"/>
     </row>
-    <row r="13" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:46">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="23"/>
-      <c r="J13" s="22" t="s">
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="23"/>
-      <c r="L13" s="23"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
-      <c r="O13" s="23"/>
-      <c r="P13" s="23"/>
-      <c r="Q13" s="22" t="s">
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="27"/>
+      <c r="O13" s="27"/>
+      <c r="P13" s="27"/>
+      <c r="Q13" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="23"/>
-      <c r="S13" s="23"/>
-      <c r="T13" s="23"/>
-      <c r="U13" s="23"/>
-      <c r="V13" s="23"/>
-      <c r="W13" s="23"/>
-      <c r="X13" s="22" t="s">
+      <c r="R13" s="27"/>
+      <c r="S13" s="27"/>
+      <c r="T13" s="27"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="27"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="Y13" s="23"/>
-      <c r="Z13" s="23"/>
-      <c r="AA13" s="23"/>
-      <c r="AB13" s="23"/>
-      <c r="AC13" s="23"/>
-      <c r="AD13" s="23"/>
-      <c r="AF13" s="22" t="s">
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27"/>
+      <c r="AB13" s="27"/>
+      <c r="AC13" s="27"/>
+      <c r="AD13" s="27"/>
+      <c r="AF13" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="AG13" s="23"/>
-      <c r="AH13" s="23"/>
-      <c r="AI13" s="23"/>
-      <c r="AJ13" s="23"/>
-      <c r="AK13" s="23"/>
-      <c r="AL13" s="23"/>
+      <c r="AG13" s="27"/>
+      <c r="AH13" s="27"/>
+      <c r="AI13" s="27"/>
+      <c r="AJ13" s="27"/>
+      <c r="AK13" s="27"/>
+      <c r="AL13" s="27"/>
       <c r="AM13" s="18"/>
       <c r="AN13" s="21" t="s">
         <v>90</v>
@@ -1528,7 +8578,7 @@
       <c r="AS13" s="18"/>
       <c r="AT13" s="18"/>
     </row>
-    <row r="14" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:46">
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
         <v>78</v>
@@ -1658,7 +8708,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:46">
       <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
@@ -1793,7 +8843,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:46">
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
@@ -1928,7 +8978,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:46">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -2063,7 +9113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:46">
       <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
@@ -2198,7 +9248,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:46">
       <c r="AF19" s="18"/>
       <c r="AG19" s="18"/>
       <c r="AH19" s="18"/>
@@ -2215,55 +9265,55 @@
       <c r="AS19" s="18"/>
       <c r="AT19" s="18"/>
     </row>
-    <row r="20" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:46">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="23"/>
-      <c r="I20" s="23"/>
-      <c r="J20" s="22" t="s">
+      <c r="D20" s="27"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="27"/>
+      <c r="J20" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="23"/>
-      <c r="P20" s="23"/>
-      <c r="Q20" s="22" t="s">
+      <c r="K20" s="27"/>
+      <c r="L20" s="27"/>
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="23"/>
-      <c r="S20" s="23"/>
-      <c r="T20" s="23"/>
-      <c r="U20" s="23"/>
-      <c r="V20" s="23"/>
-      <c r="W20" s="23"/>
-      <c r="X20" s="22" t="s">
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="27"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="23"/>
-      <c r="Z20" s="23"/>
-      <c r="AA20" s="23"/>
-      <c r="AB20" s="23"/>
-      <c r="AC20" s="23"/>
-      <c r="AD20" s="23"/>
-      <c r="AF20" s="22" t="s">
+      <c r="Y20" s="27"/>
+      <c r="Z20" s="27"/>
+      <c r="AA20" s="27"/>
+      <c r="AB20" s="27"/>
+      <c r="AC20" s="27"/>
+      <c r="AD20" s="27"/>
+      <c r="AF20" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="AG20" s="23"/>
-      <c r="AH20" s="23"/>
-      <c r="AI20" s="23"/>
-      <c r="AJ20" s="23"/>
-      <c r="AK20" s="23"/>
-      <c r="AL20" s="23"/>
+      <c r="AG20" s="27"/>
+      <c r="AH20" s="27"/>
+      <c r="AI20" s="27"/>
+      <c r="AJ20" s="27"/>
+      <c r="AK20" s="27"/>
+      <c r="AL20" s="27"/>
       <c r="AM20" s="18"/>
       <c r="AN20" s="21" t="s">
         <v>91</v>
@@ -2275,7 +9325,7 @@
       <c r="AS20" s="18"/>
       <c r="AT20" s="18"/>
     </row>
-    <row r="21" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:46">
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
         <v>79</v>
@@ -2405,7 +9455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:46">
       <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
@@ -2540,7 +9590,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:46">
       <c r="B23" s="1" t="s">
         <v>68</v>
       </c>
@@ -2675,7 +9725,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:46">
       <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,7 +9860,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:46">
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
@@ -2945,38 +9995,38 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:46" x14ac:dyDescent="0.25">
-      <c r="B27" s="24" t="s">
+    <row r="27" spans="2:46">
+      <c r="B27" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="25"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
-      <c r="G27" s="25"/>
-      <c r="H27" s="25"/>
-      <c r="I27" s="25"/>
-      <c r="J27" s="25"/>
-      <c r="K27" s="25"/>
-      <c r="L27" s="25"/>
-      <c r="M27" s="25"/>
-      <c r="N27" s="25"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="25"/>
-      <c r="Q27" s="25"/>
-      <c r="R27" s="25"/>
-      <c r="S27" s="25"/>
-      <c r="T27" s="25"/>
-      <c r="U27" s="25"/>
-      <c r="V27" s="25"/>
-      <c r="W27" s="25"/>
-      <c r="X27" s="25"/>
-      <c r="Y27" s="25"/>
-      <c r="Z27" s="25"/>
-      <c r="AA27" s="25"/>
-      <c r="AB27" s="25"/>
-      <c r="AC27" s="25"/>
-      <c r="AD27" s="25"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="29"/>
       <c r="AN27" s="20" t="s">
         <v>95</v>
       </c>
@@ -2984,55 +10034,55 @@
       <c r="AP27" s="20"/>
       <c r="AQ27" s="20"/>
     </row>
-    <row r="28" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:46">
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
-      <c r="F28" s="23"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="23"/>
-      <c r="I28" s="23"/>
-      <c r="J28" s="22" t="s">
+      <c r="D28" s="27"/>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="23"/>
-      <c r="L28" s="23"/>
-      <c r="M28" s="23"/>
-      <c r="N28" s="23"/>
-      <c r="O28" s="23"/>
-      <c r="P28" s="23"/>
-      <c r="Q28" s="22" t="s">
+      <c r="K28" s="27"/>
+      <c r="L28" s="27"/>
+      <c r="M28" s="27"/>
+      <c r="N28" s="27"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="27"/>
+      <c r="Q28" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="R28" s="23"/>
-      <c r="S28" s="23"/>
-      <c r="T28" s="23"/>
-      <c r="U28" s="23"/>
-      <c r="V28" s="23"/>
-      <c r="W28" s="23"/>
-      <c r="X28" s="22" t="s">
+      <c r="R28" s="27"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="27"/>
+      <c r="U28" s="27"/>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="Y28" s="23"/>
-      <c r="Z28" s="23"/>
-      <c r="AA28" s="23"/>
-      <c r="AB28" s="23"/>
-      <c r="AC28" s="23"/>
-      <c r="AD28" s="23"/>
-      <c r="AF28" s="22" t="s">
+      <c r="Y28" s="27"/>
+      <c r="Z28" s="27"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="27"/>
+      <c r="AC28" s="27"/>
+      <c r="AD28" s="27"/>
+      <c r="AF28" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="AG28" s="23"/>
-      <c r="AH28" s="23"/>
-      <c r="AI28" s="23"/>
-      <c r="AJ28" s="23"/>
-      <c r="AK28" s="23"/>
-      <c r="AL28" s="23"/>
+      <c r="AG28" s="27"/>
+      <c r="AH28" s="27"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="27"/>
+      <c r="AK28" s="27"/>
+      <c r="AL28" s="27"/>
       <c r="AM28" s="18"/>
       <c r="AN28" s="21" t="s">
         <v>90</v>
@@ -3044,7 +10094,7 @@
       <c r="AS28" s="18"/>
       <c r="AT28" s="18"/>
     </row>
-    <row r="29" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:46">
       <c r="B29" s="1"/>
       <c r="C29" s="14" t="s">
         <v>80</v>
@@ -3174,11 +10224,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:46">
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C30" s="26" t="s">
+      <c r="C30" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -3308,11 +10358,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:46">
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C31" s="27" t="s">
+      <c r="C31" s="24" t="s">
         <v>17</v>
       </c>
       <c r="D31" s="7" t="s">
@@ -3442,7 +10492,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:46">
       <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
@@ -3576,11 +10626,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:46">
       <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C33" s="28" t="s">
+      <c r="C33" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D33" s="6" t="s">
@@ -3710,7 +10760,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:46">
       <c r="AF34" s="18"/>
       <c r="AG34" s="18"/>
       <c r="AH34" s="18"/>
@@ -3727,55 +10777,55 @@
       <c r="AS34" s="18"/>
       <c r="AT34" s="18"/>
     </row>
-    <row r="35" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:46">
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-      <c r="H35" s="23"/>
-      <c r="I35" s="23"/>
-      <c r="J35" s="22" t="s">
+      <c r="D35" s="27"/>
+      <c r="E35" s="27"/>
+      <c r="F35" s="27"/>
+      <c r="G35" s="27"/>
+      <c r="H35" s="27"/>
+      <c r="I35" s="27"/>
+      <c r="J35" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="23"/>
-      <c r="L35" s="23"/>
-      <c r="M35" s="23"/>
-      <c r="N35" s="23"/>
-      <c r="O35" s="23"/>
-      <c r="P35" s="23"/>
-      <c r="Q35" s="22" t="s">
+      <c r="K35" s="27"/>
+      <c r="L35" s="27"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+      <c r="O35" s="27"/>
+      <c r="P35" s="27"/>
+      <c r="Q35" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="23"/>
-      <c r="S35" s="23"/>
-      <c r="T35" s="23"/>
-      <c r="U35" s="23"/>
-      <c r="V35" s="23"/>
-      <c r="W35" s="23"/>
-      <c r="X35" s="22" t="s">
+      <c r="R35" s="27"/>
+      <c r="S35" s="27"/>
+      <c r="T35" s="27"/>
+      <c r="U35" s="27"/>
+      <c r="V35" s="27"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="Y35" s="23"/>
-      <c r="Z35" s="23"/>
-      <c r="AA35" s="23"/>
-      <c r="AB35" s="23"/>
-      <c r="AC35" s="23"/>
-      <c r="AD35" s="23"/>
-      <c r="AF35" s="22" t="s">
+      <c r="Y35" s="27"/>
+      <c r="Z35" s="27"/>
+      <c r="AA35" s="27"/>
+      <c r="AB35" s="27"/>
+      <c r="AC35" s="27"/>
+      <c r="AD35" s="27"/>
+      <c r="AF35" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="AG35" s="23"/>
-      <c r="AH35" s="23"/>
-      <c r="AI35" s="23"/>
-      <c r="AJ35" s="23"/>
-      <c r="AK35" s="23"/>
-      <c r="AL35" s="23"/>
+      <c r="AG35" s="27"/>
+      <c r="AH35" s="27"/>
+      <c r="AI35" s="27"/>
+      <c r="AJ35" s="27"/>
+      <c r="AK35" s="27"/>
+      <c r="AL35" s="27"/>
       <c r="AM35" s="18"/>
       <c r="AN35" s="21" t="s">
         <v>91</v>
@@ -3787,7 +10837,7 @@
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
     </row>
-    <row r="36" spans="2:46" s="17" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:46" s="17" customFormat="1">
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -3917,7 +10967,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:46">
       <c r="B37" s="1" t="s">
         <v>67</v>
       </c>
@@ -4051,7 +11101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:46">
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
@@ -4185,7 +11235,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:46">
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
@@ -4319,7 +11369,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:46">
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
@@ -4453,48 +11503,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:46">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="26" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="23"/>
-      <c r="E42" s="23"/>
-      <c r="F42" s="23"/>
-      <c r="G42" s="23"/>
-      <c r="H42" s="23"/>
-      <c r="I42" s="23"/>
-      <c r="J42" s="22" t="s">
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="27"/>
+      <c r="J42" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="K42" s="23"/>
-      <c r="L42" s="23"/>
-      <c r="M42" s="23"/>
-      <c r="N42" s="23"/>
-      <c r="O42" s="23"/>
-      <c r="P42" s="23"/>
-      <c r="Q42" s="22" t="s">
+      <c r="K42" s="27"/>
+      <c r="L42" s="27"/>
+      <c r="M42" s="27"/>
+      <c r="N42" s="27"/>
+      <c r="O42" s="27"/>
+      <c r="P42" s="27"/>
+      <c r="Q42" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="R42" s="23"/>
-      <c r="S42" s="23"/>
-      <c r="T42" s="23"/>
-      <c r="U42" s="23"/>
-      <c r="V42" s="23"/>
-      <c r="W42" s="23"/>
-      <c r="X42" s="22" t="s">
+      <c r="R42" s="27"/>
+      <c r="S42" s="27"/>
+      <c r="T42" s="27"/>
+      <c r="U42" s="27"/>
+      <c r="V42" s="27"/>
+      <c r="W42" s="27"/>
+      <c r="X42" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="Y42" s="23"/>
-      <c r="Z42" s="23"/>
-      <c r="AA42" s="23"/>
-      <c r="AB42" s="23"/>
-      <c r="AC42" s="23"/>
-      <c r="AD42" s="23"/>
-    </row>
-    <row r="43" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="Y42" s="27"/>
+      <c r="Z42" s="27"/>
+      <c r="AA42" s="27"/>
+      <c r="AB42" s="27"/>
+      <c r="AC42" s="27"/>
+      <c r="AD42" s="27"/>
+    </row>
+    <row r="43" spans="2:46">
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
         <v>82</v>
@@ -4581,7 +11631,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:46">
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
@@ -4670,7 +11720,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:46">
       <c r="B45" s="1" t="s">
         <v>68</v>
       </c>
@@ -4759,7 +11809,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:46">
       <c r="B46" s="1" t="s">
         <v>69</v>
       </c>
@@ -4848,7 +11898,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:46" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:46">
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
@@ -4937,81 +11987,81 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B49" s="24" t="s">
+    <row r="49" spans="2:30">
+      <c r="B49" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
-      <c r="F49" s="25"/>
-      <c r="G49" s="25"/>
-      <c r="H49" s="25"/>
-      <c r="I49" s="25"/>
-      <c r="J49" s="25"/>
-      <c r="K49" s="25"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="25"/>
-      <c r="N49" s="25"/>
-      <c r="O49" s="25"/>
-      <c r="P49" s="25"/>
-      <c r="Q49" s="25"/>
-      <c r="R49" s="25"/>
-      <c r="S49" s="25"/>
-      <c r="T49" s="25"/>
-      <c r="U49" s="25"/>
-      <c r="V49" s="25"/>
-      <c r="W49" s="25"/>
-      <c r="X49" s="25"/>
-      <c r="Y49" s="25"/>
-      <c r="Z49" s="25"/>
-      <c r="AA49" s="25"/>
-      <c r="AB49" s="25"/>
-      <c r="AC49" s="25"/>
-      <c r="AD49" s="25"/>
-    </row>
-    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="29"/>
+      <c r="AA49" s="29"/>
+      <c r="AB49" s="29"/>
+      <c r="AC49" s="29"/>
+      <c r="AD49" s="29"/>
+    </row>
+    <row r="50" spans="2:30">
       <c r="B50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="23"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="23"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="23"/>
-      <c r="J50" s="22" t="s">
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="27"/>
+      <c r="G50" s="27"/>
+      <c r="H50" s="27"/>
+      <c r="I50" s="27"/>
+      <c r="J50" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="23"/>
-      <c r="L50" s="23"/>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="23"/>
-      <c r="P50" s="23"/>
-      <c r="Q50" s="22" t="s">
+      <c r="K50" s="27"/>
+      <c r="L50" s="27"/>
+      <c r="M50" s="27"/>
+      <c r="N50" s="27"/>
+      <c r="O50" s="27"/>
+      <c r="P50" s="27"/>
+      <c r="Q50" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="23"/>
-      <c r="S50" s="23"/>
-      <c r="T50" s="23"/>
-      <c r="U50" s="23"/>
-      <c r="V50" s="23"/>
-      <c r="W50" s="23"/>
-      <c r="X50" s="22" t="s">
+      <c r="R50" s="27"/>
+      <c r="S50" s="27"/>
+      <c r="T50" s="27"/>
+      <c r="U50" s="27"/>
+      <c r="V50" s="27"/>
+      <c r="W50" s="27"/>
+      <c r="X50" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="Y50" s="23"/>
-      <c r="Z50" s="23"/>
-      <c r="AA50" s="23"/>
-      <c r="AB50" s="23"/>
-      <c r="AC50" s="23"/>
-      <c r="AD50" s="23"/>
-    </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y50" s="27"/>
+      <c r="Z50" s="27"/>
+      <c r="AA50" s="27"/>
+      <c r="AB50" s="27"/>
+      <c r="AC50" s="27"/>
+      <c r="AD50" s="27"/>
+    </row>
+    <row r="51" spans="2:30">
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
         <v>83</v>
@@ -5098,11 +12148,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:30">
       <c r="B52" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="28" t="s">
+      <c r="C52" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -5187,11 +12237,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:30">
       <c r="B53" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C53" s="26" t="s">
+      <c r="C53" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D53" s="2" t="s">
@@ -5276,11 +12326,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:30">
       <c r="B54" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="24" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="7" t="s">
@@ -5365,7 +12415,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:30">
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
@@ -5454,48 +12504,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:30">
       <c r="B57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="22" t="s">
+      <c r="C57" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="23"/>
-      <c r="E57" s="23"/>
-      <c r="F57" s="23"/>
-      <c r="G57" s="23"/>
-      <c r="H57" s="23"/>
-      <c r="I57" s="23"/>
-      <c r="J57" s="22" t="s">
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="27"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="27"/>
+      <c r="J57" s="26" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
-      <c r="N57" s="23"/>
-      <c r="O57" s="23"/>
-      <c r="P57" s="23"/>
-      <c r="Q57" s="22" t="s">
+      <c r="K57" s="27"/>
+      <c r="L57" s="27"/>
+      <c r="M57" s="27"/>
+      <c r="N57" s="27"/>
+      <c r="O57" s="27"/>
+      <c r="P57" s="27"/>
+      <c r="Q57" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="R57" s="23"/>
-      <c r="S57" s="23"/>
-      <c r="T57" s="23"/>
-      <c r="U57" s="23"/>
-      <c r="V57" s="23"/>
-      <c r="W57" s="23"/>
-      <c r="X57" s="22" t="s">
+      <c r="R57" s="27"/>
+      <c r="S57" s="27"/>
+      <c r="T57" s="27"/>
+      <c r="U57" s="27"/>
+      <c r="V57" s="27"/>
+      <c r="W57" s="27"/>
+      <c r="X57" s="26" t="s">
         <v>47</v>
       </c>
-      <c r="Y57" s="23"/>
-      <c r="Z57" s="23"/>
-      <c r="AA57" s="23"/>
-      <c r="AB57" s="23"/>
-      <c r="AC57" s="23"/>
-      <c r="AD57" s="23"/>
-    </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y57" s="27"/>
+      <c r="Z57" s="27"/>
+      <c r="AA57" s="27"/>
+      <c r="AB57" s="27"/>
+      <c r="AC57" s="27"/>
+      <c r="AD57" s="27"/>
+    </row>
+    <row r="58" spans="2:30">
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -5582,7 +12632,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:30">
       <c r="B59" s="1" t="s">
         <v>67</v>
       </c>
@@ -5671,7 +12721,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:30">
       <c r="B60" s="1" t="s">
         <v>68</v>
       </c>
@@ -5760,7 +12810,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:30">
       <c r="B61" s="1" t="s">
         <v>69</v>
       </c>
@@ -5849,7 +12899,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:30">
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
@@ -5938,48 +12988,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:30">
       <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="23"/>
-      <c r="E64" s="23"/>
-      <c r="F64" s="23"/>
-      <c r="G64" s="23"/>
-      <c r="H64" s="23"/>
-      <c r="I64" s="23"/>
-      <c r="J64" s="22" t="s">
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
+      <c r="F64" s="27"/>
+      <c r="G64" s="27"/>
+      <c r="H64" s="27"/>
+      <c r="I64" s="27"/>
+      <c r="J64" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="23"/>
-      <c r="L64" s="23"/>
-      <c r="M64" s="23"/>
-      <c r="N64" s="23"/>
-      <c r="O64" s="23"/>
-      <c r="P64" s="23"/>
-      <c r="Q64" s="22" t="s">
+      <c r="K64" s="27"/>
+      <c r="L64" s="27"/>
+      <c r="M64" s="27"/>
+      <c r="N64" s="27"/>
+      <c r="O64" s="27"/>
+      <c r="P64" s="27"/>
+      <c r="Q64" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="R64" s="23"/>
-      <c r="S64" s="23"/>
-      <c r="T64" s="23"/>
-      <c r="U64" s="23"/>
-      <c r="V64" s="23"/>
-      <c r="W64" s="23"/>
-      <c r="X64" s="22" t="s">
+      <c r="R64" s="27"/>
+      <c r="S64" s="27"/>
+      <c r="T64" s="27"/>
+      <c r="U64" s="27"/>
+      <c r="V64" s="27"/>
+      <c r="W64" s="27"/>
+      <c r="X64" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="Y64" s="23"/>
-      <c r="Z64" s="23"/>
-      <c r="AA64" s="23"/>
-      <c r="AB64" s="23"/>
-      <c r="AC64" s="23"/>
-      <c r="AD64" s="23"/>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y64" s="27"/>
+      <c r="Z64" s="27"/>
+      <c r="AA64" s="27"/>
+      <c r="AB64" s="27"/>
+      <c r="AC64" s="27"/>
+      <c r="AD64" s="27"/>
+    </row>
+    <row r="65" spans="2:30">
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
         <v>86</v>
@@ -6066,7 +13116,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:30">
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
@@ -6155,7 +13205,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:30">
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
@@ -6244,7 +13294,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:30">
       <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
@@ -6333,7 +13383,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:30">
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
@@ -6422,81 +13472,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
-      <c r="B71" s="24" t="s">
+    <row r="71" spans="2:30">
+      <c r="B71" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="25"/>
-      <c r="D71" s="25"/>
-      <c r="E71" s="25"/>
-      <c r="F71" s="25"/>
-      <c r="G71" s="25"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25"/>
-      <c r="J71" s="25"/>
-      <c r="K71" s="25"/>
-      <c r="L71" s="25"/>
-      <c r="M71" s="25"/>
-      <c r="N71" s="25"/>
-      <c r="O71" s="25"/>
-      <c r="P71" s="25"/>
-      <c r="Q71" s="25"/>
-      <c r="R71" s="25"/>
-      <c r="S71" s="25"/>
-      <c r="T71" s="25"/>
-      <c r="U71" s="25"/>
-      <c r="V71" s="25"/>
-      <c r="W71" s="25"/>
-      <c r="X71" s="25"/>
-      <c r="Y71" s="25"/>
-      <c r="Z71" s="25"/>
-      <c r="AA71" s="25"/>
-      <c r="AB71" s="25"/>
-      <c r="AC71" s="25"/>
-      <c r="AD71" s="25"/>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
+      <c r="L71" s="29"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="29"/>
+      <c r="P71" s="29"/>
+      <c r="Q71" s="29"/>
+      <c r="R71" s="29"/>
+      <c r="S71" s="29"/>
+      <c r="T71" s="29"/>
+      <c r="U71" s="29"/>
+      <c r="V71" s="29"/>
+      <c r="W71" s="29"/>
+      <c r="X71" s="29"/>
+      <c r="Y71" s="29"/>
+      <c r="Z71" s="29"/>
+      <c r="AA71" s="29"/>
+      <c r="AB71" s="29"/>
+      <c r="AC71" s="29"/>
+      <c r="AD71" s="29"/>
+    </row>
+    <row r="72" spans="2:30">
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="22" t="s">
+      <c r="C72" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D72" s="23"/>
-      <c r="E72" s="23"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="23"/>
-      <c r="H72" s="23"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="22" t="s">
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
+      <c r="J72" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="K72" s="23"/>
-      <c r="L72" s="23"/>
-      <c r="M72" s="23"/>
-      <c r="N72" s="23"/>
-      <c r="O72" s="23"/>
-      <c r="P72" s="23"/>
-      <c r="Q72" s="22" t="s">
+      <c r="K72" s="27"/>
+      <c r="L72" s="27"/>
+      <c r="M72" s="27"/>
+      <c r="N72" s="27"/>
+      <c r="O72" s="27"/>
+      <c r="P72" s="27"/>
+      <c r="Q72" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="R72" s="23"/>
-      <c r="S72" s="23"/>
-      <c r="T72" s="23"/>
-      <c r="U72" s="23"/>
-      <c r="V72" s="23"/>
-      <c r="W72" s="23"/>
-      <c r="X72" s="22" t="s">
+      <c r="R72" s="27"/>
+      <c r="S72" s="27"/>
+      <c r="T72" s="27"/>
+      <c r="U72" s="27"/>
+      <c r="V72" s="27"/>
+      <c r="W72" s="27"/>
+      <c r="X72" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="Y72" s="23"/>
-      <c r="Z72" s="23"/>
-      <c r="AA72" s="23"/>
-      <c r="AB72" s="23"/>
-      <c r="AC72" s="23"/>
-      <c r="AD72" s="23"/>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y72" s="27"/>
+      <c r="Z72" s="27"/>
+      <c r="AA72" s="27"/>
+      <c r="AB72" s="27"/>
+      <c r="AC72" s="27"/>
+      <c r="AD72" s="27"/>
+    </row>
+    <row r="73" spans="2:30">
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>87</v>
@@ -6583,7 +13633,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:30">
       <c r="B74" s="1" t="s">
         <v>67</v>
       </c>
@@ -6672,11 +13722,11 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:30">
       <c r="B75" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="28" t="s">
+      <c r="C75" s="25" t="s">
         <v>15</v>
       </c>
       <c r="D75" s="6" t="s">
@@ -6761,11 +13811,11 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:30">
       <c r="B76" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="23" t="s">
         <v>16</v>
       </c>
       <c r="D76" s="2" t="s">
@@ -6850,11 +13900,11 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:30">
       <c r="B77" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C77" s="27" t="s">
+      <c r="C77" s="24" t="s">
         <v>17</v>
       </c>
       <c r="D77" s="7" t="s">
@@ -6939,48 +13989,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:30">
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="D79" s="23"/>
-      <c r="E79" s="23"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="23"/>
-      <c r="H79" s="23"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="22" t="s">
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="26" t="s">
         <v>58</v>
       </c>
-      <c r="K79" s="23"/>
-      <c r="L79" s="23"/>
-      <c r="M79" s="23"/>
-      <c r="N79" s="23"/>
-      <c r="O79" s="23"/>
-      <c r="P79" s="23"/>
-      <c r="Q79" s="22" t="s">
+      <c r="K79" s="27"/>
+      <c r="L79" s="27"/>
+      <c r="M79" s="27"/>
+      <c r="N79" s="27"/>
+      <c r="O79" s="27"/>
+      <c r="P79" s="27"/>
+      <c r="Q79" s="26" t="s">
         <v>59</v>
       </c>
-      <c r="R79" s="23"/>
-      <c r="S79" s="23"/>
-      <c r="T79" s="23"/>
-      <c r="U79" s="23"/>
-      <c r="V79" s="23"/>
-      <c r="W79" s="23"/>
-      <c r="X79" s="22" t="s">
+      <c r="R79" s="27"/>
+      <c r="S79" s="27"/>
+      <c r="T79" s="27"/>
+      <c r="U79" s="27"/>
+      <c r="V79" s="27"/>
+      <c r="W79" s="27"/>
+      <c r="X79" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="Y79" s="23"/>
-      <c r="Z79" s="23"/>
-      <c r="AA79" s="23"/>
-      <c r="AB79" s="23"/>
-      <c r="AC79" s="23"/>
-      <c r="AD79" s="23"/>
-    </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y79" s="27"/>
+      <c r="Z79" s="27"/>
+      <c r="AA79" s="27"/>
+      <c r="AB79" s="27"/>
+      <c r="AC79" s="27"/>
+      <c r="AD79" s="27"/>
+    </row>
+    <row r="80" spans="2:30">
       <c r="B80" s="1"/>
       <c r="C80" s="2" t="s">
         <v>88</v>
@@ -7067,7 +14117,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:30">
       <c r="B81" s="1" t="s">
         <v>67</v>
       </c>
@@ -7156,7 +14206,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:30">
       <c r="B82" s="1" t="s">
         <v>68</v>
       </c>
@@ -7245,7 +14295,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:30">
       <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
@@ -7334,7 +14384,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:30">
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
@@ -7423,48 +14473,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:30">
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="22" t="s">
+      <c r="C86" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="23"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="22" t="s">
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="27"/>
+      <c r="J86" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="K86" s="23"/>
-      <c r="L86" s="23"/>
-      <c r="M86" s="23"/>
-      <c r="N86" s="23"/>
-      <c r="O86" s="23"/>
-      <c r="P86" s="23"/>
-      <c r="Q86" s="22" t="s">
+      <c r="K86" s="27"/>
+      <c r="L86" s="27"/>
+      <c r="M86" s="27"/>
+      <c r="N86" s="27"/>
+      <c r="O86" s="27"/>
+      <c r="P86" s="27"/>
+      <c r="Q86" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="R86" s="23"/>
-      <c r="S86" s="23"/>
-      <c r="T86" s="23"/>
-      <c r="U86" s="23"/>
-      <c r="V86" s="23"/>
-      <c r="W86" s="23"/>
-      <c r="X86" s="22" t="s">
+      <c r="R86" s="27"/>
+      <c r="S86" s="27"/>
+      <c r="T86" s="27"/>
+      <c r="U86" s="27"/>
+      <c r="V86" s="27"/>
+      <c r="W86" s="27"/>
+      <c r="X86" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="Y86" s="23"/>
-      <c r="Z86" s="23"/>
-      <c r="AA86" s="23"/>
-      <c r="AB86" s="23"/>
-      <c r="AC86" s="23"/>
-      <c r="AD86" s="23"/>
-    </row>
-    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="Y86" s="27"/>
+      <c r="Z86" s="27"/>
+      <c r="AA86" s="27"/>
+      <c r="AB86" s="27"/>
+      <c r="AC86" s="27"/>
+      <c r="AD86" s="27"/>
+    </row>
+    <row r="87" spans="2:30">
       <c r="B87" s="1"/>
       <c r="C87" s="2" t="s">
         <v>89</v>
@@ -7551,7 +14601,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:30">
       <c r="B88" s="1" t="s">
         <v>67</v>
       </c>
@@ -7640,7 +14690,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:30">
       <c r="B89" s="1" t="s">
         <v>68</v>
       </c>
@@ -7729,7 +14779,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:30">
       <c r="B90" s="1" t="s">
         <v>69</v>
       </c>
@@ -7818,7 +14868,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:30">
       <c r="B91" s="1" t="s">
         <v>70</v>
       </c>
@@ -7909,30 +14959,11 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF35:AL35"/>
-    <mergeCell ref="AF20:AL20"/>
-    <mergeCell ref="AF13:AL13"/>
-    <mergeCell ref="X13:AD13"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="X64:AD64"/>
-    <mergeCell ref="X42:AD42"/>
-    <mergeCell ref="J50:P50"/>
-    <mergeCell ref="X6:AD6"/>
-    <mergeCell ref="X20:AD20"/>
-    <mergeCell ref="B49:AD49"/>
-    <mergeCell ref="Q6:W6"/>
-    <mergeCell ref="X28:AD28"/>
-    <mergeCell ref="Q28:W28"/>
-    <mergeCell ref="Q20:W20"/>
-    <mergeCell ref="B27:AD27"/>
-    <mergeCell ref="J20:P20"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="B71:AD71"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="Q42:W42"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="X50:AD50"/>
     <mergeCell ref="X79:AD79"/>
     <mergeCell ref="Q79:W79"/>
     <mergeCell ref="Q72:W72"/>
@@ -7949,6 +14980,11 @@
     <mergeCell ref="C35:I35"/>
     <mergeCell ref="C72:I72"/>
     <mergeCell ref="J35:P35"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
     <mergeCell ref="Q86:W86"/>
     <mergeCell ref="Q35:W35"/>
     <mergeCell ref="C50:I50"/>
@@ -7960,11 +14996,25 @@
     <mergeCell ref="Q57:W57"/>
     <mergeCell ref="J86:P86"/>
     <mergeCell ref="C57:I57"/>
-    <mergeCell ref="B71:AD71"/>
-    <mergeCell ref="C42:I42"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="X86:AD86"/>
-    <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="X64:AD64"/>
+    <mergeCell ref="X42:AD42"/>
+    <mergeCell ref="J50:P50"/>
+    <mergeCell ref="X6:AD6"/>
+    <mergeCell ref="X20:AD20"/>
+    <mergeCell ref="B49:AD49"/>
+    <mergeCell ref="Q6:W6"/>
+    <mergeCell ref="X28:AD28"/>
+    <mergeCell ref="Q28:W28"/>
+    <mergeCell ref="Q20:W20"/>
+    <mergeCell ref="B27:AD27"/>
+    <mergeCell ref="J20:P20"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="AF28:AL28"/>
+    <mergeCell ref="AF35:AL35"/>
+    <mergeCell ref="AF20:AL20"/>
+    <mergeCell ref="AF13:AL13"/>
+    <mergeCell ref="X13:AD13"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="816" yWindow="876" windowWidth="33120" windowHeight="12048"/>
+    <workbookView xWindow="816" yWindow="876" windowWidth="33120" windowHeight="12048" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="근무표 인쇄용" sheetId="2" r:id="rId1"/>
     <sheet name="48주 로테이션 근무표" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'48주 로테이션 근무표'!$A:$AE</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'근무표 인쇄용'!$A$1:$AE$88</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
@@ -598,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -659,6 +660,7 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -986,78 +988,78 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:46">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-      <c r="M2" s="29"/>
-      <c r="N2" s="29"/>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
-      <c r="X2" s="29"/>
-      <c r="Y2" s="29"/>
-      <c r="Z2" s="29"/>
-      <c r="AA2" s="29"/>
-      <c r="AB2" s="29"/>
-      <c r="AC2" s="29"/>
-      <c r="AD2" s="29"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+      <c r="P2" s="30"/>
+      <c r="Q2" s="30"/>
+      <c r="R2" s="30"/>
+      <c r="S2" s="30"/>
+      <c r="T2" s="30"/>
+      <c r="U2" s="30"/>
+      <c r="V2" s="30"/>
+      <c r="W2" s="30"/>
+      <c r="X2" s="30"/>
+      <c r="Y2" s="30"/>
+      <c r="Z2" s="30"/>
+      <c r="AA2" s="30"/>
+      <c r="AB2" s="30"/>
+      <c r="AC2" s="30"/>
+      <c r="AD2" s="30"/>
     </row>
     <row r="3" spans="2:46">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="27"/>
-      <c r="J3" s="26" t="s">
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="26" t="s">
+      <c r="K3" s="28"/>
+      <c r="L3" s="28"/>
+      <c r="M3" s="28"/>
+      <c r="N3" s="28"/>
+      <c r="O3" s="28"/>
+      <c r="P3" s="28"/>
+      <c r="Q3" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="27"/>
-      <c r="S3" s="27"/>
-      <c r="T3" s="27"/>
-      <c r="U3" s="27"/>
-      <c r="V3" s="27"/>
-      <c r="W3" s="27"/>
-      <c r="X3" s="26" t="s">
+      <c r="R3" s="28"/>
+      <c r="S3" s="28"/>
+      <c r="T3" s="28"/>
+      <c r="U3" s="28"/>
+      <c r="V3" s="28"/>
+      <c r="W3" s="28"/>
+      <c r="X3" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="27"/>
-      <c r="AA3" s="27"/>
-      <c r="AB3" s="27"/>
-      <c r="AC3" s="27"/>
-      <c r="AD3" s="27"/>
+      <c r="Y3" s="28"/>
+      <c r="Z3" s="28"/>
+      <c r="AA3" s="28"/>
+      <c r="AB3" s="28"/>
+      <c r="AC3" s="28"/>
+      <c r="AD3" s="28"/>
     </row>
     <row r="4" spans="2:46">
       <c r="B4" s="1"/>
@@ -1514,51 +1516,51 @@
       <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="C10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="30" t="s">
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="30" t="s">
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="32"/>
-      <c r="X10" s="30" t="s">
+      <c r="R10" s="32"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="32"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="32"/>
-      <c r="AF10" s="30" t="s">
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="32"/>
+      <c r="AA10" s="32"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="32"/>
+      <c r="AD10" s="33"/>
+      <c r="AF10" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="32"/>
+      <c r="AG10" s="32"/>
+      <c r="AH10" s="32"/>
+      <c r="AI10" s="32"/>
+      <c r="AJ10" s="32"/>
+      <c r="AK10" s="32"/>
+      <c r="AL10" s="33"/>
       <c r="AN10" s="21" t="s">
         <v>90</v>
       </c>
@@ -2240,51 +2242,51 @@
       <c r="B17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="30" t="s">
+      <c r="C17" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="31"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="31"/>
-      <c r="I17" s="32"/>
-      <c r="J17" s="30" t="s">
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="32"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="32"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="31"/>
-      <c r="N17" s="31"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="32"/>
-      <c r="Q17" s="30" t="s">
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32"/>
+      <c r="N17" s="32"/>
+      <c r="O17" s="32"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="R17" s="31"/>
-      <c r="S17" s="31"/>
-      <c r="T17" s="31"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="31"/>
-      <c r="W17" s="32"/>
-      <c r="X17" s="30" t="s">
+      <c r="R17" s="32"/>
+      <c r="S17" s="32"/>
+      <c r="T17" s="32"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="Y17" s="31"/>
-      <c r="Z17" s="31"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="32"/>
-      <c r="AF17" s="30" t="s">
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
+      <c r="AA17" s="32"/>
+      <c r="AB17" s="32"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="33"/>
+      <c r="AF17" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AG17" s="31"/>
-      <c r="AH17" s="31"/>
-      <c r="AI17" s="31"/>
-      <c r="AJ17" s="31"/>
-      <c r="AK17" s="31"/>
-      <c r="AL17" s="32"/>
+      <c r="AG17" s="32"/>
+      <c r="AH17" s="32"/>
+      <c r="AI17" s="32"/>
+      <c r="AJ17" s="32"/>
+      <c r="AK17" s="32"/>
+      <c r="AL17" s="33"/>
       <c r="AN17" s="21" t="s">
         <v>91</v>
       </c>
@@ -2963,37 +2965,37 @@
     </row>
     <row r="23" spans="2:46" hidden="1"/>
     <row r="24" spans="2:46">
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="29"/>
-      <c r="E24" s="29"/>
-      <c r="F24" s="29"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-      <c r="L24" s="29"/>
-      <c r="M24" s="29"/>
-      <c r="N24" s="29"/>
-      <c r="O24" s="29"/>
-      <c r="P24" s="29"/>
-      <c r="Q24" s="29"/>
-      <c r="R24" s="29"/>
-      <c r="S24" s="29"/>
-      <c r="T24" s="29"/>
-      <c r="U24" s="29"/>
-      <c r="V24" s="29"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
-      <c r="Y24" s="29"/>
-      <c r="Z24" s="29"/>
-      <c r="AA24" s="29"/>
-      <c r="AB24" s="29"/>
-      <c r="AC24" s="29"/>
-      <c r="AD24" s="29"/>
+      <c r="C24" s="30"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="30"/>
+      <c r="L24" s="30"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="30"/>
+      <c r="O24" s="30"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="30"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="30"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="30"/>
+      <c r="X24" s="30"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="30"/>
+      <c r="AA24" s="30"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="30"/>
+      <c r="AD24" s="30"/>
       <c r="AN24" s="20" t="s">
         <v>95</v>
       </c>
@@ -3005,51 +3007,51 @@
       <c r="B25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="26" t="s">
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="26" t="s">
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="28"/>
+      <c r="Q25" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="27"/>
-      <c r="V25" s="27"/>
-      <c r="W25" s="27"/>
-      <c r="X25" s="26" t="s">
+      <c r="R25" s="28"/>
+      <c r="S25" s="28"/>
+      <c r="T25" s="28"/>
+      <c r="U25" s="28"/>
+      <c r="V25" s="28"/>
+      <c r="W25" s="28"/>
+      <c r="X25" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="Y25" s="27"/>
-      <c r="Z25" s="27"/>
-      <c r="AA25" s="27"/>
-      <c r="AB25" s="27"/>
-      <c r="AC25" s="27"/>
-      <c r="AD25" s="27"/>
-      <c r="AF25" s="26" t="s">
+      <c r="Y25" s="28"/>
+      <c r="Z25" s="28"/>
+      <c r="AA25" s="28"/>
+      <c r="AB25" s="28"/>
+      <c r="AC25" s="28"/>
+      <c r="AD25" s="28"/>
+      <c r="AF25" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AG25" s="27"/>
-      <c r="AH25" s="27"/>
-      <c r="AI25" s="27"/>
-      <c r="AJ25" s="27"/>
-      <c r="AK25" s="27"/>
-      <c r="AL25" s="27"/>
+      <c r="AG25" s="28"/>
+      <c r="AH25" s="28"/>
+      <c r="AI25" s="28"/>
+      <c r="AJ25" s="28"/>
+      <c r="AK25" s="28"/>
+      <c r="AL25" s="28"/>
       <c r="AN25" s="21" t="s">
         <v>90</v>
       </c>
@@ -3727,51 +3729,51 @@
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="31"/>
-      <c r="E32" s="31"/>
-      <c r="F32" s="31"/>
-      <c r="G32" s="31"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="32"/>
-      <c r="J32" s="30" t="s">
+      <c r="D32" s="32"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="32"/>
+      <c r="G32" s="32"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
-      <c r="O32" s="31"/>
-      <c r="P32" s="32"/>
-      <c r="Q32" s="30" t="s">
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
+      <c r="O32" s="32"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="R32" s="31"/>
-      <c r="S32" s="31"/>
-      <c r="T32" s="31"/>
-      <c r="U32" s="31"/>
-      <c r="V32" s="31"/>
-      <c r="W32" s="32"/>
-      <c r="X32" s="30" t="s">
+      <c r="R32" s="32"/>
+      <c r="S32" s="32"/>
+      <c r="T32" s="32"/>
+      <c r="U32" s="32"/>
+      <c r="V32" s="32"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="Y32" s="31"/>
-      <c r="Z32" s="31"/>
-      <c r="AA32" s="31"/>
-      <c r="AB32" s="31"/>
-      <c r="AC32" s="31"/>
-      <c r="AD32" s="32"/>
-      <c r="AF32" s="30" t="s">
+      <c r="Y32" s="32"/>
+      <c r="Z32" s="32"/>
+      <c r="AA32" s="32"/>
+      <c r="AB32" s="32"/>
+      <c r="AC32" s="32"/>
+      <c r="AD32" s="33"/>
+      <c r="AF32" s="31" t="s">
         <v>97</v>
       </c>
-      <c r="AG32" s="31"/>
-      <c r="AH32" s="31"/>
-      <c r="AI32" s="31"/>
-      <c r="AJ32" s="31"/>
-      <c r="AK32" s="31"/>
-      <c r="AL32" s="32"/>
+      <c r="AG32" s="32"/>
+      <c r="AH32" s="32"/>
+      <c r="AI32" s="32"/>
+      <c r="AJ32" s="32"/>
+      <c r="AK32" s="32"/>
+      <c r="AL32" s="33"/>
       <c r="AN32" s="21" t="s">
         <v>91</v>
       </c>
@@ -4450,42 +4452,42 @@
       <c r="B39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="30" t="s">
+      <c r="C39" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="30" t="s">
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
-      <c r="M39" s="31"/>
-      <c r="N39" s="31"/>
-      <c r="O39" s="31"/>
-      <c r="P39" s="32"/>
-      <c r="Q39" s="30" t="s">
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="32"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="31" t="s">
         <v>37</v>
       </c>
-      <c r="R39" s="31"/>
-      <c r="S39" s="31"/>
-      <c r="T39" s="31"/>
-      <c r="U39" s="31"/>
-      <c r="V39" s="31"/>
-      <c r="W39" s="32"/>
-      <c r="X39" s="30" t="s">
+      <c r="R39" s="32"/>
+      <c r="S39" s="32"/>
+      <c r="T39" s="32"/>
+      <c r="U39" s="32"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="31" t="s">
         <v>38</v>
       </c>
-      <c r="Y39" s="31"/>
-      <c r="Z39" s="31"/>
-      <c r="AA39" s="31"/>
-      <c r="AB39" s="31"/>
-      <c r="AC39" s="31"/>
-      <c r="AD39" s="32"/>
+      <c r="Y39" s="32"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="32"/>
+      <c r="AB39" s="32"/>
+      <c r="AC39" s="32"/>
+      <c r="AD39" s="33"/>
     </row>
     <row r="40" spans="2:46" hidden="1">
       <c r="B40" s="1"/>
@@ -4932,78 +4934,78 @@
     </row>
     <row r="45" spans="2:46" hidden="1"/>
     <row r="46" spans="2:46">
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
-      <c r="AA46" s="29"/>
-      <c r="AB46" s="29"/>
-      <c r="AC46" s="29"/>
-      <c r="AD46" s="29"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
+      <c r="AA46" s="30"/>
+      <c r="AB46" s="30"/>
+      <c r="AC46" s="30"/>
+      <c r="AD46" s="30"/>
     </row>
     <row r="47" spans="2:46">
       <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="26" t="s">
+      <c r="C47" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="27"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="27"/>
-      <c r="G47" s="27"/>
-      <c r="H47" s="27"/>
-      <c r="I47" s="27"/>
-      <c r="J47" s="26" t="s">
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28"/>
+      <c r="H47" s="28"/>
+      <c r="I47" s="28"/>
+      <c r="J47" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="K47" s="27"/>
-      <c r="L47" s="27"/>
-      <c r="M47" s="27"/>
-      <c r="N47" s="27"/>
-      <c r="O47" s="27"/>
-      <c r="P47" s="27"/>
-      <c r="Q47" s="26" t="s">
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28"/>
+      <c r="P47" s="28"/>
+      <c r="Q47" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="R47" s="27"/>
-      <c r="S47" s="27"/>
-      <c r="T47" s="27"/>
-      <c r="U47" s="27"/>
-      <c r="V47" s="27"/>
-      <c r="W47" s="27"/>
-      <c r="X47" s="26" t="s">
+      <c r="R47" s="28"/>
+      <c r="S47" s="28"/>
+      <c r="T47" s="28"/>
+      <c r="U47" s="28"/>
+      <c r="V47" s="28"/>
+      <c r="W47" s="28"/>
+      <c r="X47" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="Y47" s="27"/>
-      <c r="Z47" s="27"/>
-      <c r="AA47" s="27"/>
-      <c r="AB47" s="27"/>
-      <c r="AC47" s="27"/>
-      <c r="AD47" s="27"/>
+      <c r="Y47" s="28"/>
+      <c r="Z47" s="28"/>
+      <c r="AA47" s="28"/>
+      <c r="AB47" s="28"/>
+      <c r="AC47" s="28"/>
+      <c r="AD47" s="28"/>
     </row>
     <row r="48" spans="2:46">
       <c r="B48" s="1"/>
@@ -5453,42 +5455,42 @@
       <c r="B54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="26" t="s">
+      <c r="C54" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="27"/>
-      <c r="E54" s="27"/>
-      <c r="F54" s="27"/>
-      <c r="G54" s="27"/>
-      <c r="H54" s="27"/>
-      <c r="I54" s="27"/>
-      <c r="J54" s="26" t="s">
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="K54" s="27"/>
-      <c r="L54" s="27"/>
-      <c r="M54" s="27"/>
-      <c r="N54" s="27"/>
-      <c r="O54" s="27"/>
-      <c r="P54" s="27"/>
-      <c r="Q54" s="26" t="s">
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="R54" s="27"/>
-      <c r="S54" s="27"/>
-      <c r="T54" s="27"/>
-      <c r="U54" s="27"/>
-      <c r="V54" s="27"/>
-      <c r="W54" s="27"/>
-      <c r="X54" s="26" t="s">
+      <c r="R54" s="28"/>
+      <c r="S54" s="28"/>
+      <c r="T54" s="28"/>
+      <c r="U54" s="28"/>
+      <c r="V54" s="28"/>
+      <c r="W54" s="28"/>
+      <c r="X54" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="Y54" s="27"/>
-      <c r="Z54" s="27"/>
-      <c r="AA54" s="27"/>
-      <c r="AB54" s="27"/>
-      <c r="AC54" s="27"/>
-      <c r="AD54" s="27"/>
+      <c r="Y54" s="28"/>
+      <c r="Z54" s="28"/>
+      <c r="AA54" s="28"/>
+      <c r="AB54" s="28"/>
+      <c r="AC54" s="28"/>
+      <c r="AD54" s="28"/>
     </row>
     <row r="55" spans="2:30" hidden="1">
       <c r="B55" s="1"/>
@@ -5938,42 +5940,42 @@
       <c r="B61" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="26" t="s">
+      <c r="C61" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="26" t="s">
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="26" t="s">
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="26" t="s">
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
-      <c r="AC61" s="27"/>
-      <c r="AD61" s="27"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
+      <c r="AC61" s="28"/>
+      <c r="AD61" s="28"/>
     </row>
     <row r="62" spans="2:30" hidden="1">
       <c r="B62" s="1"/>
@@ -6420,78 +6422,78 @@
     </row>
     <row r="67" spans="2:30" hidden="1"/>
     <row r="68" spans="2:30">
-      <c r="B68" s="28" t="s">
+      <c r="B68" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="29"/>
-      <c r="I68" s="29"/>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29"/>
-      <c r="P68" s="29"/>
-      <c r="Q68" s="29"/>
-      <c r="R68" s="29"/>
-      <c r="S68" s="29"/>
-      <c r="T68" s="29"/>
-      <c r="U68" s="29"/>
-      <c r="V68" s="29"/>
-      <c r="W68" s="29"/>
-      <c r="X68" s="29"/>
-      <c r="Y68" s="29"/>
-      <c r="Z68" s="29"/>
-      <c r="AA68" s="29"/>
-      <c r="AB68" s="29"/>
-      <c r="AC68" s="29"/>
-      <c r="AD68" s="29"/>
+      <c r="C68" s="30"/>
+      <c r="D68" s="30"/>
+      <c r="E68" s="30"/>
+      <c r="F68" s="30"/>
+      <c r="G68" s="30"/>
+      <c r="H68" s="30"/>
+      <c r="I68" s="30"/>
+      <c r="J68" s="30"/>
+      <c r="K68" s="30"/>
+      <c r="L68" s="30"/>
+      <c r="M68" s="30"/>
+      <c r="N68" s="30"/>
+      <c r="O68" s="30"/>
+      <c r="P68" s="30"/>
+      <c r="Q68" s="30"/>
+      <c r="R68" s="30"/>
+      <c r="S68" s="30"/>
+      <c r="T68" s="30"/>
+      <c r="U68" s="30"/>
+      <c r="V68" s="30"/>
+      <c r="W68" s="30"/>
+      <c r="X68" s="30"/>
+      <c r="Y68" s="30"/>
+      <c r="Z68" s="30"/>
+      <c r="AA68" s="30"/>
+      <c r="AB68" s="30"/>
+      <c r="AC68" s="30"/>
+      <c r="AD68" s="30"/>
     </row>
     <row r="69" spans="2:30">
       <c r="B69" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="26" t="s">
+      <c r="C69" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="26" t="s">
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28"/>
+      <c r="H69" s="28"/>
+      <c r="I69" s="28"/>
+      <c r="J69" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="K69" s="27"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="27"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="26" t="s">
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28"/>
+      <c r="P69" s="28"/>
+      <c r="Q69" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="R69" s="27"/>
-      <c r="S69" s="27"/>
-      <c r="T69" s="27"/>
-      <c r="U69" s="27"/>
-      <c r="V69" s="27"/>
-      <c r="W69" s="27"/>
-      <c r="X69" s="26" t="s">
+      <c r="R69" s="28"/>
+      <c r="S69" s="28"/>
+      <c r="T69" s="28"/>
+      <c r="U69" s="28"/>
+      <c r="V69" s="28"/>
+      <c r="W69" s="28"/>
+      <c r="X69" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y69" s="27"/>
-      <c r="Z69" s="27"/>
-      <c r="AA69" s="27"/>
-      <c r="AB69" s="27"/>
-      <c r="AC69" s="27"/>
-      <c r="AD69" s="27"/>
+      <c r="Y69" s="28"/>
+      <c r="Z69" s="28"/>
+      <c r="AA69" s="28"/>
+      <c r="AB69" s="28"/>
+      <c r="AC69" s="28"/>
+      <c r="AD69" s="28"/>
     </row>
     <row r="70" spans="2:30">
       <c r="B70" s="1"/>
@@ -6941,42 +6943,42 @@
       <c r="B76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C76" s="26" t="s">
+      <c r="C76" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="27"/>
-      <c r="J76" s="26" t="s">
+      <c r="D76" s="28"/>
+      <c r="E76" s="28"/>
+      <c r="F76" s="28"/>
+      <c r="G76" s="28"/>
+      <c r="H76" s="28"/>
+      <c r="I76" s="28"/>
+      <c r="J76" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="K76" s="27"/>
-      <c r="L76" s="27"/>
-      <c r="M76" s="27"/>
-      <c r="N76" s="27"/>
-      <c r="O76" s="27"/>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="26" t="s">
+      <c r="K76" s="28"/>
+      <c r="L76" s="28"/>
+      <c r="M76" s="28"/>
+      <c r="N76" s="28"/>
+      <c r="O76" s="28"/>
+      <c r="P76" s="28"/>
+      <c r="Q76" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="R76" s="27"/>
-      <c r="S76" s="27"/>
-      <c r="T76" s="27"/>
-      <c r="U76" s="27"/>
-      <c r="V76" s="27"/>
-      <c r="W76" s="27"/>
-      <c r="X76" s="26" t="s">
+      <c r="R76" s="28"/>
+      <c r="S76" s="28"/>
+      <c r="T76" s="28"/>
+      <c r="U76" s="28"/>
+      <c r="V76" s="28"/>
+      <c r="W76" s="28"/>
+      <c r="X76" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="Y76" s="27"/>
-      <c r="Z76" s="27"/>
-      <c r="AA76" s="27"/>
-      <c r="AB76" s="27"/>
-      <c r="AC76" s="27"/>
-      <c r="AD76" s="27"/>
+      <c r="Y76" s="28"/>
+      <c r="Z76" s="28"/>
+      <c r="AA76" s="28"/>
+      <c r="AB76" s="28"/>
+      <c r="AC76" s="28"/>
+      <c r="AD76" s="28"/>
     </row>
     <row r="77" spans="2:30" hidden="1">
       <c r="B77" s="1"/>
@@ -7426,42 +7428,42 @@
       <c r="B83" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="26" t="s">
+      <c r="C83" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
-      <c r="J83" s="26" t="s">
+      <c r="D83" s="28"/>
+      <c r="E83" s="28"/>
+      <c r="F83" s="28"/>
+      <c r="G83" s="28"/>
+      <c r="H83" s="28"/>
+      <c r="I83" s="28"/>
+      <c r="J83" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-      <c r="M83" s="27"/>
-      <c r="N83" s="27"/>
-      <c r="O83" s="27"/>
-      <c r="P83" s="27"/>
-      <c r="Q83" s="26" t="s">
+      <c r="K83" s="28"/>
+      <c r="L83" s="28"/>
+      <c r="M83" s="28"/>
+      <c r="N83" s="28"/>
+      <c r="O83" s="28"/>
+      <c r="P83" s="28"/>
+      <c r="Q83" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="R83" s="27"/>
-      <c r="S83" s="27"/>
-      <c r="T83" s="27"/>
-      <c r="U83" s="27"/>
-      <c r="V83" s="27"/>
-      <c r="W83" s="27"/>
-      <c r="X83" s="26" t="s">
+      <c r="R83" s="28"/>
+      <c r="S83" s="28"/>
+      <c r="T83" s="28"/>
+      <c r="U83" s="28"/>
+      <c r="V83" s="28"/>
+      <c r="W83" s="28"/>
+      <c r="X83" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="Y83" s="27"/>
-      <c r="Z83" s="27"/>
-      <c r="AA83" s="27"/>
-      <c r="AB83" s="27"/>
-      <c r="AC83" s="27"/>
-      <c r="AD83" s="27"/>
+      <c r="Y83" s="28"/>
+      <c r="Z83" s="28"/>
+      <c r="AA83" s="28"/>
+      <c r="AB83" s="28"/>
+      <c r="AC83" s="28"/>
+      <c r="AD83" s="28"/>
     </row>
     <row r="84" spans="2:30" hidden="1">
       <c r="B84" s="1"/>
@@ -7908,19 +7910,36 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="J76:P76"/>
-    <mergeCell ref="Q76:W76"/>
-    <mergeCell ref="X76:AD76"/>
-    <mergeCell ref="C83:I83"/>
-    <mergeCell ref="J83:P83"/>
-    <mergeCell ref="Q83:W83"/>
-    <mergeCell ref="X83:AD83"/>
-    <mergeCell ref="C61:I61"/>
-    <mergeCell ref="J61:P61"/>
-    <mergeCell ref="Q61:W61"/>
-    <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="B68:AD68"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="Q3:W3"/>
+    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="AF25:AL25"/>
+    <mergeCell ref="AF10:AL10"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:W17"/>
+    <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="AF17:AL17"/>
+    <mergeCell ref="X10:AD10"/>
+    <mergeCell ref="Q10:W10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="B24:AD24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:W32"/>
+    <mergeCell ref="X32:AD32"/>
+    <mergeCell ref="AF32:AL32"/>
     <mergeCell ref="C69:I69"/>
     <mergeCell ref="J69:P69"/>
     <mergeCell ref="Q69:W69"/>
@@ -7934,36 +7953,19 @@
     <mergeCell ref="J54:P54"/>
     <mergeCell ref="Q54:W54"/>
     <mergeCell ref="X54:AD54"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:W32"/>
-    <mergeCell ref="X32:AD32"/>
-    <mergeCell ref="AF32:AL32"/>
-    <mergeCell ref="C39:I39"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="Q39:W39"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="B24:AD24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:W25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="AF25:AL25"/>
-    <mergeCell ref="AF10:AL10"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="X17:AD17"/>
-    <mergeCell ref="AF17:AL17"/>
-    <mergeCell ref="X10:AD10"/>
-    <mergeCell ref="Q10:W10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="J3:P3"/>
-    <mergeCell ref="Q3:W3"/>
-    <mergeCell ref="X3:AD3"/>
+    <mergeCell ref="C61:I61"/>
+    <mergeCell ref="J61:P61"/>
+    <mergeCell ref="Q61:W61"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="B68:AD68"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="J76:P76"/>
+    <mergeCell ref="Q76:W76"/>
+    <mergeCell ref="X76:AD76"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="J83:P83"/>
+    <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="X83:AD83"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7974,100 +7976,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AT91"/>
+  <dimension ref="B2:AU91"/>
   <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
   <cols>
-    <col min="1" max="1" width="3" style="9" customWidth="1"/>
+    <col min="1" max="1" width="2" style="9" customWidth="1"/>
     <col min="2" max="2" width="10.3984375" style="9" customWidth="1"/>
     <col min="3" max="30" width="7" style="9" customWidth="1"/>
-    <col min="31" max="16384" width="8.69921875" style="9"/>
+    <col min="31" max="31" width="2" style="9" customWidth="1"/>
+    <col min="32" max="32" width="3.296875" style="26" customWidth="1"/>
+    <col min="33" max="16384" width="8.69921875" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46">
+    <row r="2" spans="2:47">
       <c r="B2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:46">
+    <row r="3" spans="2:47">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:46">
-      <c r="B5" s="28" t="s">
+    <row r="5" spans="2:47">
+      <c r="B5" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="29"/>
-      <c r="AC5" s="29"/>
-      <c r="AD5" s="29"/>
-    </row>
-    <row r="6" spans="2:46">
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30"/>
+      <c r="AD5" s="30"/>
+    </row>
+    <row r="6" spans="2:47">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="26" t="s">
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="26" t="s">
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="28"/>
+      <c r="Q6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27"/>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="26" t="s">
+      <c r="R6" s="28"/>
+      <c r="S6" s="28"/>
+      <c r="T6" s="28"/>
+      <c r="U6" s="28"/>
+      <c r="V6" s="28"/>
+      <c r="W6" s="28"/>
+      <c r="X6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="27"/>
-      <c r="AC6" s="27"/>
-      <c r="AD6" s="27"/>
-    </row>
-    <row r="7" spans="2:46">
+      <c r="Y6" s="28"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="28"/>
+      <c r="AB6" s="28"/>
+      <c r="AC6" s="28"/>
+      <c r="AD6" s="28"/>
+    </row>
+    <row r="7" spans="2:47">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
@@ -8154,7 +8158,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:46">
+    <row r="8" spans="2:47">
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
@@ -8243,7 +8247,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:46">
+    <row r="9" spans="2:47">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -8332,7 +8336,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:46">
+    <row r="10" spans="2:47">
       <c r="B10" s="1" t="s">
         <v>69</v>
       </c>
@@ -8421,7 +8425,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:46">
+    <row r="11" spans="2:47">
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
@@ -8510,75 +8514,75 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:46">
-      <c r="AN12" s="20" t="s">
+    <row r="12" spans="2:47">
+      <c r="AO12" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="AO12" s="20"/>
       <c r="AP12" s="20"/>
       <c r="AQ12" s="20"/>
-    </row>
-    <row r="13" spans="2:46">
+      <c r="AR12" s="20"/>
+    </row>
+    <row r="13" spans="2:47">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="26" t="s">
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="27" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="26" t="s">
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28"/>
+      <c r="P13" s="28"/>
+      <c r="Q13" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="27"/>
-      <c r="X13" s="26" t="s">
+      <c r="R13" s="28"/>
+      <c r="S13" s="28"/>
+      <c r="T13" s="28"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="28"/>
+      <c r="W13" s="28"/>
+      <c r="X13" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="Y13" s="27"/>
-      <c r="Z13" s="27"/>
-      <c r="AA13" s="27"/>
-      <c r="AB13" s="27"/>
-      <c r="AC13" s="27"/>
-      <c r="AD13" s="27"/>
-      <c r="AF13" s="26" t="s">
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="28"/>
+      <c r="AA13" s="28"/>
+      <c r="AB13" s="28"/>
+      <c r="AC13" s="28"/>
+      <c r="AD13" s="28"/>
+      <c r="AG13" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AG13" s="27"/>
-      <c r="AH13" s="27"/>
-      <c r="AI13" s="27"/>
-      <c r="AJ13" s="27"/>
-      <c r="AK13" s="27"/>
-      <c r="AL13" s="27"/>
-      <c r="AM13" s="18"/>
-      <c r="AN13" s="21" t="s">
+      <c r="AH13" s="28"/>
+      <c r="AI13" s="28"/>
+      <c r="AJ13" s="28"/>
+      <c r="AK13" s="28"/>
+      <c r="AL13" s="28"/>
+      <c r="AM13" s="28"/>
+      <c r="AN13" s="18"/>
+      <c r="AO13" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="AO13" s="21"/>
       <c r="AP13" s="21"/>
       <c r="AQ13" s="21"/>
-      <c r="AR13" s="18"/>
+      <c r="AR13" s="21"/>
       <c r="AS13" s="18"/>
       <c r="AT13" s="18"/>
-    </row>
-    <row r="14" spans="2:46">
+      <c r="AU13" s="18"/>
+    </row>
+    <row r="14" spans="2:47">
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
         <v>78</v>
@@ -8664,51 +8668,51 @@
       <c r="AD14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AF14" s="2" t="s">
+      <c r="AG14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG14" s="2" t="s">
+      <c r="AH14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="2" t="s">
+      <c r="AI14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI14" s="2" t="s">
+      <c r="AJ14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AJ14" s="2" t="s">
+      <c r="AK14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AK14" s="3" t="s">
+      <c r="AL14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AL14" s="4" t="s">
+      <c r="AM14" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AM14" s="18"/>
-      <c r="AN14" s="14" t="s">
+      <c r="AN14" s="18"/>
+      <c r="AO14" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AO14" s="2" t="s">
+      <c r="AP14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AP14" s="2" t="s">
+      <c r="AQ14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ14" s="2" t="s">
+      <c r="AR14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AR14" s="2" t="s">
+      <c r="AS14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AS14" s="3" t="s">
+      <c r="AT14" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AT14" s="4" t="s">
+      <c r="AU14" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:46">
+    <row r="15" spans="2:47">
       <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
@@ -8797,11 +8801,9 @@
         <v>15</v>
       </c>
       <c r="AE15" s="19"/>
-      <c r="AF15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG15" s="6" t="s">
-        <v>16</v>
+      <c r="AF15" s="19"/>
+      <c r="AG15" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AH15" s="6" t="s">
         <v>16</v>
@@ -8815,23 +8817,23 @@
       <c r="AK15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM15" s="19" t="s">
+      <c r="AL15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN15" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="AO15" s="2" t="s">
-        <v>15</v>
+      <c r="AO15" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AP15" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AQ15" s="6" t="s">
-        <v>16</v>
+      <c r="AQ15" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AR15" s="6" t="s">
         <v>16</v>
@@ -8839,11 +8841,14 @@
       <c r="AS15" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AT15" s="12" t="s">
+      <c r="AT15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU15" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:46">
+    <row r="16" spans="2:47">
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
@@ -8932,9 +8937,7 @@
         <v>15</v>
       </c>
       <c r="AE16" s="19"/>
-      <c r="AF16" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="AF16" s="19"/>
       <c r="AG16" s="5" t="s">
         <v>14</v>
       </c>
@@ -8947,20 +8950,20 @@
       <c r="AJ16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AK16" s="2" t="s">
-        <v>15</v>
+      <c r="AK16" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AL16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM16" s="19" t="s">
+      <c r="AM16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN16" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO16" s="7" t="s">
-        <v>17</v>
+      <c r="AO16" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AP16" s="7" t="s">
         <v>17</v>
@@ -8974,11 +8977,14 @@
       <c r="AS16" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AT16" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="2:46">
+      <c r="AT16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU16" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="2:47">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -9067,33 +9073,31 @@
         <v>66</v>
       </c>
       <c r="AE17" s="19"/>
-      <c r="AF17" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="AF17" s="19"/>
       <c r="AG17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="AH17" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AI17" s="2" t="s">
-        <v>15</v>
+      <c r="AI17" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AJ17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL17" s="12" t="s">
+      <c r="AK17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM17" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AM17" s="19" t="s">
+      <c r="AN17" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN17" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AO17" s="5" t="s">
         <v>14</v>
       </c>
@@ -9106,14 +9110,17 @@
       <c r="AR17" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS17" s="2" t="s">
-        <v>15</v>
+      <c r="AS17" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AT17" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="18" spans="2:46">
+      <c r="AU17" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="2:47">
       <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
@@ -9202,17 +9209,15 @@
         <v>65</v>
       </c>
       <c r="AE18" s="19"/>
-      <c r="AF18" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG18" s="2" t="s">
-        <v>15</v>
+      <c r="AF18" s="19"/>
+      <c r="AG18" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AH18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI18" s="7" t="s">
-        <v>17</v>
+      <c r="AI18" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AJ18" s="7" t="s">
         <v>17</v>
@@ -9220,36 +9225,38 @@
       <c r="AK18" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AL18" s="11" t="s">
+      <c r="AL18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM18" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AM18" s="19" t="s">
+      <c r="AN18" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN18" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="AO18" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AP18" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AQ18" s="2" t="s">
-        <v>15</v>
+      <c r="AQ18" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AR18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS18" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT18" s="11" t="s">
+      <c r="AS18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT18" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU18" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:46">
-      <c r="AF19" s="18"/>
+    <row r="19" spans="2:47">
       <c r="AG19" s="18"/>
       <c r="AH19" s="18"/>
       <c r="AI19" s="18"/>
@@ -9264,68 +9271,69 @@
       <c r="AR19" s="18"/>
       <c r="AS19" s="18"/>
       <c r="AT19" s="18"/>
-    </row>
-    <row r="20" spans="2:46">
+      <c r="AU19" s="18"/>
+    </row>
+    <row r="20" spans="2:47">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="26" t="s">
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="26" t="s">
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="26" t="s">
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="27"/>
-      <c r="AF20" s="26" t="s">
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AG20" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="27"/>
-      <c r="AI20" s="27"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="27"/>
-      <c r="AL20" s="27"/>
-      <c r="AM20" s="18"/>
-      <c r="AN20" s="21" t="s">
+      <c r="AH20" s="28"/>
+      <c r="AI20" s="28"/>
+      <c r="AJ20" s="28"/>
+      <c r="AK20" s="28"/>
+      <c r="AL20" s="28"/>
+      <c r="AM20" s="28"/>
+      <c r="AN20" s="18"/>
+      <c r="AO20" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="AO20" s="21"/>
       <c r="AP20" s="21"/>
       <c r="AQ20" s="21"/>
-      <c r="AR20" s="18"/>
+      <c r="AR20" s="21"/>
       <c r="AS20" s="18"/>
       <c r="AT20" s="18"/>
-    </row>
-    <row r="21" spans="2:46">
+      <c r="AU20" s="18"/>
+    </row>
+    <row r="21" spans="2:47">
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
         <v>79</v>
@@ -9411,51 +9419,51 @@
       <c r="AD21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AF21" s="2" t="s">
+      <c r="AG21" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG21" s="2" t="s">
+      <c r="AH21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AH21" s="2" t="s">
+      <c r="AI21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI21" s="2" t="s">
+      <c r="AJ21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AJ21" s="2" t="s">
+      <c r="AK21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AK21" s="3" t="s">
+      <c r="AL21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AL21" s="4" t="s">
+      <c r="AM21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AM21" s="18"/>
-      <c r="AN21" s="14" t="s">
+      <c r="AN21" s="18"/>
+      <c r="AO21" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AO21" s="2" t="s">
+      <c r="AP21" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AP21" s="2" t="s">
+      <c r="AQ21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ21" s="2" t="s">
+      <c r="AR21" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AR21" s="2" t="s">
+      <c r="AS21" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AS21" s="3" t="s">
+      <c r="AT21" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AT21" s="4" t="s">
+      <c r="AU21" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:46">
+    <row r="22" spans="2:47">
       <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
@@ -9544,11 +9552,9 @@
         <v>15</v>
       </c>
       <c r="AE22" s="19"/>
-      <c r="AF22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG22" s="6" t="s">
-        <v>16</v>
+      <c r="AF22" s="19"/>
+      <c r="AG22" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AH22" s="6" t="s">
         <v>16</v>
@@ -9562,15 +9568,15 @@
       <c r="AK22" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM22" s="19" t="s">
+      <c r="AL22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN22" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN22" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AO22" s="5" t="s">
         <v>14</v>
       </c>
@@ -9583,14 +9589,17 @@
       <c r="AR22" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS22" s="2" t="s">
-        <v>15</v>
+      <c r="AS22" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AT22" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="2:46">
+      <c r="AU22" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="2:47">
       <c r="B23" s="1" t="s">
         <v>68</v>
       </c>
@@ -9679,9 +9688,7 @@
         <v>15</v>
       </c>
       <c r="AE23" s="19"/>
-      <c r="AF23" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="AF23" s="19"/>
       <c r="AG23" s="5" t="s">
         <v>14</v>
       </c>
@@ -9694,38 +9701,41 @@
       <c r="AJ23" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AK23" s="2" t="s">
-        <v>15</v>
+      <c r="AK23" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AL23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM23" s="19" t="s">
+      <c r="AM23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN23" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN23" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="AO23" s="7" t="s">
         <v>17</v>
       </c>
       <c r="AP23" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AQ23" s="2" t="s">
-        <v>15</v>
+      <c r="AQ23" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AR23" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT23" s="12" t="s">
+      <c r="AS23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU23" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:46">
+    <row r="24" spans="2:47">
       <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
@@ -9814,41 +9824,39 @@
         <v>66</v>
       </c>
       <c r="AE24" s="19"/>
-      <c r="AF24" s="7" t="s">
-        <v>17</v>
-      </c>
+      <c r="AF24" s="19"/>
       <c r="AG24" s="7" t="s">
         <v>17</v>
       </c>
       <c r="AH24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AI24" s="2" t="s">
-        <v>15</v>
+      <c r="AI24" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AJ24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK24" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL24" s="12" t="s">
+      <c r="AK24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL24" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM24" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AM24" s="19" t="s">
+      <c r="AN24" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN24" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO24" s="2" t="s">
-        <v>15</v>
+      <c r="AO24" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AP24" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AQ24" s="7" t="s">
-        <v>17</v>
+      <c r="AQ24" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AR24" s="7" t="s">
         <v>17</v>
@@ -9856,11 +9864,14 @@
       <c r="AS24" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AT24" s="11" t="s">
+      <c r="AT24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU24" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:46">
+    <row r="25" spans="2:47">
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
@@ -9949,17 +9960,15 @@
         <v>65</v>
       </c>
       <c r="AE25" s="19"/>
-      <c r="AF25" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AG25" s="2" t="s">
-        <v>15</v>
+      <c r="AF25" s="19"/>
+      <c r="AG25" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AH25" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI25" s="7" t="s">
-        <v>17</v>
+      <c r="AI25" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AJ25" s="7" t="s">
         <v>17</v>
@@ -9967,17 +9976,17 @@
       <c r="AK25" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AL25" s="11" t="s">
+      <c r="AL25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM25" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AM25" s="19" t="s">
+      <c r="AN25" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO25" s="6" t="s">
-        <v>16</v>
+      <c r="AO25" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AP25" s="6" t="s">
         <v>16</v>
@@ -9991,110 +10000,113 @@
       <c r="AS25" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AT25" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="27" spans="2:46">
-      <c r="B27" s="28" t="s">
+      <c r="AT25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU25" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="27" spans="2:47">
+      <c r="B27" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="29"/>
-      <c r="D27" s="29"/>
-      <c r="E27" s="29"/>
-      <c r="F27" s="29"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-      <c r="L27" s="29"/>
-      <c r="M27" s="29"/>
-      <c r="N27" s="29"/>
-      <c r="O27" s="29"/>
-      <c r="P27" s="29"/>
-      <c r="Q27" s="29"/>
-      <c r="R27" s="29"/>
-      <c r="S27" s="29"/>
-      <c r="T27" s="29"/>
-      <c r="U27" s="29"/>
-      <c r="V27" s="29"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
-      <c r="Y27" s="29"/>
-      <c r="Z27" s="29"/>
-      <c r="AA27" s="29"/>
-      <c r="AB27" s="29"/>
-      <c r="AC27" s="29"/>
-      <c r="AD27" s="29"/>
-      <c r="AN27" s="20" t="s">
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="30"/>
+      <c r="I27" s="30"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="30"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="30"/>
+      <c r="X27" s="30"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="30"/>
+      <c r="AA27" s="30"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="30"/>
+      <c r="AD27" s="30"/>
+      <c r="AO27" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="AO27" s="20"/>
       <c r="AP27" s="20"/>
       <c r="AQ27" s="20"/>
-    </row>
-    <row r="28" spans="2:46">
+      <c r="AR27" s="20"/>
+    </row>
+    <row r="28" spans="2:47">
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="26" t="s">
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="26" t="s">
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28"/>
+      <c r="P28" s="28"/>
+      <c r="Q28" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="27"/>
-      <c r="W28" s="27"/>
-      <c r="X28" s="26" t="s">
+      <c r="R28" s="28"/>
+      <c r="S28" s="28"/>
+      <c r="T28" s="28"/>
+      <c r="U28" s="28"/>
+      <c r="V28" s="28"/>
+      <c r="W28" s="28"/>
+      <c r="X28" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="Y28" s="27"/>
-      <c r="Z28" s="27"/>
-      <c r="AA28" s="27"/>
-      <c r="AB28" s="27"/>
-      <c r="AC28" s="27"/>
-      <c r="AD28" s="27"/>
-      <c r="AF28" s="26" t="s">
+      <c r="Y28" s="28"/>
+      <c r="Z28" s="28"/>
+      <c r="AA28" s="28"/>
+      <c r="AB28" s="28"/>
+      <c r="AC28" s="28"/>
+      <c r="AD28" s="28"/>
+      <c r="AG28" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AG28" s="27"/>
-      <c r="AH28" s="27"/>
-      <c r="AI28" s="27"/>
-      <c r="AJ28" s="27"/>
-      <c r="AK28" s="27"/>
-      <c r="AL28" s="27"/>
-      <c r="AM28" s="18"/>
-      <c r="AN28" s="21" t="s">
+      <c r="AH28" s="28"/>
+      <c r="AI28" s="28"/>
+      <c r="AJ28" s="28"/>
+      <c r="AK28" s="28"/>
+      <c r="AL28" s="28"/>
+      <c r="AM28" s="28"/>
+      <c r="AN28" s="18"/>
+      <c r="AO28" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="AO28" s="21"/>
       <c r="AP28" s="21"/>
       <c r="AQ28" s="21"/>
-      <c r="AR28" s="18"/>
+      <c r="AR28" s="21"/>
       <c r="AS28" s="18"/>
       <c r="AT28" s="18"/>
-    </row>
-    <row r="29" spans="2:46">
+      <c r="AU28" s="18"/>
+    </row>
+    <row r="29" spans="2:47">
       <c r="B29" s="1"/>
       <c r="C29" s="14" t="s">
         <v>80</v>
@@ -10180,51 +10192,51 @@
       <c r="AD29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AF29" s="2" t="s">
+      <c r="AG29" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG29" s="2" t="s">
+      <c r="AH29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="2" t="s">
+      <c r="AI29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI29" s="2" t="s">
+      <c r="AJ29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AJ29" s="2" t="s">
+      <c r="AK29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AK29" s="3" t="s">
+      <c r="AL29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AL29" s="4" t="s">
+      <c r="AM29" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AM29" s="18"/>
-      <c r="AN29" s="14" t="s">
+      <c r="AN29" s="18"/>
+      <c r="AO29" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="AO29" s="2" t="s">
+      <c r="AP29" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AP29" s="2" t="s">
+      <c r="AQ29" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ29" s="2" t="s">
+      <c r="AR29" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AR29" s="2" t="s">
+      <c r="AS29" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AS29" s="3" t="s">
+      <c r="AT29" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AT29" s="4" t="s">
+      <c r="AU29" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:46">
+    <row r="30" spans="2:47">
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
@@ -10312,11 +10324,8 @@
       <c r="AD30" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AF30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG30" s="7" t="s">
-        <v>17</v>
+      <c r="AG30" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AH30" s="7" t="s">
         <v>17</v>
@@ -10330,23 +10339,23 @@
       <c r="AK30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AL30" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM30" s="19" t="s">
+      <c r="AL30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN30" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN30" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="AO30" s="2" t="s">
-        <v>15</v>
+      <c r="AO30" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AP30" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AQ30" s="7" t="s">
-        <v>17</v>
+      <c r="AQ30" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AR30" s="7" t="s">
         <v>17</v>
@@ -10354,11 +10363,14 @@
       <c r="AS30" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AT30" s="11" t="s">
+      <c r="AT30" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU30" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:46">
+    <row r="31" spans="2:47">
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
@@ -10446,9 +10458,6 @@
       <c r="AD31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF31" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AG31" s="5" t="s">
         <v>14</v>
       </c>
@@ -10461,20 +10470,20 @@
       <c r="AJ31" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AK31" s="2" t="s">
-        <v>15</v>
+      <c r="AK31" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AL31" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM31" s="19" t="s">
+      <c r="AM31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN31" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO31" s="6" t="s">
-        <v>16</v>
+      <c r="AO31" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AP31" s="6" t="s">
         <v>16</v>
@@ -10488,11 +10497,14 @@
       <c r="AS31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AT31" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="2:46">
+      <c r="AT31" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AU31" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="32" spans="2:47">
       <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
@@ -10580,33 +10592,30 @@
       <c r="AD32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF32" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="AG32" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AH32" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AI32" s="2" t="s">
-        <v>15</v>
+      <c r="AI32" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AJ32" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK32" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL32" s="11" t="s">
+      <c r="AK32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL32" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM32" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AM32" s="19" t="s">
+      <c r="AN32" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN32" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AO32" s="5" t="s">
         <v>14</v>
       </c>
@@ -10619,14 +10628,17 @@
       <c r="AR32" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS32" s="2" t="s">
-        <v>15</v>
+      <c r="AS32" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AT32" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="33" spans="2:46">
+      <c r="AU32" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="2:47">
       <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
@@ -10714,17 +10726,14 @@
       <c r="AD33" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AF33" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG33" s="2" t="s">
-        <v>15</v>
+      <c r="AG33" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AH33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI33" s="6" t="s">
-        <v>16</v>
+      <c r="AI33" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AJ33" s="6" t="s">
         <v>16</v>
@@ -10732,36 +10741,38 @@
       <c r="AK33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL33" s="12" t="s">
+      <c r="AL33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM33" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AM33" s="19" t="s">
+      <c r="AN33" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN33" s="7" t="s">
-        <v>17</v>
-      </c>
       <c r="AO33" s="7" t="s">
         <v>17</v>
       </c>
       <c r="AP33" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AQ33" s="2" t="s">
-        <v>15</v>
+      <c r="AQ33" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AR33" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT33" s="12" t="s">
+      <c r="AS33" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU33" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:46">
-      <c r="AF34" s="18"/>
+    <row r="34" spans="2:47">
       <c r="AG34" s="18"/>
       <c r="AH34" s="18"/>
       <c r="AI34" s="18"/>
@@ -10776,68 +10787,69 @@
       <c r="AR34" s="18"/>
       <c r="AS34" s="18"/>
       <c r="AT34" s="18"/>
-    </row>
-    <row r="35" spans="2:46">
+      <c r="AU34" s="18"/>
+    </row>
+    <row r="35" spans="2:47">
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="26" t="s">
+      <c r="C35" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="26" t="s">
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="26" t="s">
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="28"/>
+      <c r="N35" s="28"/>
+      <c r="O35" s="28"/>
+      <c r="P35" s="28"/>
+      <c r="Q35" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="27"/>
-      <c r="V35" s="27"/>
-      <c r="W35" s="27"/>
-      <c r="X35" s="26" t="s">
+      <c r="R35" s="28"/>
+      <c r="S35" s="28"/>
+      <c r="T35" s="28"/>
+      <c r="U35" s="28"/>
+      <c r="V35" s="28"/>
+      <c r="W35" s="28"/>
+      <c r="X35" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="Y35" s="27"/>
-      <c r="Z35" s="27"/>
-      <c r="AA35" s="27"/>
-      <c r="AB35" s="27"/>
-      <c r="AC35" s="27"/>
-      <c r="AD35" s="27"/>
-      <c r="AF35" s="26" t="s">
+      <c r="Y35" s="28"/>
+      <c r="Z35" s="28"/>
+      <c r="AA35" s="28"/>
+      <c r="AB35" s="28"/>
+      <c r="AC35" s="28"/>
+      <c r="AD35" s="28"/>
+      <c r="AG35" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="AG35" s="27"/>
-      <c r="AH35" s="27"/>
-      <c r="AI35" s="27"/>
-      <c r="AJ35" s="27"/>
-      <c r="AK35" s="27"/>
-      <c r="AL35" s="27"/>
-      <c r="AM35" s="18"/>
-      <c r="AN35" s="21" t="s">
+      <c r="AH35" s="28"/>
+      <c r="AI35" s="28"/>
+      <c r="AJ35" s="28"/>
+      <c r="AK35" s="28"/>
+      <c r="AL35" s="28"/>
+      <c r="AM35" s="28"/>
+      <c r="AN35" s="18"/>
+      <c r="AO35" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="AO35" s="21"/>
       <c r="AP35" s="21"/>
       <c r="AQ35" s="21"/>
-      <c r="AR35" s="18"/>
+      <c r="AR35" s="21"/>
       <c r="AS35" s="18"/>
       <c r="AT35" s="18"/>
-    </row>
-    <row r="36" spans="2:46" s="17" customFormat="1">
+      <c r="AU35" s="18"/>
+    </row>
+    <row r="36" spans="2:47" s="17" customFormat="1">
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -10923,51 +10935,51 @@
       <c r="AD36" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="AF36" s="2" t="s">
+      <c r="AG36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="AG36" s="2" t="s">
+      <c r="AH36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AH36" s="2" t="s">
+      <c r="AI36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AI36" s="2" t="s">
+      <c r="AJ36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AJ36" s="2" t="s">
+      <c r="AK36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AK36" s="3" t="s">
+      <c r="AL36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AL36" s="4" t="s">
+      <c r="AM36" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AM36" s="18"/>
-      <c r="AN36" s="14" t="s">
+      <c r="AN36" s="18"/>
+      <c r="AO36" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="AO36" s="2" t="s">
+      <c r="AP36" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="AP36" s="2" t="s">
+      <c r="AQ36" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AQ36" s="2" t="s">
+      <c r="AR36" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="AR36" s="2" t="s">
+      <c r="AS36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="AS36" s="3" t="s">
+      <c r="AT36" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="AT36" s="4" t="s">
+      <c r="AU36" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:46">
+    <row r="37" spans="2:47">
       <c r="B37" s="1" t="s">
         <v>67</v>
       </c>
@@ -11055,11 +11067,8 @@
       <c r="AD37" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AF37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG37" s="7" t="s">
-        <v>17</v>
+      <c r="AG37" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AH37" s="7" t="s">
         <v>17</v>
@@ -11073,15 +11082,15 @@
       <c r="AK37" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AL37" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM37" s="19" t="s">
+      <c r="AL37" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM37" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN37" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN37" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AO37" s="5" t="s">
         <v>14</v>
       </c>
@@ -11094,14 +11103,17 @@
       <c r="AR37" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AS37" s="2" t="s">
-        <v>15</v>
+      <c r="AS37" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AT37" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="38" spans="2:46">
+      <c r="AU37" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="2:47">
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
@@ -11189,9 +11201,6 @@
       <c r="AD38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF38" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="AG38" s="5" t="s">
         <v>14</v>
       </c>
@@ -11204,38 +11213,41 @@
       <c r="AJ38" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="AK38" s="2" t="s">
-        <v>15</v>
+      <c r="AK38" s="5" t="s">
+        <v>14</v>
       </c>
       <c r="AL38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AM38" s="19" t="s">
+      <c r="AM38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN38" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN38" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="AO38" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AP38" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AQ38" s="2" t="s">
-        <v>15</v>
+      <c r="AQ38" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AR38" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AS38" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AT38" s="11" t="s">
+      <c r="AS38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AT38" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AU38" s="11" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="2:46">
+    <row r="39" spans="2:47">
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
@@ -11323,41 +11335,38 @@
       <c r="AD39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AF39" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="AG39" s="6" t="s">
         <v>16</v>
       </c>
       <c r="AH39" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AI39" s="2" t="s">
-        <v>15</v>
+      <c r="AI39" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="AJ39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AK39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AL39" s="11" t="s">
+      <c r="AK39" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AM39" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="AM39" s="19" t="s">
+      <c r="AN39" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN39" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="AO39" s="2" t="s">
-        <v>15</v>
+      <c r="AO39" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AP39" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AQ39" s="6" t="s">
-        <v>16</v>
+      <c r="AQ39" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AR39" s="6" t="s">
         <v>16</v>
@@ -11368,8 +11377,11 @@
       <c r="AT39" s="6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="40" spans="2:46">
+      <c r="AU39" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="40" spans="2:47">
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
@@ -11457,17 +11469,14 @@
       <c r="AD40" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AF40" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="AG40" s="2" t="s">
-        <v>15</v>
+      <c r="AG40" s="7" t="s">
+        <v>17</v>
       </c>
       <c r="AH40" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="AI40" s="6" t="s">
-        <v>16</v>
+      <c r="AI40" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AJ40" s="6" t="s">
         <v>16</v>
@@ -11475,17 +11484,17 @@
       <c r="AK40" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="AL40" s="12" t="s">
+      <c r="AL40" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AM40" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="AM40" s="19" t="s">
+      <c r="AN40" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="AN40" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO40" s="7" t="s">
-        <v>17</v>
+      <c r="AO40" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="AP40" s="7" t="s">
         <v>17</v>
@@ -11499,52 +11508,55 @@
       <c r="AS40" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AT40" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="2:46">
+      <c r="AT40" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AU40" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="2:47">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="26" t="s">
+      <c r="C42" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="26" t="s">
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="26" t="s">
+      <c r="K42" s="28"/>
+      <c r="L42" s="28"/>
+      <c r="M42" s="28"/>
+      <c r="N42" s="28"/>
+      <c r="O42" s="28"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="27"/>
-      <c r="U42" s="27"/>
-      <c r="V42" s="27"/>
-      <c r="W42" s="27"/>
-      <c r="X42" s="26" t="s">
+      <c r="R42" s="28"/>
+      <c r="S42" s="28"/>
+      <c r="T42" s="28"/>
+      <c r="U42" s="28"/>
+      <c r="V42" s="28"/>
+      <c r="W42" s="28"/>
+      <c r="X42" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="Y42" s="27"/>
-      <c r="Z42" s="27"/>
-      <c r="AA42" s="27"/>
-      <c r="AB42" s="27"/>
-      <c r="AC42" s="27"/>
-      <c r="AD42" s="27"/>
-    </row>
-    <row r="43" spans="2:46">
+      <c r="Y42" s="28"/>
+      <c r="Z42" s="28"/>
+      <c r="AA42" s="28"/>
+      <c r="AB42" s="28"/>
+      <c r="AC42" s="28"/>
+      <c r="AD42" s="28"/>
+    </row>
+    <row r="43" spans="2:47">
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
         <v>82</v>
@@ -11631,7 +11643,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:46">
+    <row r="44" spans="2:47">
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
@@ -11720,7 +11732,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:46">
+    <row r="45" spans="2:47">
       <c r="B45" s="1" t="s">
         <v>68</v>
       </c>
@@ -11809,7 +11821,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:46">
+    <row r="46" spans="2:47">
       <c r="B46" s="1" t="s">
         <v>69</v>
       </c>
@@ -11898,7 +11910,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:46">
+    <row r="47" spans="2:47">
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
@@ -11988,78 +12000,78 @@
       </c>
     </row>
     <row r="49" spans="2:30">
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
-      <c r="AA49" s="29"/>
-      <c r="AB49" s="29"/>
-      <c r="AC49" s="29"/>
-      <c r="AD49" s="29"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
+      <c r="AA49" s="30"/>
+      <c r="AB49" s="30"/>
+      <c r="AC49" s="30"/>
+      <c r="AD49" s="30"/>
     </row>
     <row r="50" spans="2:30">
       <c r="B50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="26" t="s">
+      <c r="C50" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="27"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="27"/>
-      <c r="G50" s="27"/>
-      <c r="H50" s="27"/>
-      <c r="I50" s="27"/>
-      <c r="J50" s="26" t="s">
+      <c r="D50" s="28"/>
+      <c r="E50" s="28"/>
+      <c r="F50" s="28"/>
+      <c r="G50" s="28"/>
+      <c r="H50" s="28"/>
+      <c r="I50" s="28"/>
+      <c r="J50" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
-      <c r="N50" s="27"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="27"/>
-      <c r="Q50" s="26" t="s">
+      <c r="K50" s="28"/>
+      <c r="L50" s="28"/>
+      <c r="M50" s="28"/>
+      <c r="N50" s="28"/>
+      <c r="O50" s="28"/>
+      <c r="P50" s="28"/>
+      <c r="Q50" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="27"/>
-      <c r="S50" s="27"/>
-      <c r="T50" s="27"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="27"/>
-      <c r="W50" s="27"/>
-      <c r="X50" s="26" t="s">
+      <c r="R50" s="28"/>
+      <c r="S50" s="28"/>
+      <c r="T50" s="28"/>
+      <c r="U50" s="28"/>
+      <c r="V50" s="28"/>
+      <c r="W50" s="28"/>
+      <c r="X50" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="Y50" s="27"/>
-      <c r="Z50" s="27"/>
-      <c r="AA50" s="27"/>
-      <c r="AB50" s="27"/>
-      <c r="AC50" s="27"/>
-      <c r="AD50" s="27"/>
+      <c r="Y50" s="28"/>
+      <c r="Z50" s="28"/>
+      <c r="AA50" s="28"/>
+      <c r="AB50" s="28"/>
+      <c r="AC50" s="28"/>
+      <c r="AD50" s="28"/>
     </row>
     <row r="51" spans="2:30">
       <c r="B51" s="1"/>
@@ -12508,42 +12520,42 @@
       <c r="B57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="26" t="s">
+      <c r="C57" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="27"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="27"/>
-      <c r="G57" s="27"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="27"/>
-      <c r="J57" s="26" t="s">
+      <c r="D57" s="28"/>
+      <c r="E57" s="28"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="27"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="27"/>
-      <c r="N57" s="27"/>
-      <c r="O57" s="27"/>
-      <c r="P57" s="27"/>
-      <c r="Q57" s="26" t="s">
+      <c r="K57" s="28"/>
+      <c r="L57" s="28"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="28"/>
+      <c r="P57" s="28"/>
+      <c r="Q57" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="R57" s="27"/>
-      <c r="S57" s="27"/>
-      <c r="T57" s="27"/>
-      <c r="U57" s="27"/>
-      <c r="V57" s="27"/>
-      <c r="W57" s="27"/>
-      <c r="X57" s="26" t="s">
+      <c r="R57" s="28"/>
+      <c r="S57" s="28"/>
+      <c r="T57" s="28"/>
+      <c r="U57" s="28"/>
+      <c r="V57" s="28"/>
+      <c r="W57" s="28"/>
+      <c r="X57" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="Y57" s="27"/>
-      <c r="Z57" s="27"/>
-      <c r="AA57" s="27"/>
-      <c r="AB57" s="27"/>
-      <c r="AC57" s="27"/>
-      <c r="AD57" s="27"/>
+      <c r="Y57" s="28"/>
+      <c r="Z57" s="28"/>
+      <c r="AA57" s="28"/>
+      <c r="AB57" s="28"/>
+      <c r="AC57" s="28"/>
+      <c r="AD57" s="28"/>
     </row>
     <row r="58" spans="2:30">
       <c r="B58" s="1"/>
@@ -12992,42 +13004,42 @@
       <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="26" t="s">
+      <c r="C64" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="26" t="s">
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="26" t="s">
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="26" t="s">
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
-      <c r="AC64" s="27"/>
-      <c r="AD64" s="27"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
+      <c r="AC64" s="28"/>
+      <c r="AD64" s="28"/>
     </row>
     <row r="65" spans="2:30">
       <c r="B65" s="1"/>
@@ -13473,78 +13485,78 @@
       </c>
     </row>
     <row r="71" spans="2:30">
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="29"/>
-      <c r="I71" s="29"/>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
-      <c r="O71" s="29"/>
-      <c r="P71" s="29"/>
-      <c r="Q71" s="29"/>
-      <c r="R71" s="29"/>
-      <c r="S71" s="29"/>
-      <c r="T71" s="29"/>
-      <c r="U71" s="29"/>
-      <c r="V71" s="29"/>
-      <c r="W71" s="29"/>
-      <c r="X71" s="29"/>
-      <c r="Y71" s="29"/>
-      <c r="Z71" s="29"/>
-      <c r="AA71" s="29"/>
-      <c r="AB71" s="29"/>
-      <c r="AC71" s="29"/>
-      <c r="AD71" s="29"/>
+      <c r="C71" s="30"/>
+      <c r="D71" s="30"/>
+      <c r="E71" s="30"/>
+      <c r="F71" s="30"/>
+      <c r="G71" s="30"/>
+      <c r="H71" s="30"/>
+      <c r="I71" s="30"/>
+      <c r="J71" s="30"/>
+      <c r="K71" s="30"/>
+      <c r="L71" s="30"/>
+      <c r="M71" s="30"/>
+      <c r="N71" s="30"/>
+      <c r="O71" s="30"/>
+      <c r="P71" s="30"/>
+      <c r="Q71" s="30"/>
+      <c r="R71" s="30"/>
+      <c r="S71" s="30"/>
+      <c r="T71" s="30"/>
+      <c r="U71" s="30"/>
+      <c r="V71" s="30"/>
+      <c r="W71" s="30"/>
+      <c r="X71" s="30"/>
+      <c r="Y71" s="30"/>
+      <c r="Z71" s="30"/>
+      <c r="AA71" s="30"/>
+      <c r="AB71" s="30"/>
+      <c r="AC71" s="30"/>
+      <c r="AD71" s="30"/>
     </row>
     <row r="72" spans="2:30">
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="26" t="s">
+      <c r="C72" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="26" t="s">
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28"/>
+      <c r="H72" s="28"/>
+      <c r="I72" s="28"/>
+      <c r="J72" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="K72" s="27"/>
-      <c r="L72" s="27"/>
-      <c r="M72" s="27"/>
-      <c r="N72" s="27"/>
-      <c r="O72" s="27"/>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="26" t="s">
+      <c r="K72" s="28"/>
+      <c r="L72" s="28"/>
+      <c r="M72" s="28"/>
+      <c r="N72" s="28"/>
+      <c r="O72" s="28"/>
+      <c r="P72" s="28"/>
+      <c r="Q72" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="R72" s="27"/>
-      <c r="S72" s="27"/>
-      <c r="T72" s="27"/>
-      <c r="U72" s="27"/>
-      <c r="V72" s="27"/>
-      <c r="W72" s="27"/>
-      <c r="X72" s="26" t="s">
+      <c r="R72" s="28"/>
+      <c r="S72" s="28"/>
+      <c r="T72" s="28"/>
+      <c r="U72" s="28"/>
+      <c r="V72" s="28"/>
+      <c r="W72" s="28"/>
+      <c r="X72" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="Y72" s="27"/>
-      <c r="Z72" s="27"/>
-      <c r="AA72" s="27"/>
-      <c r="AB72" s="27"/>
-      <c r="AC72" s="27"/>
-      <c r="AD72" s="27"/>
+      <c r="Y72" s="28"/>
+      <c r="Z72" s="28"/>
+      <c r="AA72" s="28"/>
+      <c r="AB72" s="28"/>
+      <c r="AC72" s="28"/>
+      <c r="AD72" s="28"/>
     </row>
     <row r="73" spans="2:30">
       <c r="B73" s="1"/>
@@ -13993,42 +14005,42 @@
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="26" t="s">
+      <c r="C79" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="26" t="s">
+      <c r="D79" s="28"/>
+      <c r="E79" s="28"/>
+      <c r="F79" s="28"/>
+      <c r="G79" s="28"/>
+      <c r="H79" s="28"/>
+      <c r="I79" s="28"/>
+      <c r="J79" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-      <c r="M79" s="27"/>
-      <c r="N79" s="27"/>
-      <c r="O79" s="27"/>
-      <c r="P79" s="27"/>
-      <c r="Q79" s="26" t="s">
+      <c r="K79" s="28"/>
+      <c r="L79" s="28"/>
+      <c r="M79" s="28"/>
+      <c r="N79" s="28"/>
+      <c r="O79" s="28"/>
+      <c r="P79" s="28"/>
+      <c r="Q79" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="R79" s="27"/>
-      <c r="S79" s="27"/>
-      <c r="T79" s="27"/>
-      <c r="U79" s="27"/>
-      <c r="V79" s="27"/>
-      <c r="W79" s="27"/>
-      <c r="X79" s="26" t="s">
+      <c r="R79" s="28"/>
+      <c r="S79" s="28"/>
+      <c r="T79" s="28"/>
+      <c r="U79" s="28"/>
+      <c r="V79" s="28"/>
+      <c r="W79" s="28"/>
+      <c r="X79" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="Y79" s="27"/>
-      <c r="Z79" s="27"/>
-      <c r="AA79" s="27"/>
-      <c r="AB79" s="27"/>
-      <c r="AC79" s="27"/>
-      <c r="AD79" s="27"/>
+      <c r="Y79" s="28"/>
+      <c r="Z79" s="28"/>
+      <c r="AA79" s="28"/>
+      <c r="AB79" s="28"/>
+      <c r="AC79" s="28"/>
+      <c r="AD79" s="28"/>
     </row>
     <row r="80" spans="2:30">
       <c r="B80" s="1"/>
@@ -14477,42 +14489,42 @@
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="26" t="s">
+      <c r="C86" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
-      <c r="J86" s="26" t="s">
+      <c r="D86" s="28"/>
+      <c r="E86" s="28"/>
+      <c r="F86" s="28"/>
+      <c r="G86" s="28"/>
+      <c r="H86" s="28"/>
+      <c r="I86" s="28"/>
+      <c r="J86" s="27" t="s">
         <v>62</v>
       </c>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-      <c r="M86" s="27"/>
-      <c r="N86" s="27"/>
-      <c r="O86" s="27"/>
-      <c r="P86" s="27"/>
-      <c r="Q86" s="26" t="s">
+      <c r="K86" s="28"/>
+      <c r="L86" s="28"/>
+      <c r="M86" s="28"/>
+      <c r="N86" s="28"/>
+      <c r="O86" s="28"/>
+      <c r="P86" s="28"/>
+      <c r="Q86" s="27" t="s">
         <v>63</v>
       </c>
-      <c r="R86" s="27"/>
-      <c r="S86" s="27"/>
-      <c r="T86" s="27"/>
-      <c r="U86" s="27"/>
-      <c r="V86" s="27"/>
-      <c r="W86" s="27"/>
-      <c r="X86" s="26" t="s">
+      <c r="R86" s="28"/>
+      <c r="S86" s="28"/>
+      <c r="T86" s="28"/>
+      <c r="U86" s="28"/>
+      <c r="V86" s="28"/>
+      <c r="W86" s="28"/>
+      <c r="X86" s="27" t="s">
         <v>64</v>
       </c>
-      <c r="Y86" s="27"/>
-      <c r="Z86" s="27"/>
-      <c r="AA86" s="27"/>
-      <c r="AB86" s="27"/>
-      <c r="AC86" s="27"/>
-      <c r="AD86" s="27"/>
+      <c r="Y86" s="28"/>
+      <c r="Z86" s="28"/>
+      <c r="AA86" s="28"/>
+      <c r="AB86" s="28"/>
+      <c r="AC86" s="28"/>
+      <c r="AD86" s="28"/>
     </row>
     <row r="87" spans="2:30">
       <c r="B87" s="1"/>
@@ -14959,43 +14971,11 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="B71:AD71"/>
-    <mergeCell ref="C42:I42"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="X86:AD86"/>
-    <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="X79:AD79"/>
-    <mergeCell ref="Q79:W79"/>
-    <mergeCell ref="Q72:W72"/>
-    <mergeCell ref="B5:AD5"/>
-    <mergeCell ref="J64:P64"/>
-    <mergeCell ref="X72:AD72"/>
-    <mergeCell ref="X57:AD57"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="X35:AD35"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="J79:P79"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="Q86:W86"/>
-    <mergeCell ref="Q35:W35"/>
-    <mergeCell ref="C50:I50"/>
-    <mergeCell ref="J72:P72"/>
-    <mergeCell ref="C79:I79"/>
-    <mergeCell ref="J42:P42"/>
-    <mergeCell ref="C64:I64"/>
-    <mergeCell ref="Q64:W64"/>
-    <mergeCell ref="Q57:W57"/>
-    <mergeCell ref="J86:P86"/>
-    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="AG28:AM28"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="AG20:AM20"/>
+    <mergeCell ref="AG13:AM13"/>
+    <mergeCell ref="X13:AD13"/>
     <mergeCell ref="J6:P6"/>
     <mergeCell ref="X64:AD64"/>
     <mergeCell ref="X42:AD42"/>
@@ -15010,14 +14990,47 @@
     <mergeCell ref="B27:AD27"/>
     <mergeCell ref="J20:P20"/>
     <mergeCell ref="C6:I6"/>
-    <mergeCell ref="AF28:AL28"/>
-    <mergeCell ref="AF35:AL35"/>
-    <mergeCell ref="AF20:AL20"/>
-    <mergeCell ref="AF13:AL13"/>
-    <mergeCell ref="X13:AD13"/>
+    <mergeCell ref="Q35:W35"/>
+    <mergeCell ref="C50:I50"/>
+    <mergeCell ref="J72:P72"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="J42:P42"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="Q64:W64"/>
+    <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B5:AD5"/>
+    <mergeCell ref="J64:P64"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="X57:AD57"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="X35:AD35"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="J35:P35"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="B71:AD71"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="Q42:W42"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="X79:AD79"/>
+    <mergeCell ref="Q79:W79"/>
+    <mergeCell ref="Q72:W72"/>
+    <mergeCell ref="J79:P79"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="Q86:W86"/>
+    <mergeCell ref="J86:P86"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
+  <pageSetup paperSize="8" scale="88" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/배차작업/근무조편성/본사_배차원_48주.xlsx
+++ b/배차작업/근무조편성/본사_배차원_48주.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="816" yWindow="876" windowWidth="33120" windowHeight="12048" activeTab="1"/>
+    <workbookView xWindow="810" yWindow="870" windowWidth="33120" windowHeight="12045" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="근무표 인쇄용" sheetId="2" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4198" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4646" uniqueCount="100">
   <si>
     <t>※ 주간 전담 순서: 1. 차현철 → 2. 진영만 → 3. 박원호 → 4. 한원석 (12주 단위 / 한 줄에 4주씩 배치)</t>
   </si>
@@ -343,12 +343,20 @@
     <t>전주</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>■ 5차 순환 주기 (49주 ~ 60주차)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>월</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="15">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,7 +607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -661,14 +669,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -976,92 +985,92 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B2:AT88"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.3984375" style="22" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" style="22" customWidth="1"/>
+    <col min="1" max="1" width="1.375" style="22" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="22" customWidth="1"/>
     <col min="3" max="30" width="7" style="22" customWidth="1"/>
-    <col min="31" max="31" width="1.09765625" style="22" customWidth="1"/>
-    <col min="32" max="16384" width="8.69921875" style="22"/>
+    <col min="31" max="31" width="1.125" style="22" customWidth="1"/>
+    <col min="32" max="16384" width="8.75" style="22"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="30"/>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="30"/>
-      <c r="M2" s="30"/>
-      <c r="N2" s="30"/>
-      <c r="O2" s="30"/>
-      <c r="P2" s="30"/>
-      <c r="Q2" s="30"/>
-      <c r="R2" s="30"/>
-      <c r="S2" s="30"/>
-      <c r="T2" s="30"/>
-      <c r="U2" s="30"/>
-      <c r="V2" s="30"/>
-      <c r="W2" s="30"/>
-      <c r="X2" s="30"/>
-      <c r="Y2" s="30"/>
-      <c r="Z2" s="30"/>
-      <c r="AA2" s="30"/>
-      <c r="AB2" s="30"/>
-      <c r="AC2" s="30"/>
-      <c r="AD2" s="30"/>
-    </row>
-    <row r="3" spans="2:46">
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+      <c r="M2" s="29"/>
+      <c r="N2" s="29"/>
+      <c r="O2" s="29"/>
+      <c r="P2" s="29"/>
+      <c r="Q2" s="29"/>
+      <c r="R2" s="29"/>
+      <c r="S2" s="29"/>
+      <c r="T2" s="29"/>
+      <c r="U2" s="29"/>
+      <c r="V2" s="29"/>
+      <c r="W2" s="29"/>
+      <c r="X2" s="29"/>
+      <c r="Y2" s="29"/>
+      <c r="Z2" s="29"/>
+      <c r="AA2" s="29"/>
+      <c r="AB2" s="29"/>
+      <c r="AC2" s="29"/>
+      <c r="AD2" s="29"/>
+    </row>
+    <row r="3" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="27" t="s">
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="28"/>
-      <c r="L3" s="28"/>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="27" t="s">
+      <c r="K3" s="31"/>
+      <c r="L3" s="31"/>
+      <c r="M3" s="31"/>
+      <c r="N3" s="31"/>
+      <c r="O3" s="31"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
-      <c r="V3" s="28"/>
-      <c r="W3" s="28"/>
-      <c r="X3" s="27" t="s">
+      <c r="R3" s="31"/>
+      <c r="S3" s="31"/>
+      <c r="T3" s="31"/>
+      <c r="U3" s="31"/>
+      <c r="V3" s="31"/>
+      <c r="W3" s="31"/>
+      <c r="X3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="Y3" s="28"/>
-      <c r="Z3" s="28"/>
-      <c r="AA3" s="28"/>
-      <c r="AB3" s="28"/>
-      <c r="AC3" s="28"/>
-      <c r="AD3" s="28"/>
-    </row>
-    <row r="4" spans="2:46">
+      <c r="Y3" s="31"/>
+      <c r="Z3" s="31"/>
+      <c r="AA3" s="31"/>
+      <c r="AB3" s="31"/>
+      <c r="AC3" s="31"/>
+      <c r="AD3" s="31"/>
+    </row>
+    <row r="4" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B4" s="1"/>
       <c r="C4" s="2" t="s">
         <v>75</v>
@@ -1148,7 +1157,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:46">
+    <row r="5" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
@@ -1237,7 +1246,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:46">
+    <row r="6" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>68</v>
       </c>
@@ -1326,7 +1335,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="2:46">
+    <row r="7" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -1415,7 +1424,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="8" spans="2:46">
+    <row r="8" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>70</v>
       </c>
@@ -1504,7 +1513,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="2:46" hidden="1">
+    <row r="9" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="AN9" s="20" t="s">
         <v>96</v>
       </c>
@@ -1512,55 +1521,55 @@
       <c r="AP9" s="20"/>
       <c r="AQ9" s="20"/>
     </row>
-    <row r="10" spans="2:46" hidden="1">
+    <row r="10" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="31" t="s">
+      <c r="C10" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="31" t="s">
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="33"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="32"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="33"/>
-      <c r="Q10" s="31" t="s">
+      <c r="K10" s="33"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="34"/>
+      <c r="Q10" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="R10" s="32"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="32"/>
-      <c r="U10" s="32"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="31" t="s">
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="33"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="34"/>
+      <c r="X10" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="32"/>
-      <c r="AA10" s="32"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="32"/>
-      <c r="AD10" s="33"/>
-      <c r="AF10" s="31" t="s">
+      <c r="Y10" s="33"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="33"/>
+      <c r="AB10" s="33"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="34"/>
+      <c r="AF10" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AG10" s="32"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="32"/>
-      <c r="AJ10" s="32"/>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="33"/>
+      <c r="AG10" s="33"/>
+      <c r="AH10" s="33"/>
+      <c r="AI10" s="33"/>
+      <c r="AJ10" s="33"/>
+      <c r="AK10" s="33"/>
+      <c r="AL10" s="34"/>
       <c r="AN10" s="21" t="s">
         <v>90</v>
       </c>
@@ -1568,7 +1577,7 @@
       <c r="AP10" s="21"/>
       <c r="AQ10" s="21"/>
     </row>
-    <row r="11" spans="2:46" hidden="1">
+    <row r="11" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B11" s="1"/>
       <c r="C11" s="2" t="s">
         <v>78</v>
@@ -1697,7 +1706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="2:46">
+    <row r="12" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
         <v>67</v>
       </c>
@@ -1832,7 +1841,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="13" spans="2:46">
+    <row r="13" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>68</v>
       </c>
@@ -1967,7 +1976,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="2:46">
+    <row r="14" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
         <v>69</v>
       </c>
@@ -2102,7 +2111,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="2:46">
+    <row r="15" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>70</v>
       </c>
@@ -2237,56 +2246,56 @@
         <v>65</v>
       </c>
     </row>
-    <row r="16" spans="2:46" hidden="1"/>
-    <row r="17" spans="2:46" hidden="1">
+    <row r="16" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="32"/>
-      <c r="G17" s="32"/>
-      <c r="H17" s="32"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="31" t="s">
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="32"/>
-      <c r="M17" s="32"/>
-      <c r="N17" s="32"/>
-      <c r="O17" s="32"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="31" t="s">
+      <c r="K17" s="33"/>
+      <c r="L17" s="33"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="32" t="s">
         <v>24</v>
       </c>
-      <c r="R17" s="32"/>
-      <c r="S17" s="32"/>
-      <c r="T17" s="32"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="31" t="s">
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="33"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="34"/>
+      <c r="X17" s="32" t="s">
         <v>25</v>
       </c>
-      <c r="Y17" s="32"/>
-      <c r="Z17" s="32"/>
-      <c r="AA17" s="32"/>
-      <c r="AB17" s="32"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="33"/>
-      <c r="AF17" s="31" t="s">
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="33"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="34"/>
+      <c r="AF17" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AG17" s="32"/>
-      <c r="AH17" s="32"/>
-      <c r="AI17" s="32"/>
-      <c r="AJ17" s="32"/>
-      <c r="AK17" s="32"/>
-      <c r="AL17" s="33"/>
+      <c r="AG17" s="33"/>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="33"/>
+      <c r="AK17" s="33"/>
+      <c r="AL17" s="34"/>
       <c r="AN17" s="21" t="s">
         <v>91</v>
       </c>
@@ -2294,7 +2303,7 @@
       <c r="AP17" s="21"/>
       <c r="AQ17" s="21"/>
     </row>
-    <row r="18" spans="2:46" hidden="1">
+    <row r="18" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B18" s="1"/>
       <c r="C18" s="2" t="s">
         <v>79</v>
@@ -2423,7 +2432,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="2:46">
+    <row r="19" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
         <v>67</v>
       </c>
@@ -2558,7 +2567,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:46">
+    <row r="20" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>68</v>
       </c>
@@ -2693,7 +2702,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="21" spans="2:46">
+    <row r="21" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
         <v>69</v>
       </c>
@@ -2828,7 +2837,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="2:46">
+    <row r="22" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>70</v>
       </c>
@@ -2963,39 +2972,39 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:46" hidden="1"/>
-    <row r="24" spans="2:46">
-      <c r="B24" s="29" t="s">
+    <row r="23" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B24" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
-      <c r="K24" s="30"/>
-      <c r="L24" s="30"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="30"/>
-      <c r="O24" s="30"/>
-      <c r="P24" s="30"/>
-      <c r="Q24" s="30"/>
-      <c r="R24" s="30"/>
-      <c r="S24" s="30"/>
-      <c r="T24" s="30"/>
-      <c r="U24" s="30"/>
-      <c r="V24" s="30"/>
-      <c r="W24" s="30"/>
-      <c r="X24" s="30"/>
-      <c r="Y24" s="30"/>
-      <c r="Z24" s="30"/>
-      <c r="AA24" s="30"/>
-      <c r="AB24" s="30"/>
-      <c r="AC24" s="30"/>
-      <c r="AD24" s="30"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
+      <c r="N24" s="29"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="29"/>
+      <c r="Q24" s="29"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="29"/>
+      <c r="T24" s="29"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="29"/>
+      <c r="W24" s="29"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="29"/>
+      <c r="Z24" s="29"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="29"/>
+      <c r="AC24" s="29"/>
+      <c r="AD24" s="29"/>
       <c r="AN24" s="20" t="s">
         <v>95</v>
       </c>
@@ -3003,55 +3012,55 @@
       <c r="AP24" s="20"/>
       <c r="AQ24" s="20"/>
     </row>
-    <row r="25" spans="2:46">
+    <row r="25" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="27" t="s">
+      <c r="D25" s="31"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="28"/>
-      <c r="Q25" s="27" t="s">
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="R25" s="28"/>
-      <c r="S25" s="28"/>
-      <c r="T25" s="28"/>
-      <c r="U25" s="28"/>
-      <c r="V25" s="28"/>
-      <c r="W25" s="28"/>
-      <c r="X25" s="27" t="s">
+      <c r="R25" s="31"/>
+      <c r="S25" s="31"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="Y25" s="28"/>
-      <c r="Z25" s="28"/>
-      <c r="AA25" s="28"/>
-      <c r="AB25" s="28"/>
-      <c r="AC25" s="28"/>
-      <c r="AD25" s="28"/>
-      <c r="AF25" s="27" t="s">
+      <c r="Y25" s="31"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="31"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="31"/>
+      <c r="AF25" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AG25" s="28"/>
-      <c r="AH25" s="28"/>
-      <c r="AI25" s="28"/>
-      <c r="AJ25" s="28"/>
-      <c r="AK25" s="28"/>
-      <c r="AL25" s="28"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="31"/>
+      <c r="AL25" s="31"/>
       <c r="AN25" s="21" t="s">
         <v>90</v>
       </c>
@@ -3059,7 +3068,7 @@
       <c r="AP25" s="21"/>
       <c r="AQ25" s="21"/>
     </row>
-    <row r="26" spans="2:46">
+    <row r="26" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B26" s="1"/>
       <c r="C26" s="14" t="s">
         <v>80</v>
@@ -3188,7 +3197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="27" spans="2:46">
+    <row r="27" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
         <v>67</v>
       </c>
@@ -3322,7 +3331,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="2:46">
+    <row r="28" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>68</v>
       </c>
@@ -3456,7 +3465,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="29" spans="2:46">
+    <row r="29" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
         <v>69</v>
       </c>
@@ -3590,7 +3599,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="30" spans="2:46">
+    <row r="30" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>70</v>
       </c>
@@ -3724,56 +3733,56 @@
         <v>66</v>
       </c>
     </row>
-    <row r="31" spans="2:46" hidden="1"/>
-    <row r="32" spans="2:46" hidden="1">
+    <row r="31" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="D32" s="32"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="32"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="31" t="s">
+      <c r="D32" s="33"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="K32" s="32"/>
-      <c r="L32" s="32"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
-      <c r="O32" s="32"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="31" t="s">
+      <c r="K32" s="33"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="R32" s="32"/>
-      <c r="S32" s="32"/>
-      <c r="T32" s="32"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="31" t="s">
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+      <c r="T32" s="33"/>
+      <c r="U32" s="33"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="Y32" s="32"/>
-      <c r="Z32" s="32"/>
-      <c r="AA32" s="32"/>
-      <c r="AB32" s="32"/>
-      <c r="AC32" s="32"/>
-      <c r="AD32" s="33"/>
-      <c r="AF32" s="31" t="s">
+      <c r="Y32" s="33"/>
+      <c r="Z32" s="33"/>
+      <c r="AA32" s="33"/>
+      <c r="AB32" s="33"/>
+      <c r="AC32" s="33"/>
+      <c r="AD32" s="34"/>
+      <c r="AF32" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AG32" s="32"/>
-      <c r="AH32" s="32"/>
-      <c r="AI32" s="32"/>
-      <c r="AJ32" s="32"/>
-      <c r="AK32" s="32"/>
-      <c r="AL32" s="33"/>
+      <c r="AG32" s="33"/>
+      <c r="AH32" s="33"/>
+      <c r="AI32" s="33"/>
+      <c r="AJ32" s="33"/>
+      <c r="AK32" s="33"/>
+      <c r="AL32" s="34"/>
       <c r="AN32" s="21" t="s">
         <v>91</v>
       </c>
@@ -3781,7 +3790,7 @@
       <c r="AP32" s="21"/>
       <c r="AQ32" s="21"/>
     </row>
-    <row r="33" spans="2:46" s="17" customFormat="1" hidden="1">
+    <row r="33" spans="2:46" s="17" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="s">
         <v>81</v>
@@ -3911,7 +3920,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="2:46">
+    <row r="34" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>67</v>
       </c>
@@ -4045,7 +4054,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="2:46">
+    <row r="35" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>68</v>
       </c>
@@ -4179,7 +4188,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="2:46">
+    <row r="36" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
         <v>69</v>
       </c>
@@ -4313,7 +4322,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="37" spans="2:46">
+    <row r="37" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>70</v>
       </c>
@@ -4447,49 +4456,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:46" hidden="1"/>
-    <row r="39" spans="2:46" hidden="1">
+    <row r="38" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="31" t="s">
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
-      <c r="N39" s="32"/>
-      <c r="O39" s="32"/>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="31" t="s">
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="32" t="s">
         <v>37</v>
       </c>
-      <c r="R39" s="32"/>
-      <c r="S39" s="32"/>
-      <c r="T39" s="32"/>
-      <c r="U39" s="32"/>
-      <c r="V39" s="32"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="31" t="s">
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="33"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="34"/>
+      <c r="X39" s="32" t="s">
         <v>38</v>
       </c>
-      <c r="Y39" s="32"/>
-      <c r="Z39" s="32"/>
-      <c r="AA39" s="32"/>
-      <c r="AB39" s="32"/>
-      <c r="AC39" s="32"/>
-      <c r="AD39" s="33"/>
-    </row>
-    <row r="40" spans="2:46" hidden="1">
+      <c r="Y39" s="33"/>
+      <c r="Z39" s="33"/>
+      <c r="AA39" s="33"/>
+      <c r="AB39" s="33"/>
+      <c r="AC39" s="33"/>
+      <c r="AD39" s="34"/>
+    </row>
+    <row r="40" spans="2:46" hidden="1" x14ac:dyDescent="0.25">
       <c r="B40" s="1"/>
       <c r="C40" s="14" t="s">
         <v>82</v>
@@ -4576,7 +4585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="2:46">
+    <row r="41" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
         <v>67</v>
       </c>
@@ -4665,7 +4674,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="2:46">
+    <row r="42" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>68</v>
       </c>
@@ -4754,7 +4763,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="43" spans="2:46">
+    <row r="43" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B43" s="1" t="s">
         <v>69</v>
       </c>
@@ -4843,7 +4852,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="44" spans="2:46">
+    <row r="44" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>70</v>
       </c>
@@ -4932,82 +4941,82 @@
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="2:46" hidden="1"/>
-    <row r="46" spans="2:46">
-      <c r="B46" s="29" t="s">
+    <row r="45" spans="2:46" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="46" spans="2:46" x14ac:dyDescent="0.25">
+      <c r="B46" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
-      <c r="AA46" s="30"/>
-      <c r="AB46" s="30"/>
-      <c r="AC46" s="30"/>
-      <c r="AD46" s="30"/>
-    </row>
-    <row r="47" spans="2:46">
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29"/>
+      <c r="AC46" s="29"/>
+      <c r="AD46" s="29"/>
+    </row>
+    <row r="47" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="27" t="s">
+      <c r="C47" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="27" t="s">
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="28"/>
-      <c r="P47" s="28"/>
-      <c r="Q47" s="27" t="s">
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="R47" s="28"/>
-      <c r="S47" s="28"/>
-      <c r="T47" s="28"/>
-      <c r="U47" s="28"/>
-      <c r="V47" s="28"/>
-      <c r="W47" s="28"/>
-      <c r="X47" s="27" t="s">
+      <c r="R47" s="31"/>
+      <c r="S47" s="31"/>
+      <c r="T47" s="31"/>
+      <c r="U47" s="31"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="31"/>
+      <c r="X47" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="Y47" s="28"/>
-      <c r="Z47" s="28"/>
-      <c r="AA47" s="28"/>
-      <c r="AB47" s="28"/>
-      <c r="AC47" s="28"/>
-      <c r="AD47" s="28"/>
-    </row>
-    <row r="48" spans="2:46">
+      <c r="Y47" s="31"/>
+      <c r="Z47" s="31"/>
+      <c r="AA47" s="31"/>
+      <c r="AB47" s="31"/>
+      <c r="AC47" s="31"/>
+      <c r="AD47" s="31"/>
+    </row>
+    <row r="48" spans="2:46" x14ac:dyDescent="0.25">
       <c r="B48" s="1"/>
       <c r="C48" s="2" t="s">
         <v>83</v>
@@ -5094,7 +5103,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="2:30">
+    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B49" s="1" t="s">
         <v>67</v>
       </c>
@@ -5183,7 +5192,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="50" spans="2:30">
+    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>68</v>
       </c>
@@ -5272,7 +5281,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="51" spans="2:30">
+    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
         <v>69</v>
       </c>
@@ -5361,7 +5370,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="52" spans="2:30">
+    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>70</v>
       </c>
@@ -5450,49 +5459,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="53" spans="2:30" hidden="1"/>
-    <row r="54" spans="2:30" hidden="1">
+    <row r="53" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C54" s="27" t="s">
+      <c r="C54" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D54" s="28"/>
-      <c r="E54" s="28"/>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="27" t="s">
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="K54" s="28"/>
-      <c r="L54" s="28"/>
-      <c r="M54" s="28"/>
-      <c r="N54" s="28"/>
-      <c r="O54" s="28"/>
-      <c r="P54" s="28"/>
-      <c r="Q54" s="27" t="s">
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="R54" s="28"/>
-      <c r="S54" s="28"/>
-      <c r="T54" s="28"/>
-      <c r="U54" s="28"/>
-      <c r="V54" s="28"/>
-      <c r="W54" s="28"/>
-      <c r="X54" s="27" t="s">
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+      <c r="U54" s="31"/>
+      <c r="V54" s="31"/>
+      <c r="W54" s="31"/>
+      <c r="X54" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="Y54" s="28"/>
-      <c r="Z54" s="28"/>
-      <c r="AA54" s="28"/>
-      <c r="AB54" s="28"/>
-      <c r="AC54" s="28"/>
-      <c r="AD54" s="28"/>
-    </row>
-    <row r="55" spans="2:30" hidden="1">
+      <c r="Y54" s="31"/>
+      <c r="Z54" s="31"/>
+      <c r="AA54" s="31"/>
+      <c r="AB54" s="31"/>
+      <c r="AC54" s="31"/>
+      <c r="AD54" s="31"/>
+    </row>
+    <row r="55" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B55" s="1"/>
       <c r="C55" s="2" t="s">
         <v>84</v>
@@ -5579,7 +5588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="2:30">
+    <row r="56" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
         <v>67</v>
       </c>
@@ -5668,7 +5677,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="57" spans="2:30">
+    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>68</v>
       </c>
@@ -5757,7 +5766,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="2:30">
+    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
         <v>69</v>
       </c>
@@ -5846,7 +5855,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="59" spans="2:30">
+    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>70</v>
       </c>
@@ -5935,49 +5944,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="60" spans="2:30" hidden="1"/>
-    <row r="61" spans="2:30" hidden="1">
+    <row r="60" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C61" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="27" t="s">
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="27" t="s">
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="27" t="s">
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
-      <c r="AA61" s="28"/>
-      <c r="AB61" s="28"/>
-      <c r="AC61" s="28"/>
-      <c r="AD61" s="28"/>
-    </row>
-    <row r="62" spans="2:30" hidden="1">
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
+      <c r="AA61" s="31"/>
+      <c r="AB61" s="31"/>
+      <c r="AC61" s="31"/>
+      <c r="AD61" s="31"/>
+    </row>
+    <row r="62" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B62" s="1"/>
       <c r="C62" s="2" t="s">
         <v>86</v>
@@ -6064,7 +6073,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="63" spans="2:30">
+    <row r="63" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
         <v>67</v>
       </c>
@@ -6153,7 +6162,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="2:30">
+    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>68</v>
       </c>
@@ -6242,7 +6251,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="65" spans="2:30">
+    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
         <v>69</v>
       </c>
@@ -6331,7 +6340,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="66" spans="2:30">
+    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>70</v>
       </c>
@@ -6420,82 +6429,82 @@
         <v>15</v>
       </c>
     </row>
-    <row r="67" spans="2:30" hidden="1"/>
-    <row r="68" spans="2:30">
-      <c r="B68" s="29" t="s">
+    <row r="67" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B68" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C68" s="30"/>
-      <c r="D68" s="30"/>
-      <c r="E68" s="30"/>
-      <c r="F68" s="30"/>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="30"/>
-      <c r="J68" s="30"/>
-      <c r="K68" s="30"/>
-      <c r="L68" s="30"/>
-      <c r="M68" s="30"/>
-      <c r="N68" s="30"/>
-      <c r="O68" s="30"/>
-      <c r="P68" s="30"/>
-      <c r="Q68" s="30"/>
-      <c r="R68" s="30"/>
-      <c r="S68" s="30"/>
-      <c r="T68" s="30"/>
-      <c r="U68" s="30"/>
-      <c r="V68" s="30"/>
-      <c r="W68" s="30"/>
-      <c r="X68" s="30"/>
-      <c r="Y68" s="30"/>
-      <c r="Z68" s="30"/>
-      <c r="AA68" s="30"/>
-      <c r="AB68" s="30"/>
-      <c r="AC68" s="30"/>
-      <c r="AD68" s="30"/>
-    </row>
-    <row r="69" spans="2:30">
+      <c r="C68" s="29"/>
+      <c r="D68" s="29"/>
+      <c r="E68" s="29"/>
+      <c r="F68" s="29"/>
+      <c r="G68" s="29"/>
+      <c r="H68" s="29"/>
+      <c r="I68" s="29"/>
+      <c r="J68" s="29"/>
+      <c r="K68" s="29"/>
+      <c r="L68" s="29"/>
+      <c r="M68" s="29"/>
+      <c r="N68" s="29"/>
+      <c r="O68" s="29"/>
+      <c r="P68" s="29"/>
+      <c r="Q68" s="29"/>
+      <c r="R68" s="29"/>
+      <c r="S68" s="29"/>
+      <c r="T68" s="29"/>
+      <c r="U68" s="29"/>
+      <c r="V68" s="29"/>
+      <c r="W68" s="29"/>
+      <c r="X68" s="29"/>
+      <c r="Y68" s="29"/>
+      <c r="Z68" s="29"/>
+      <c r="AA68" s="29"/>
+      <c r="AB68" s="29"/>
+      <c r="AC68" s="29"/>
+      <c r="AD68" s="29"/>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C69" s="27" t="s">
+      <c r="C69" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="28"/>
-      <c r="I69" s="28"/>
-      <c r="J69" s="27" t="s">
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="28"/>
-      <c r="N69" s="28"/>
-      <c r="O69" s="28"/>
-      <c r="P69" s="28"/>
-      <c r="Q69" s="27" t="s">
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31"/>
+      <c r="Q69" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="R69" s="28"/>
-      <c r="S69" s="28"/>
-      <c r="T69" s="28"/>
-      <c r="U69" s="28"/>
-      <c r="V69" s="28"/>
-      <c r="W69" s="28"/>
-      <c r="X69" s="27" t="s">
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
+      <c r="X69" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="Y69" s="28"/>
-      <c r="Z69" s="28"/>
-      <c r="AA69" s="28"/>
-      <c r="AB69" s="28"/>
-      <c r="AC69" s="28"/>
-      <c r="AD69" s="28"/>
-    </row>
-    <row r="70" spans="2:30">
+      <c r="Y69" s="31"/>
+      <c r="Z69" s="31"/>
+      <c r="AA69" s="31"/>
+      <c r="AB69" s="31"/>
+      <c r="AC69" s="31"/>
+      <c r="AD69" s="31"/>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B70" s="1"/>
       <c r="C70" s="2" t="s">
         <v>87</v>
@@ -6582,7 +6591,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" spans="2:30">
+    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
         <v>67</v>
       </c>
@@ -6671,7 +6680,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="72" spans="2:30">
+    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>68</v>
       </c>
@@ -6760,7 +6769,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="73" spans="2:30">
+    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
         <v>69</v>
       </c>
@@ -6849,7 +6858,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="74" spans="2:30">
+    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>70</v>
       </c>
@@ -6938,49 +6947,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30" hidden="1"/>
-    <row r="76" spans="2:30" hidden="1">
+    <row r="75" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C76" s="27" t="s">
+      <c r="C76" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D76" s="28"/>
-      <c r="E76" s="28"/>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
-      <c r="H76" s="28"/>
-      <c r="I76" s="28"/>
-      <c r="J76" s="27" t="s">
+      <c r="D76" s="31"/>
+      <c r="E76" s="31"/>
+      <c r="F76" s="31"/>
+      <c r="G76" s="31"/>
+      <c r="H76" s="31"/>
+      <c r="I76" s="31"/>
+      <c r="J76" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="K76" s="28"/>
-      <c r="L76" s="28"/>
-      <c r="M76" s="28"/>
-      <c r="N76" s="28"/>
-      <c r="O76" s="28"/>
-      <c r="P76" s="28"/>
-      <c r="Q76" s="27" t="s">
+      <c r="K76" s="31"/>
+      <c r="L76" s="31"/>
+      <c r="M76" s="31"/>
+      <c r="N76" s="31"/>
+      <c r="O76" s="31"/>
+      <c r="P76" s="31"/>
+      <c r="Q76" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="R76" s="28"/>
-      <c r="S76" s="28"/>
-      <c r="T76" s="28"/>
-      <c r="U76" s="28"/>
-      <c r="V76" s="28"/>
-      <c r="W76" s="28"/>
-      <c r="X76" s="27" t="s">
+      <c r="R76" s="31"/>
+      <c r="S76" s="31"/>
+      <c r="T76" s="31"/>
+      <c r="U76" s="31"/>
+      <c r="V76" s="31"/>
+      <c r="W76" s="31"/>
+      <c r="X76" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="Y76" s="28"/>
-      <c r="Z76" s="28"/>
-      <c r="AA76" s="28"/>
-      <c r="AB76" s="28"/>
-      <c r="AC76" s="28"/>
-      <c r="AD76" s="28"/>
-    </row>
-    <row r="77" spans="2:30" hidden="1">
+      <c r="Y76" s="31"/>
+      <c r="Z76" s="31"/>
+      <c r="AA76" s="31"/>
+      <c r="AB76" s="31"/>
+      <c r="AC76" s="31"/>
+      <c r="AD76" s="31"/>
+    </row>
+    <row r="77" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B77" s="1"/>
       <c r="C77" s="2" t="s">
         <v>88</v>
@@ -7067,7 +7076,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="78" spans="2:30">
+    <row r="78" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
         <v>67</v>
       </c>
@@ -7156,7 +7165,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30">
+    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>68</v>
       </c>
@@ -7245,7 +7254,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="80" spans="2:30">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
         <v>69</v>
       </c>
@@ -7334,7 +7343,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="81" spans="2:30">
+    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>70</v>
       </c>
@@ -7423,49 +7432,49 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30" hidden="1"/>
-    <row r="83" spans="2:30" hidden="1">
+    <row r="82" spans="2:30" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C83" s="27" t="s">
+      <c r="C83" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D83" s="28"/>
-      <c r="E83" s="28"/>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
-      <c r="H83" s="28"/>
-      <c r="I83" s="28"/>
-      <c r="J83" s="27" t="s">
+      <c r="D83" s="31"/>
+      <c r="E83" s="31"/>
+      <c r="F83" s="31"/>
+      <c r="G83" s="31"/>
+      <c r="H83" s="31"/>
+      <c r="I83" s="31"/>
+      <c r="J83" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="K83" s="28"/>
-      <c r="L83" s="28"/>
-      <c r="M83" s="28"/>
-      <c r="N83" s="28"/>
-      <c r="O83" s="28"/>
-      <c r="P83" s="28"/>
-      <c r="Q83" s="27" t="s">
+      <c r="K83" s="31"/>
+      <c r="L83" s="31"/>
+      <c r="M83" s="31"/>
+      <c r="N83" s="31"/>
+      <c r="O83" s="31"/>
+      <c r="P83" s="31"/>
+      <c r="Q83" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="R83" s="28"/>
-      <c r="S83" s="28"/>
-      <c r="T83" s="28"/>
-      <c r="U83" s="28"/>
-      <c r="V83" s="28"/>
-      <c r="W83" s="28"/>
-      <c r="X83" s="27" t="s">
+      <c r="R83" s="31"/>
+      <c r="S83" s="31"/>
+      <c r="T83" s="31"/>
+      <c r="U83" s="31"/>
+      <c r="V83" s="31"/>
+      <c r="W83" s="31"/>
+      <c r="X83" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="Y83" s="28"/>
-      <c r="Z83" s="28"/>
-      <c r="AA83" s="28"/>
-      <c r="AB83" s="28"/>
-      <c r="AC83" s="28"/>
-      <c r="AD83" s="28"/>
-    </row>
-    <row r="84" spans="2:30" hidden="1">
+      <c r="Y83" s="31"/>
+      <c r="Z83" s="31"/>
+      <c r="AA83" s="31"/>
+      <c r="AB83" s="31"/>
+      <c r="AC83" s="31"/>
+      <c r="AD83" s="31"/>
+    </row>
+    <row r="84" spans="2:30" hidden="1" x14ac:dyDescent="0.25">
       <c r="B84" s="1"/>
       <c r="C84" s="2" t="s">
         <v>89</v>
@@ -7552,7 +7561,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="85" spans="2:30">
+    <row r="85" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
         <v>67</v>
       </c>
@@ -7641,7 +7650,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30">
+    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>68</v>
       </c>
@@ -7730,7 +7739,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="87" spans="2:30">
+    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
         <v>69</v>
       </c>
@@ -7819,7 +7828,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="88" spans="2:30">
+    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>70</v>
       </c>
@@ -7910,35 +7919,17 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="B2:AD2"/>
-    <mergeCell ref="C3:I3"/>
-    <mergeCell ref="J3:P3"/>
-    <mergeCell ref="Q3:W3"/>
-    <mergeCell ref="X3:AD3"/>
-    <mergeCell ref="AF25:AL25"/>
-    <mergeCell ref="AF10:AL10"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="J17:P17"/>
-    <mergeCell ref="Q17:W17"/>
-    <mergeCell ref="X17:AD17"/>
-    <mergeCell ref="AF17:AL17"/>
-    <mergeCell ref="X10:AD10"/>
-    <mergeCell ref="Q10:W10"/>
-    <mergeCell ref="J10:P10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="C39:I39"/>
-    <mergeCell ref="J39:P39"/>
-    <mergeCell ref="Q39:W39"/>
-    <mergeCell ref="X39:AD39"/>
-    <mergeCell ref="B24:AD24"/>
-    <mergeCell ref="C25:I25"/>
-    <mergeCell ref="J25:P25"/>
-    <mergeCell ref="Q25:W25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C32:I32"/>
-    <mergeCell ref="J32:P32"/>
-    <mergeCell ref="Q32:W32"/>
-    <mergeCell ref="X32:AD32"/>
+    <mergeCell ref="C83:I83"/>
+    <mergeCell ref="J83:P83"/>
+    <mergeCell ref="Q83:W83"/>
+    <mergeCell ref="X83:AD83"/>
+    <mergeCell ref="Q61:W61"/>
+    <mergeCell ref="X61:AD61"/>
+    <mergeCell ref="B68:AD68"/>
+    <mergeCell ref="C76:I76"/>
+    <mergeCell ref="J76:P76"/>
+    <mergeCell ref="Q76:W76"/>
+    <mergeCell ref="X76:AD76"/>
     <mergeCell ref="AF32:AL32"/>
     <mergeCell ref="C69:I69"/>
     <mergeCell ref="J69:P69"/>
@@ -7955,17 +7946,35 @@
     <mergeCell ref="X54:AD54"/>
     <mergeCell ref="C61:I61"/>
     <mergeCell ref="J61:P61"/>
-    <mergeCell ref="Q61:W61"/>
-    <mergeCell ref="X61:AD61"/>
-    <mergeCell ref="B68:AD68"/>
-    <mergeCell ref="C76:I76"/>
-    <mergeCell ref="J76:P76"/>
-    <mergeCell ref="Q76:W76"/>
-    <mergeCell ref="X76:AD76"/>
-    <mergeCell ref="C83:I83"/>
-    <mergeCell ref="J83:P83"/>
-    <mergeCell ref="Q83:W83"/>
-    <mergeCell ref="X83:AD83"/>
+    <mergeCell ref="C39:I39"/>
+    <mergeCell ref="J39:P39"/>
+    <mergeCell ref="Q39:W39"/>
+    <mergeCell ref="X39:AD39"/>
+    <mergeCell ref="B24:AD24"/>
+    <mergeCell ref="C25:I25"/>
+    <mergeCell ref="J25:P25"/>
+    <mergeCell ref="Q25:W25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C32:I32"/>
+    <mergeCell ref="J32:P32"/>
+    <mergeCell ref="Q32:W32"/>
+    <mergeCell ref="X32:AD32"/>
+    <mergeCell ref="AF25:AL25"/>
+    <mergeCell ref="AF10:AL10"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q17:W17"/>
+    <mergeCell ref="X17:AD17"/>
+    <mergeCell ref="AF17:AL17"/>
+    <mergeCell ref="X10:AD10"/>
+    <mergeCell ref="Q10:W10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="B2:AD2"/>
+    <mergeCell ref="C3:I3"/>
+    <mergeCell ref="J3:P3"/>
+    <mergeCell ref="Q3:W3"/>
+    <mergeCell ref="X3:AD3"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -7975,103 +7984,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:AU91"/>
-  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="15.6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:AU113"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="9" customWidth="1"/>
-    <col min="2" max="2" width="10.3984375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="9" customWidth="1"/>
     <col min="3" max="30" width="7" style="9" customWidth="1"/>
     <col min="31" max="31" width="2" style="9" customWidth="1"/>
-    <col min="32" max="32" width="3.296875" style="26" customWidth="1"/>
-    <col min="33" max="16384" width="8.69921875" style="9"/>
+    <col min="32" max="32" width="3.25" style="26" customWidth="1"/>
+    <col min="33" max="16384" width="8.75" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:47">
+    <row r="2" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B2" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="2:47">
+    <row r="3" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B3" s="10" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:47">
-      <c r="B5" s="29" t="s">
+    <row r="5" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30"/>
-      <c r="AD5" s="30"/>
-    </row>
-    <row r="6" spans="2:47">
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
+      <c r="H5" s="29"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="29"/>
+      <c r="K5" s="29"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="29"/>
+      <c r="N5" s="29"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="29"/>
+      <c r="Q5" s="29"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="29"/>
+      <c r="T5" s="29"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="29"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="29"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29"/>
+      <c r="AC5" s="29"/>
+      <c r="AD5" s="29"/>
+    </row>
+    <row r="6" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28"/>
-      <c r="H6" s="28"/>
-      <c r="I6" s="28"/>
-      <c r="J6" s="27" t="s">
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="28"/>
-      <c r="Q6" s="27" t="s">
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="R6" s="28"/>
-      <c r="S6" s="28"/>
-      <c r="T6" s="28"/>
-      <c r="U6" s="28"/>
-      <c r="V6" s="28"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="27" t="s">
+      <c r="R6" s="31"/>
+      <c r="S6" s="31"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="Y6" s="28"/>
-      <c r="Z6" s="28"/>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="28"/>
-      <c r="AC6" s="28"/>
-      <c r="AD6" s="28"/>
-    </row>
-    <row r="7" spans="2:47">
+      <c r="Y6" s="31"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+    </row>
+    <row r="7" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B7" s="1"/>
       <c r="C7" s="2" t="s">
         <v>75</v>
@@ -8158,7 +8167,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="2:47">
+    <row r="8" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
         <v>67</v>
       </c>
@@ -8247,7 +8256,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="2:47">
+    <row r="9" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B9" s="1" t="s">
         <v>68</v>
       </c>
@@ -8336,7 +8345,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="2:47">
+    <row r="10" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>69</v>
       </c>
@@ -8425,7 +8434,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:47">
+    <row r="11" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
         <v>70</v>
       </c>
@@ -8514,7 +8523,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="2:47">
+    <row r="12" spans="2:47" x14ac:dyDescent="0.25">
       <c r="AO12" s="20" t="s">
         <v>96</v>
       </c>
@@ -8522,55 +8531,55 @@
       <c r="AQ12" s="20"/>
       <c r="AR12" s="20"/>
     </row>
-    <row r="13" spans="2:47">
+    <row r="13" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="28"/>
-      <c r="J13" s="27" t="s">
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28"/>
-      <c r="P13" s="28"/>
-      <c r="Q13" s="27" t="s">
+      <c r="K13" s="31"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="31"/>
+      <c r="Q13" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="R13" s="28"/>
-      <c r="S13" s="28"/>
-      <c r="T13" s="28"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="28"/>
-      <c r="W13" s="28"/>
-      <c r="X13" s="27" t="s">
+      <c r="R13" s="31"/>
+      <c r="S13" s="31"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28"/>
-      <c r="AB13" s="28"/>
-      <c r="AC13" s="28"/>
-      <c r="AD13" s="28"/>
-      <c r="AG13" s="27" t="s">
+      <c r="Y13" s="31"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="31"/>
+      <c r="AG13" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AH13" s="28"/>
-      <c r="AI13" s="28"/>
-      <c r="AJ13" s="28"/>
-      <c r="AK13" s="28"/>
-      <c r="AL13" s="28"/>
-      <c r="AM13" s="28"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="31"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="31"/>
       <c r="AN13" s="18"/>
       <c r="AO13" s="21" t="s">
         <v>90</v>
@@ -8582,7 +8591,7 @@
       <c r="AT13" s="18"/>
       <c r="AU13" s="18"/>
     </row>
-    <row r="14" spans="2:47">
+    <row r="14" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
         <v>78</v>
@@ -8712,7 +8721,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="2:47">
+    <row r="15" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
         <v>67</v>
       </c>
@@ -8848,7 +8857,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="2:47">
+    <row r="16" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
         <v>68</v>
       </c>
@@ -8984,7 +8993,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="2:47">
+    <row r="17" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -9120,7 +9129,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="2:47">
+    <row r="18" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
         <v>70</v>
       </c>
@@ -9256,7 +9265,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="19" spans="2:47">
+    <row r="19" spans="2:47" x14ac:dyDescent="0.25">
       <c r="AG19" s="18"/>
       <c r="AH19" s="18"/>
       <c r="AI19" s="18"/>
@@ -9273,55 +9282,55 @@
       <c r="AT19" s="18"/>
       <c r="AU19" s="18"/>
     </row>
-    <row r="20" spans="2:47">
+    <row r="20" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="27" t="s">
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="27" t="s">
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="27" t="s">
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
-      <c r="AA20" s="28"/>
-      <c r="AB20" s="28"/>
-      <c r="AC20" s="28"/>
-      <c r="AD20" s="28"/>
-      <c r="AG20" s="27" t="s">
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="31"/>
+      <c r="AG20" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AH20" s="28"/>
-      <c r="AI20" s="28"/>
-      <c r="AJ20" s="28"/>
-      <c r="AK20" s="28"/>
-      <c r="AL20" s="28"/>
-      <c r="AM20" s="28"/>
+      <c r="AH20" s="31"/>
+      <c r="AI20" s="31"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="31"/>
+      <c r="AL20" s="31"/>
+      <c r="AM20" s="31"/>
       <c r="AN20" s="18"/>
       <c r="AO20" s="21" t="s">
         <v>91</v>
@@ -9333,7 +9342,7 @@
       <c r="AT20" s="18"/>
       <c r="AU20" s="18"/>
     </row>
-    <row r="21" spans="2:47">
+    <row r="21" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B21" s="1"/>
       <c r="C21" s="2" t="s">
         <v>79</v>
@@ -9463,7 +9472,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="2:47">
+    <row r="22" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B22" s="1" t="s">
         <v>67</v>
       </c>
@@ -9599,7 +9608,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="23" spans="2:47">
+    <row r="23" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B23" s="1" t="s">
         <v>68</v>
       </c>
@@ -9735,7 +9744,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:47">
+    <row r="24" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
@@ -9871,7 +9880,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="2:47">
+    <row r="25" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
         <v>70</v>
       </c>
@@ -10007,38 +10016,38 @@
         <v>15</v>
       </c>
     </row>
-    <row r="27" spans="2:47">
-      <c r="B27" s="29" t="s">
+    <row r="27" spans="2:47" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="30"/>
-      <c r="I27" s="30"/>
-      <c r="J27" s="30"/>
-      <c r="K27" s="30"/>
-      <c r="L27" s="30"/>
-      <c r="M27" s="30"/>
-      <c r="N27" s="30"/>
-      <c r="O27" s="30"/>
-      <c r="P27" s="30"/>
-      <c r="Q27" s="30"/>
-      <c r="R27" s="30"/>
-      <c r="S27" s="30"/>
-      <c r="T27" s="30"/>
-      <c r="U27" s="30"/>
-      <c r="V27" s="30"/>
-      <c r="W27" s="30"/>
-      <c r="X27" s="30"/>
-      <c r="Y27" s="30"/>
-      <c r="Z27" s="30"/>
-      <c r="AA27" s="30"/>
-      <c r="AB27" s="30"/>
-      <c r="AC27" s="30"/>
-      <c r="AD27" s="30"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="29"/>
+      <c r="E27" s="29"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="29"/>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="29"/>
+      <c r="K27" s="29"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="29"/>
+      <c r="W27" s="29"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="29"/>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29"/>
+      <c r="AC27" s="29"/>
+      <c r="AD27" s="29"/>
       <c r="AO27" s="20" t="s">
         <v>95</v>
       </c>
@@ -10046,55 +10055,55 @@
       <c r="AQ27" s="20"/>
       <c r="AR27" s="20"/>
     </row>
-    <row r="28" spans="2:47">
+    <row r="28" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="27" t="s">
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28"/>
-      <c r="P28" s="28"/>
-      <c r="Q28" s="27" t="s">
+      <c r="K28" s="31"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="31"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="R28" s="28"/>
-      <c r="S28" s="28"/>
-      <c r="T28" s="28"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="28"/>
-      <c r="X28" s="27" t="s">
+      <c r="R28" s="31"/>
+      <c r="S28" s="31"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="Y28" s="28"/>
-      <c r="Z28" s="28"/>
-      <c r="AA28" s="28"/>
-      <c r="AB28" s="28"/>
-      <c r="AC28" s="28"/>
-      <c r="AD28" s="28"/>
-      <c r="AG28" s="27" t="s">
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="31"/>
+      <c r="AG28" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AH28" s="28"/>
-      <c r="AI28" s="28"/>
-      <c r="AJ28" s="28"/>
-      <c r="AK28" s="28"/>
-      <c r="AL28" s="28"/>
-      <c r="AM28" s="28"/>
+      <c r="AH28" s="31"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="31"/>
       <c r="AN28" s="18"/>
       <c r="AO28" s="21" t="s">
         <v>90</v>
@@ -10106,7 +10115,7 @@
       <c r="AT28" s="18"/>
       <c r="AU28" s="18"/>
     </row>
-    <row r="29" spans="2:47">
+    <row r="29" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B29" s="1"/>
       <c r="C29" s="14" t="s">
         <v>80</v>
@@ -10236,7 +10245,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="30" spans="2:47">
+    <row r="30" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B30" s="1" t="s">
         <v>67</v>
       </c>
@@ -10370,7 +10379,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="31" spans="2:47">
+    <row r="31" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
         <v>68</v>
       </c>
@@ -10504,7 +10513,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="2:47">
+    <row r="32" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>69</v>
       </c>
@@ -10638,7 +10647,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="2:47">
+    <row r="33" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B33" s="1" t="s">
         <v>70</v>
       </c>
@@ -10772,7 +10781,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="2:47">
+    <row r="34" spans="2:47" x14ac:dyDescent="0.25">
       <c r="AG34" s="18"/>
       <c r="AH34" s="18"/>
       <c r="AI34" s="18"/>
@@ -10789,55 +10798,55 @@
       <c r="AT34" s="18"/>
       <c r="AU34" s="18"/>
     </row>
-    <row r="35" spans="2:47">
+    <row r="35" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="27" t="s">
+      <c r="C35" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="27" t="s">
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
+      <c r="F35" s="31"/>
+      <c r="G35" s="31"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28"/>
-      <c r="N35" s="28"/>
-      <c r="O35" s="28"/>
-      <c r="P35" s="28"/>
-      <c r="Q35" s="27" t="s">
+      <c r="K35" s="31"/>
+      <c r="L35" s="31"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
+      <c r="O35" s="31"/>
+      <c r="P35" s="31"/>
+      <c r="Q35" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="R35" s="28"/>
-      <c r="S35" s="28"/>
-      <c r="T35" s="28"/>
-      <c r="U35" s="28"/>
-      <c r="V35" s="28"/>
-      <c r="W35" s="28"/>
-      <c r="X35" s="27" t="s">
+      <c r="R35" s="31"/>
+      <c r="S35" s="31"/>
+      <c r="T35" s="31"/>
+      <c r="U35" s="31"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="Y35" s="28"/>
-      <c r="Z35" s="28"/>
-      <c r="AA35" s="28"/>
-      <c r="AB35" s="28"/>
-      <c r="AC35" s="28"/>
-      <c r="AD35" s="28"/>
-      <c r="AG35" s="27" t="s">
+      <c r="Y35" s="31"/>
+      <c r="Z35" s="31"/>
+      <c r="AA35" s="31"/>
+      <c r="AB35" s="31"/>
+      <c r="AC35" s="31"/>
+      <c r="AD35" s="31"/>
+      <c r="AG35" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AH35" s="28"/>
-      <c r="AI35" s="28"/>
-      <c r="AJ35" s="28"/>
-      <c r="AK35" s="28"/>
-      <c r="AL35" s="28"/>
-      <c r="AM35" s="28"/>
+      <c r="AH35" s="31"/>
+      <c r="AI35" s="31"/>
+      <c r="AJ35" s="31"/>
+      <c r="AK35" s="31"/>
+      <c r="AL35" s="31"/>
+      <c r="AM35" s="31"/>
       <c r="AN35" s="18"/>
       <c r="AO35" s="21" t="s">
         <v>91</v>
@@ -10849,7 +10858,7 @@
       <c r="AT35" s="18"/>
       <c r="AU35" s="18"/>
     </row>
-    <row r="36" spans="2:47" s="17" customFormat="1">
+    <row r="36" spans="2:47" s="17" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="s">
         <v>81</v>
@@ -10979,7 +10988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="2:47">
+    <row r="37" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B37" s="1" t="s">
         <v>67</v>
       </c>
@@ -11113,7 +11122,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="2:47">
+    <row r="38" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B38" s="1" t="s">
         <v>68</v>
       </c>
@@ -11247,7 +11256,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="2:47">
+    <row r="39" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B39" s="1" t="s">
         <v>69</v>
       </c>
@@ -11381,7 +11390,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="2:47">
+    <row r="40" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B40" s="1" t="s">
         <v>70</v>
       </c>
@@ -11515,48 +11524,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="2:47">
+    <row r="42" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="27" t="s">
+      <c r="C42" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="27" t="s">
+      <c r="D42" s="31"/>
+      <c r="E42" s="31"/>
+      <c r="F42" s="31"/>
+      <c r="G42" s="31"/>
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="K42" s="28"/>
-      <c r="L42" s="28"/>
-      <c r="M42" s="28"/>
-      <c r="N42" s="28"/>
-      <c r="O42" s="28"/>
-      <c r="P42" s="28"/>
-      <c r="Q42" s="27" t="s">
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+      <c r="M42" s="31"/>
+      <c r="N42" s="31"/>
+      <c r="O42" s="31"/>
+      <c r="P42" s="31"/>
+      <c r="Q42" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="R42" s="28"/>
-      <c r="S42" s="28"/>
-      <c r="T42" s="28"/>
-      <c r="U42" s="28"/>
-      <c r="V42" s="28"/>
-      <c r="W42" s="28"/>
-      <c r="X42" s="27" t="s">
+      <c r="R42" s="31"/>
+      <c r="S42" s="31"/>
+      <c r="T42" s="31"/>
+      <c r="U42" s="31"/>
+      <c r="V42" s="31"/>
+      <c r="W42" s="31"/>
+      <c r="X42" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="Y42" s="28"/>
-      <c r="Z42" s="28"/>
-      <c r="AA42" s="28"/>
-      <c r="AB42" s="28"/>
-      <c r="AC42" s="28"/>
-      <c r="AD42" s="28"/>
-    </row>
-    <row r="43" spans="2:47">
+      <c r="Y42" s="31"/>
+      <c r="Z42" s="31"/>
+      <c r="AA42" s="31"/>
+      <c r="AB42" s="31"/>
+      <c r="AC42" s="31"/>
+      <c r="AD42" s="31"/>
+    </row>
+    <row r="43" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B43" s="1"/>
       <c r="C43" s="14" t="s">
         <v>82</v>
@@ -11643,7 +11652,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="2:47">
+    <row r="44" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B44" s="1" t="s">
         <v>67</v>
       </c>
@@ -11732,7 +11741,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="45" spans="2:47">
+    <row r="45" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B45" s="1" t="s">
         <v>68</v>
       </c>
@@ -11821,7 +11830,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="46" spans="2:47">
+    <row r="46" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B46" s="1" t="s">
         <v>69</v>
       </c>
@@ -11910,7 +11919,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="2:47">
+    <row r="47" spans="2:47" x14ac:dyDescent="0.25">
       <c r="B47" s="1" t="s">
         <v>70</v>
       </c>
@@ -11999,81 +12008,81 @@
         <v>66</v>
       </c>
     </row>
-    <row r="49" spans="2:30">
-      <c r="B49" s="29" t="s">
+    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B49" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
-      <c r="AA49" s="30"/>
-      <c r="AB49" s="30"/>
-      <c r="AC49" s="30"/>
-      <c r="AD49" s="30"/>
-    </row>
-    <row r="50" spans="2:30">
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="29"/>
+      <c r="AA49" s="29"/>
+      <c r="AB49" s="29"/>
+      <c r="AC49" s="29"/>
+      <c r="AD49" s="29"/>
+    </row>
+    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C50" s="27" t="s">
+      <c r="C50" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="D50" s="28"/>
-      <c r="E50" s="28"/>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="27" t="s">
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+      <c r="G50" s="31"/>
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="K50" s="28"/>
-      <c r="L50" s="28"/>
-      <c r="M50" s="28"/>
-      <c r="N50" s="28"/>
-      <c r="O50" s="28"/>
-      <c r="P50" s="28"/>
-      <c r="Q50" s="27" t="s">
+      <c r="K50" s="31"/>
+      <c r="L50" s="31"/>
+      <c r="M50" s="31"/>
+      <c r="N50" s="31"/>
+      <c r="O50" s="31"/>
+      <c r="P50" s="31"/>
+      <c r="Q50" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="R50" s="28"/>
-      <c r="S50" s="28"/>
-      <c r="T50" s="28"/>
-      <c r="U50" s="28"/>
-      <c r="V50" s="28"/>
-      <c r="W50" s="28"/>
-      <c r="X50" s="27" t="s">
+      <c r="R50" s="31"/>
+      <c r="S50" s="31"/>
+      <c r="T50" s="31"/>
+      <c r="U50" s="31"/>
+      <c r="V50" s="31"/>
+      <c r="W50" s="31"/>
+      <c r="X50" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="Y50" s="28"/>
-      <c r="Z50" s="28"/>
-      <c r="AA50" s="28"/>
-      <c r="AB50" s="28"/>
-      <c r="AC50" s="28"/>
-      <c r="AD50" s="28"/>
-    </row>
-    <row r="51" spans="2:30">
+      <c r="Y50" s="31"/>
+      <c r="Z50" s="31"/>
+      <c r="AA50" s="31"/>
+      <c r="AB50" s="31"/>
+      <c r="AC50" s="31"/>
+      <c r="AD50" s="31"/>
+    </row>
+    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B51" s="1"/>
       <c r="C51" s="2" t="s">
         <v>83</v>
@@ -12160,7 +12169,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="2:30">
+    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
         <v>67</v>
       </c>
@@ -12249,7 +12258,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="53" spans="2:30">
+    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
         <v>68</v>
       </c>
@@ -12338,7 +12347,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="54" spans="2:30">
+    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B54" s="1" t="s">
         <v>69</v>
       </c>
@@ -12427,7 +12436,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="2:30">
+    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
         <v>70</v>
       </c>
@@ -12516,48 +12525,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="57" spans="2:30">
+    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C57" s="27" t="s">
+      <c r="C57" s="30" t="s">
         <v>44</v>
       </c>
-      <c r="D57" s="28"/>
-      <c r="E57" s="28"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="27" t="s">
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="K57" s="28"/>
-      <c r="L57" s="28"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="28"/>
-      <c r="P57" s="28"/>
-      <c r="Q57" s="27" t="s">
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="R57" s="28"/>
-      <c r="S57" s="28"/>
-      <c r="T57" s="28"/>
-      <c r="U57" s="28"/>
-      <c r="V57" s="28"/>
-      <c r="W57" s="28"/>
-      <c r="X57" s="27" t="s">
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="31"/>
+      <c r="W57" s="31"/>
+      <c r="X57" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="Y57" s="28"/>
-      <c r="Z57" s="28"/>
-      <c r="AA57" s="28"/>
-      <c r="AB57" s="28"/>
-      <c r="AC57" s="28"/>
-      <c r="AD57" s="28"/>
-    </row>
-    <row r="58" spans="2:30">
+      <c r="Y57" s="31"/>
+      <c r="Z57" s="31"/>
+      <c r="AA57" s="31"/>
+      <c r="AB57" s="31"/>
+      <c r="AC57" s="31"/>
+      <c r="AD57" s="31"/>
+    </row>
+    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B58" s="1"/>
       <c r="C58" s="2" t="s">
         <v>84</v>
@@ -12644,7 +12653,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:30">
+    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
         <v>67</v>
       </c>
@@ -12733,7 +12742,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="60" spans="2:30">
+    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
         <v>68</v>
       </c>
@@ -12822,7 +12831,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="61" spans="2:30">
+    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>69</v>
       </c>
@@ -12911,7 +12920,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="62" spans="2:30">
+    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
         <v>70</v>
       </c>
@@ -13000,48 +13009,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="64" spans="2:30">
+    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C64" s="27" t="s">
+      <c r="C64" s="30" t="s">
         <v>48</v>
       </c>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="27" t="s">
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="27" t="s">
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="30" t="s">
         <v>50</v>
       </c>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="27" t="s">
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="30" t="s">
         <v>51</v>
       </c>
-      <c r="Y64" s="28"/>
-      <c r="Z64" s="28"/>
-      <c r="AA64" s="28"/>
-      <c r="AB64" s="28"/>
-      <c r="AC64" s="28"/>
-      <c r="AD64" s="28"/>
-    </row>
-    <row r="65" spans="2:30">
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
+      <c r="AA64" s="31"/>
+      <c r="AB64" s="31"/>
+      <c r="AC64" s="31"/>
+      <c r="AD64" s="31"/>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B65" s="1"/>
       <c r="C65" s="2" t="s">
         <v>86</v>
@@ -13128,7 +13137,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="66" spans="2:30">
+    <row r="66" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
         <v>67</v>
       </c>
@@ -13217,7 +13226,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="2:30">
+    <row r="67" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
         <v>68</v>
       </c>
@@ -13306,7 +13315,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="2:30">
+    <row r="68" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
         <v>69</v>
       </c>
@@ -13395,7 +13404,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="69" spans="2:30">
+    <row r="69" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
         <v>70</v>
       </c>
@@ -13484,81 +13493,81 @@
         <v>15</v>
       </c>
     </row>
-    <row r="71" spans="2:30">
-      <c r="B71" s="29" t="s">
+    <row r="71" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B71" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C71" s="30"/>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="30"/>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="30"/>
-      <c r="J71" s="30"/>
-      <c r="K71" s="30"/>
-      <c r="L71" s="30"/>
-      <c r="M71" s="30"/>
-      <c r="N71" s="30"/>
-      <c r="O71" s="30"/>
-      <c r="P71" s="30"/>
-      <c r="Q71" s="30"/>
-      <c r="R71" s="30"/>
-      <c r="S71" s="30"/>
-      <c r="T71" s="30"/>
-      <c r="U71" s="30"/>
-      <c r="V71" s="30"/>
-      <c r="W71" s="30"/>
-      <c r="X71" s="30"/>
-      <c r="Y71" s="30"/>
-      <c r="Z71" s="30"/>
-      <c r="AA71" s="30"/>
-      <c r="AB71" s="30"/>
-      <c r="AC71" s="30"/>
-      <c r="AD71" s="30"/>
-    </row>
-    <row r="72" spans="2:30">
+      <c r="C71" s="29"/>
+      <c r="D71" s="29"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="29"/>
+      <c r="G71" s="29"/>
+      <c r="H71" s="29"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="29"/>
+      <c r="K71" s="29"/>
+      <c r="L71" s="29"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="29"/>
+      <c r="O71" s="29"/>
+      <c r="P71" s="29"/>
+      <c r="Q71" s="29"/>
+      <c r="R71" s="29"/>
+      <c r="S71" s="29"/>
+      <c r="T71" s="29"/>
+      <c r="U71" s="29"/>
+      <c r="V71" s="29"/>
+      <c r="W71" s="29"/>
+      <c r="X71" s="29"/>
+      <c r="Y71" s="29"/>
+      <c r="Z71" s="29"/>
+      <c r="AA71" s="29"/>
+      <c r="AB71" s="29"/>
+      <c r="AC71" s="29"/>
+      <c r="AD71" s="29"/>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C72" s="27" t="s">
+      <c r="C72" s="30" t="s">
         <v>53</v>
       </c>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
-      <c r="H72" s="28"/>
-      <c r="I72" s="28"/>
-      <c r="J72" s="27" t="s">
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="K72" s="28"/>
-      <c r="L72" s="28"/>
-      <c r="M72" s="28"/>
-      <c r="N72" s="28"/>
-      <c r="O72" s="28"/>
-      <c r="P72" s="28"/>
-      <c r="Q72" s="27" t="s">
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="R72" s="28"/>
-      <c r="S72" s="28"/>
-      <c r="T72" s="28"/>
-      <c r="U72" s="28"/>
-      <c r="V72" s="28"/>
-      <c r="W72" s="28"/>
-      <c r="X72" s="27" t="s">
+      <c r="R72" s="31"/>
+      <c r="S72" s="31"/>
+      <c r="T72" s="31"/>
+      <c r="U72" s="31"/>
+      <c r="V72" s="31"/>
+      <c r="W72" s="31"/>
+      <c r="X72" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="Y72" s="28"/>
-      <c r="Z72" s="28"/>
-      <c r="AA72" s="28"/>
-      <c r="AB72" s="28"/>
-      <c r="AC72" s="28"/>
-      <c r="AD72" s="28"/>
-    </row>
-    <row r="73" spans="2:30">
+      <c r="Y72" s="31"/>
+      <c r="Z72" s="31"/>
+      <c r="AA72" s="31"/>
+      <c r="AB72" s="31"/>
+      <c r="AC72" s="31"/>
+      <c r="AD72" s="31"/>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B73" s="1"/>
       <c r="C73" s="2" t="s">
         <v>87</v>
@@ -13645,7 +13654,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:30">
+    <row r="74" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
         <v>67</v>
       </c>
@@ -13734,7 +13743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="75" spans="2:30">
+    <row r="75" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
         <v>68</v>
       </c>
@@ -13823,7 +13832,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="2:30">
+    <row r="76" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
         <v>69</v>
       </c>
@@ -13912,7 +13921,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="77" spans="2:30">
+    <row r="77" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
         <v>70</v>
       </c>
@@ -14001,48 +14010,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="79" spans="2:30">
+    <row r="79" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D79" s="28"/>
-      <c r="E79" s="28"/>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
-      <c r="H79" s="28"/>
-      <c r="I79" s="28"/>
-      <c r="J79" s="27" t="s">
+      <c r="D79" s="31"/>
+      <c r="E79" s="31"/>
+      <c r="F79" s="31"/>
+      <c r="G79" s="31"/>
+      <c r="H79" s="31"/>
+      <c r="I79" s="31"/>
+      <c r="J79" s="30" t="s">
         <v>58</v>
       </c>
-      <c r="K79" s="28"/>
-      <c r="L79" s="28"/>
-      <c r="M79" s="28"/>
-      <c r="N79" s="28"/>
-      <c r="O79" s="28"/>
-      <c r="P79" s="28"/>
-      <c r="Q79" s="27" t="s">
+      <c r="K79" s="31"/>
+      <c r="L79" s="31"/>
+      <c r="M79" s="31"/>
+      <c r="N79" s="31"/>
+      <c r="O79" s="31"/>
+      <c r="P79" s="31"/>
+      <c r="Q79" s="30" t="s">
         <v>59</v>
       </c>
-      <c r="R79" s="28"/>
-      <c r="S79" s="28"/>
-      <c r="T79" s="28"/>
-      <c r="U79" s="28"/>
-      <c r="V79" s="28"/>
-      <c r="W79" s="28"/>
-      <c r="X79" s="27" t="s">
+      <c r="R79" s="31"/>
+      <c r="S79" s="31"/>
+      <c r="T79" s="31"/>
+      <c r="U79" s="31"/>
+      <c r="V79" s="31"/>
+      <c r="W79" s="31"/>
+      <c r="X79" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="Y79" s="28"/>
-      <c r="Z79" s="28"/>
-      <c r="AA79" s="28"/>
-      <c r="AB79" s="28"/>
-      <c r="AC79" s="28"/>
-      <c r="AD79" s="28"/>
-    </row>
-    <row r="80" spans="2:30">
+      <c r="Y79" s="31"/>
+      <c r="Z79" s="31"/>
+      <c r="AA79" s="31"/>
+      <c r="AB79" s="31"/>
+      <c r="AC79" s="31"/>
+      <c r="AD79" s="31"/>
+    </row>
+    <row r="80" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B80" s="1"/>
       <c r="C80" s="2" t="s">
         <v>88</v>
@@ -14129,7 +14138,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="2:30">
+    <row r="81" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
         <v>67</v>
       </c>
@@ -14218,7 +14227,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="82" spans="2:30">
+    <row r="82" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
         <v>68</v>
       </c>
@@ -14307,7 +14316,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="83" spans="2:30">
+    <row r="83" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
         <v>69</v>
       </c>
@@ -14396,7 +14405,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="84" spans="2:30">
+    <row r="84" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
         <v>70</v>
       </c>
@@ -14485,48 +14494,48 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="2:30">
+    <row r="86" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C86" s="27" t="s">
+      <c r="C86" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D86" s="28"/>
-      <c r="E86" s="28"/>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
-      <c r="H86" s="28"/>
-      <c r="I86" s="28"/>
-      <c r="J86" s="27" t="s">
+      <c r="D86" s="31"/>
+      <c r="E86" s="31"/>
+      <c r="F86" s="31"/>
+      <c r="G86" s="31"/>
+      <c r="H86" s="31"/>
+      <c r="I86" s="31"/>
+      <c r="J86" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="K86" s="28"/>
-      <c r="L86" s="28"/>
-      <c r="M86" s="28"/>
-      <c r="N86" s="28"/>
-      <c r="O86" s="28"/>
-      <c r="P86" s="28"/>
-      <c r="Q86" s="27" t="s">
+      <c r="K86" s="31"/>
+      <c r="L86" s="31"/>
+      <c r="M86" s="31"/>
+      <c r="N86" s="31"/>
+      <c r="O86" s="31"/>
+      <c r="P86" s="31"/>
+      <c r="Q86" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="R86" s="28"/>
-      <c r="S86" s="28"/>
-      <c r="T86" s="28"/>
-      <c r="U86" s="28"/>
-      <c r="V86" s="28"/>
-      <c r="W86" s="28"/>
-      <c r="X86" s="27" t="s">
+      <c r="R86" s="31"/>
+      <c r="S86" s="31"/>
+      <c r="T86" s="31"/>
+      <c r="U86" s="31"/>
+      <c r="V86" s="31"/>
+      <c r="W86" s="31"/>
+      <c r="X86" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="Y86" s="28"/>
-      <c r="Z86" s="28"/>
-      <c r="AA86" s="28"/>
-      <c r="AB86" s="28"/>
-      <c r="AC86" s="28"/>
-      <c r="AD86" s="28"/>
-    </row>
-    <row r="87" spans="2:30">
+      <c r="Y86" s="31"/>
+      <c r="Z86" s="31"/>
+      <c r="AA86" s="31"/>
+      <c r="AB86" s="31"/>
+      <c r="AC86" s="31"/>
+      <c r="AD86" s="31"/>
+    </row>
+    <row r="87" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B87" s="1"/>
       <c r="C87" s="2" t="s">
         <v>89</v>
@@ -14613,7 +14622,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="88" spans="2:30">
+    <row r="88" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
         <v>67</v>
       </c>
@@ -14702,7 +14711,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="89" spans="2:30">
+    <row r="89" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
         <v>68</v>
       </c>
@@ -14791,7 +14800,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="2:30">
+    <row r="90" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
         <v>69</v>
       </c>
@@ -14880,7 +14889,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="91" spans="2:30">
+    <row r="91" spans="2:30" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
         <v>70</v>
       </c>
@@ -14969,13 +14978,1603 @@
         <v>15</v>
       </c>
     </row>
+    <row r="93" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B93" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="C93" s="29"/>
+      <c r="D93" s="29"/>
+      <c r="E93" s="29"/>
+      <c r="F93" s="29"/>
+      <c r="G93" s="29"/>
+      <c r="H93" s="29"/>
+      <c r="I93" s="29"/>
+      <c r="J93" s="29"/>
+      <c r="K93" s="29"/>
+      <c r="L93" s="29"/>
+      <c r="M93" s="29"/>
+      <c r="N93" s="29"/>
+      <c r="O93" s="29"/>
+      <c r="P93" s="29"/>
+      <c r="Q93" s="29"/>
+      <c r="R93" s="29"/>
+      <c r="S93" s="29"/>
+      <c r="T93" s="29"/>
+      <c r="U93" s="29"/>
+      <c r="V93" s="29"/>
+      <c r="W93" s="29"/>
+      <c r="X93" s="29"/>
+      <c r="Y93" s="29"/>
+      <c r="Z93" s="29"/>
+      <c r="AA93" s="29"/>
+      <c r="AB93" s="29"/>
+      <c r="AC93" s="29"/>
+      <c r="AD93" s="29"/>
+    </row>
+    <row r="94" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D94" s="31"/>
+      <c r="E94" s="31"/>
+      <c r="F94" s="31"/>
+      <c r="G94" s="31"/>
+      <c r="H94" s="31"/>
+      <c r="I94" s="31"/>
+      <c r="J94" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K94" s="31"/>
+      <c r="L94" s="31"/>
+      <c r="M94" s="31"/>
+      <c r="N94" s="31"/>
+      <c r="O94" s="31"/>
+      <c r="P94" s="31"/>
+      <c r="Q94" s="30" t="s">
+        <v>55</v>
+      </c>
+      <c r="R94" s="31"/>
+      <c r="S94" s="31"/>
+      <c r="T94" s="31"/>
+      <c r="U94" s="31"/>
+      <c r="V94" s="31"/>
+      <c r="W94" s="31"/>
+      <c r="X94" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y94" s="31"/>
+      <c r="Z94" s="31"/>
+      <c r="AA94" s="31"/>
+      <c r="AB94" s="31"/>
+      <c r="AC94" s="31"/>
+      <c r="AD94" s="31"/>
+    </row>
+    <row r="95" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B95" s="1"/>
+      <c r="C95" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P95" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W95" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X95" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y95" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA95" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB95" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD95" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B96" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC96" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD96" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B97" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD97" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B98" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C98" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I98" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P98" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S98" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W98" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z98" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD98" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="99" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B99" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P99" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W99" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X99" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC99" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD99" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="100" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B100" s="27"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="27"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="27"/>
+      <c r="I100" s="27"/>
+      <c r="J100" s="27"/>
+      <c r="K100" s="27"/>
+      <c r="L100" s="27"/>
+      <c r="M100" s="27"/>
+      <c r="N100" s="27"/>
+      <c r="O100" s="27"/>
+      <c r="P100" s="27"/>
+      <c r="Q100" s="27"/>
+      <c r="R100" s="27"/>
+      <c r="S100" s="27"/>
+      <c r="T100" s="27"/>
+      <c r="U100" s="27"/>
+      <c r="V100" s="27"/>
+      <c r="W100" s="27"/>
+      <c r="X100" s="27"/>
+      <c r="Y100" s="27"/>
+      <c r="Z100" s="27"/>
+      <c r="AA100" s="27"/>
+      <c r="AB100" s="27"/>
+      <c r="AC100" s="27"/>
+      <c r="AD100" s="27"/>
+    </row>
+    <row r="101" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B101" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C101" s="30" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101" s="31"/>
+      <c r="E101" s="31"/>
+      <c r="F101" s="31"/>
+      <c r="G101" s="31"/>
+      <c r="H101" s="31"/>
+      <c r="I101" s="31"/>
+      <c r="J101" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="K101" s="31"/>
+      <c r="L101" s="31"/>
+      <c r="M101" s="31"/>
+      <c r="N101" s="31"/>
+      <c r="O101" s="31"/>
+      <c r="P101" s="31"/>
+      <c r="Q101" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="R101" s="31"/>
+      <c r="S101" s="31"/>
+      <c r="T101" s="31"/>
+      <c r="U101" s="31"/>
+      <c r="V101" s="31"/>
+      <c r="W101" s="31"/>
+      <c r="X101" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="Y101" s="31"/>
+      <c r="Z101" s="31"/>
+      <c r="AA101" s="31"/>
+      <c r="AB101" s="31"/>
+      <c r="AC101" s="31"/>
+      <c r="AD101" s="31"/>
+    </row>
+    <row r="102" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B102" s="1"/>
+      <c r="C102" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W102" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X102" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y102" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD102" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B103" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V103" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC103" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD103" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B104" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC104" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD104" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B105" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I105" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P105" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S105" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W105" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z105" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB105" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD105" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="106" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B106" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P106" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W106" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X106" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z106" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC106" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD106" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="107" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B107" s="27"/>
+      <c r="C107" s="27"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="27"/>
+      <c r="H107" s="27"/>
+      <c r="I107" s="27"/>
+      <c r="J107" s="27"/>
+      <c r="K107" s="27"/>
+      <c r="L107" s="27"/>
+      <c r="M107" s="27"/>
+      <c r="N107" s="27"/>
+      <c r="O107" s="27"/>
+      <c r="P107" s="27"/>
+      <c r="Q107" s="27"/>
+      <c r="R107" s="27"/>
+      <c r="S107" s="27"/>
+      <c r="T107" s="27"/>
+      <c r="U107" s="27"/>
+      <c r="V107" s="27"/>
+      <c r="W107" s="27"/>
+      <c r="X107" s="27"/>
+      <c r="Y107" s="27"/>
+      <c r="Z107" s="27"/>
+      <c r="AA107" s="27"/>
+      <c r="AB107" s="27"/>
+      <c r="AC107" s="27"/>
+      <c r="AD107" s="27"/>
+    </row>
+    <row r="108" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B108" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C108" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D108" s="31"/>
+      <c r="E108" s="31"/>
+      <c r="F108" s="31"/>
+      <c r="G108" s="31"/>
+      <c r="H108" s="31"/>
+      <c r="I108" s="31"/>
+      <c r="J108" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="K108" s="31"/>
+      <c r="L108" s="31"/>
+      <c r="M108" s="31"/>
+      <c r="N108" s="31"/>
+      <c r="O108" s="31"/>
+      <c r="P108" s="31"/>
+      <c r="Q108" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="R108" s="31"/>
+      <c r="S108" s="31"/>
+      <c r="T108" s="31"/>
+      <c r="U108" s="31"/>
+      <c r="V108" s="31"/>
+      <c r="W108" s="31"/>
+      <c r="X108" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="Y108" s="31"/>
+      <c r="Z108" s="31"/>
+      <c r="AA108" s="31"/>
+      <c r="AB108" s="31"/>
+      <c r="AC108" s="31"/>
+      <c r="AD108" s="31"/>
+    </row>
+    <row r="109" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B109" s="1"/>
+      <c r="C109" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="N109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="O109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="P109" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="S109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="T109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="V109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="W109" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="X109" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y109" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA109" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AB109" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="AC109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD109" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B110" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="G110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="P110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="R110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="S110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="T110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="U110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="V110" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="W110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X110" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Z110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AA110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AB110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AC110" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="AD110" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B111" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="K111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="O111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="P111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="T111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="W111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="X111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AA111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AB111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AC111" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD111" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="112" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B112" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I112" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="N112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O112" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P112" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="S112" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="T112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="U112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="V112" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="W112" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="X112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z112" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AA112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB112" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC112" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="AD112" s="12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="113" spans="2:30" x14ac:dyDescent="0.25">
+      <c r="B113" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="J113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="N113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P113" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="R113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="S113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="T113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="U113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="W113" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="X113" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="Y113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z113" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AB113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AC113" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD113" s="11" t="s">
+        <v>65</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="AG28:AM28"/>
-    <mergeCell ref="AG35:AM35"/>
-    <mergeCell ref="AG20:AM20"/>
-    <mergeCell ref="AG13:AM13"/>
-    <mergeCell ref="X13:AD13"/>
+  <mergeCells count="69">
+    <mergeCell ref="C101:I101"/>
+    <mergeCell ref="J101:P101"/>
+    <mergeCell ref="Q101:W101"/>
+    <mergeCell ref="X101:AD101"/>
+    <mergeCell ref="C108:I108"/>
+    <mergeCell ref="J108:P108"/>
+    <mergeCell ref="Q108:W108"/>
+    <mergeCell ref="X108:AD108"/>
+    <mergeCell ref="C86:I86"/>
+    <mergeCell ref="Q86:W86"/>
+    <mergeCell ref="J86:P86"/>
+    <mergeCell ref="B93:AD93"/>
+    <mergeCell ref="C94:I94"/>
+    <mergeCell ref="J94:P94"/>
+    <mergeCell ref="Q94:W94"/>
+    <mergeCell ref="X94:AD94"/>
+    <mergeCell ref="X86:AD86"/>
+    <mergeCell ref="X50:AD50"/>
+    <mergeCell ref="X79:AD79"/>
+    <mergeCell ref="Q79:W79"/>
+    <mergeCell ref="Q72:W72"/>
+    <mergeCell ref="B5:AD5"/>
+    <mergeCell ref="J64:P64"/>
+    <mergeCell ref="X72:AD72"/>
+    <mergeCell ref="X57:AD57"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="Q13:W13"/>
+    <mergeCell ref="X35:AD35"/>
+    <mergeCell ref="J28:P28"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="C72:I72"/>
+    <mergeCell ref="J35:P35"/>
+    <mergeCell ref="J57:P57"/>
+    <mergeCell ref="Q50:W50"/>
+    <mergeCell ref="C20:I20"/>
+    <mergeCell ref="C28:I28"/>
+    <mergeCell ref="J72:P72"/>
+    <mergeCell ref="C79:I79"/>
+    <mergeCell ref="J42:P42"/>
+    <mergeCell ref="C64:I64"/>
+    <mergeCell ref="Q64:W64"/>
+    <mergeCell ref="Q57:W57"/>
+    <mergeCell ref="C57:I57"/>
+    <mergeCell ref="B71:AD71"/>
+    <mergeCell ref="C42:I42"/>
+    <mergeCell ref="Q42:W42"/>
+    <mergeCell ref="J79:P79"/>
     <mergeCell ref="J6:P6"/>
     <mergeCell ref="X64:AD64"/>
     <mergeCell ref="X42:AD42"/>
@@ -14992,41 +16591,11 @@
     <mergeCell ref="C6:I6"/>
     <mergeCell ref="Q35:W35"/>
     <mergeCell ref="C50:I50"/>
-    <mergeCell ref="J72:P72"/>
-    <mergeCell ref="C79:I79"/>
-    <mergeCell ref="J42:P42"/>
-    <mergeCell ref="C64:I64"/>
-    <mergeCell ref="Q64:W64"/>
-    <mergeCell ref="Q57:W57"/>
-    <mergeCell ref="C57:I57"/>
-    <mergeCell ref="B5:AD5"/>
-    <mergeCell ref="J64:P64"/>
-    <mergeCell ref="X72:AD72"/>
-    <mergeCell ref="X57:AD57"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="Q13:W13"/>
-    <mergeCell ref="X35:AD35"/>
-    <mergeCell ref="J28:P28"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C72:I72"/>
-    <mergeCell ref="J35:P35"/>
-    <mergeCell ref="J57:P57"/>
-    <mergeCell ref="Q50:W50"/>
-    <mergeCell ref="C20:I20"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="B71:AD71"/>
-    <mergeCell ref="C42:I42"/>
-    <mergeCell ref="Q42:W42"/>
-    <mergeCell ref="X86:AD86"/>
-    <mergeCell ref="X50:AD50"/>
-    <mergeCell ref="X79:AD79"/>
-    <mergeCell ref="Q79:W79"/>
-    <mergeCell ref="Q72:W72"/>
-    <mergeCell ref="J79:P79"/>
-    <mergeCell ref="C86:I86"/>
-    <mergeCell ref="Q86:W86"/>
-    <mergeCell ref="J86:P86"/>
+    <mergeCell ref="AG28:AM28"/>
+    <mergeCell ref="AG35:AM35"/>
+    <mergeCell ref="AG20:AM20"/>
+    <mergeCell ref="AG13:AM13"/>
+    <mergeCell ref="X13:AD13"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
